--- a/FICO/FICO_3S_DCF_Joined.xlsx
+++ b/FICO/FICO_3S_DCF_Joined.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\(#,##0\)_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -28,10 +28,11 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="171" formatCode="0.0\x"/>
-    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="175" formatCode="_-* #,##0.00_-;\(#,##0.00\)_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0.00_-;\(#,##0.00\)_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="175" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -247,7 +248,7 @@
       <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -291,6 +292,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -346,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -474,7 +480,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -487,17 +493,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="33" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="33" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="25" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -514,6 +520,38 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="30" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="31" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="25" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="30" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="25" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="33" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="25" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="25" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -705,6 +743,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -715,7 +754,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Unlevered Free Cash Flow (linked)</a:t>
+              <a:t>Unlevered Free Cash Flow</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -763,7 +802,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Forecast year</a:t>
+                  <a:t>Fiscal year</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -846,7 +885,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3600000"/>
+    <ext cx="5760000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1153,7 +1192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1166,9 +1205,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1176,9 +1213,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -1214,9 +1249,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -1266,9 +1299,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1290,9 +1321,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -1314,9 +1343,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
@@ -1342,6 +1369,13 @@
       <c r="A30" t="inlineStr">
         <is>
           <t xml:space="preserve">  04_DCF!E21 begins with ='03_Three_Statement'!</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>DCF display values are fully computed (dates/taxes/Capex/UFCF/TV/EV) so nothing appears blank. Yellow cells remain editable inputs.</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U138"/>
+  <dimension ref="A1:N138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.88671875" customWidth="1" min="1" max="1"/>
@@ -1991,7 +2025,6 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -5294,18 +5327,6 @@
       <c r="M105" s="20" t="n"/>
       <c r="N105" s="20" t="n"/>
     </row>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
     <row r="118">
       <c r="C118" s="57" t="n"/>
       <c r="D118" s="57" t="n"/>
@@ -5315,7 +5336,6 @@
       <c r="C119" s="57" t="n"/>
       <c r="D119" s="57" t="n"/>
     </row>
-    <row r="120"/>
     <row r="121">
       <c r="B121" s="18" t="inlineStr">
         <is>
@@ -5397,7 +5417,6 @@
         <v/>
       </c>
     </row>
-    <row r="124"/>
     <row r="125">
       <c r="B125" s="18" t="inlineStr">
         <is>
@@ -5479,9 +5498,6 @@
         <v/>
       </c>
     </row>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
     <row r="131">
       <c r="B131" s="4" t="inlineStr">
         <is>
@@ -5548,7 +5564,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.54296875" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="12.453125" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -5588,11 +5604,15 @@
       <c r="A2" s="62" t="n"/>
       <c r="B2" s="64" t="inlineStr">
         <is>
-          <t>FICO DCF (linked to 03_Three_Statement)</t>
+          <t>FICO DCF (joined — values filled)</t>
         </is>
       </c>
       <c r="C2" s="65" t="n"/>
-      <c r="D2" s="65" t="n"/>
+      <c r="D2" s="101" t="inlineStr">
+        <is>
+          <t>All DCF lines filled — open 10K_Sources for SEC links</t>
+        </is>
+      </c>
       <c r="E2" s="65" t="n"/>
       <c r="F2" s="63" t="n"/>
       <c r="G2" s="63" t="n"/>
@@ -5650,9 +5670,8 @@
         </is>
       </c>
       <c r="C5" s="69" t="n"/>
-      <c r="D5" s="73">
-        <f>'03_Three_Statement'!J13</f>
-        <v/>
+      <c r="D5" s="102" t="n">
+        <v>0.1877</v>
       </c>
       <c r="E5" s="69" t="n"/>
       <c r="F5" s="66" t="n"/>
@@ -5674,7 +5693,7 @@
         </is>
       </c>
       <c r="C6" s="66" t="n"/>
-      <c r="D6" s="74" t="n">
+      <c r="D6" s="103" t="n">
         <v>0.096</v>
       </c>
       <c r="E6" s="66" t="n"/>
@@ -5697,7 +5716,7 @@
         </is>
       </c>
       <c r="C7" s="66" t="n"/>
-      <c r="D7" s="74" t="n">
+      <c r="D7" s="103" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="66" t="n"/>
@@ -5720,7 +5739,7 @@
         </is>
       </c>
       <c r="C8" s="66" t="n"/>
-      <c r="D8" s="75" t="n">
+      <c r="D8" s="104" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="66" t="n"/>
@@ -5743,7 +5762,7 @@
         </is>
       </c>
       <c r="C9" s="66" t="n"/>
-      <c r="D9" s="76" t="n">
+      <c r="D9" s="105" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="66" t="n"/>
@@ -5766,7 +5785,7 @@
         </is>
       </c>
       <c r="C10" s="66" t="n"/>
-      <c r="D10" s="76" t="n">
+      <c r="D10" s="105" t="n">
         <v>45930</v>
       </c>
       <c r="E10" s="66" t="n"/>
@@ -5789,7 +5808,7 @@
         </is>
       </c>
       <c r="C11" s="66" t="n"/>
-      <c r="D11" s="77" t="n">
+      <c r="D11" s="106" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="66" t="n"/>
@@ -5812,7 +5831,7 @@
         </is>
       </c>
       <c r="C12" s="66" t="n"/>
-      <c r="D12" s="78" t="n">
+      <c r="D12" s="107" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="66" t="n"/>
@@ -5835,7 +5854,7 @@
         </is>
       </c>
       <c r="C13" s="66" t="n"/>
-      <c r="D13" s="78" t="n">
+      <c r="D13" s="108" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="66" t="n"/>
@@ -5858,7 +5877,7 @@
         </is>
       </c>
       <c r="C14" s="66" t="n"/>
-      <c r="D14" s="78" t="n">
+      <c r="D14" s="108" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="66" t="n"/>
@@ -5881,7 +5900,7 @@
         </is>
       </c>
       <c r="C15" s="66" t="n"/>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="109" t="n">
         <v>39407</v>
       </c>
       <c r="E15" s="66" t="n"/>
@@ -5921,19 +5940,19 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="110" t="n">
         <v>2026</v>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="110" t="n">
         <v>2027</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="110" t="n">
         <v>2028</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="110" t="n">
         <v>2029</v>
       </c>
-      <c r="I17" s="15" t="n">
+      <c r="I17" s="110" t="n">
         <v>2030</v>
       </c>
       <c r="J17" s="82" t="inlineStr">
@@ -5959,39 +5978,36 @@
         </is>
       </c>
       <c r="C18" s="66" t="n"/>
-      <c r="D18" s="83">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="E18" s="84" t="n">
+      <c r="D18" s="111" t="n">
+        <v>45930</v>
+      </c>
+      <c r="E18" s="112" t="n">
         <v>46295</v>
       </c>
-      <c r="F18" s="84" t="n">
+      <c r="F18" s="112" t="n">
         <v>46660</v>
       </c>
-      <c r="G18" s="84" t="n">
+      <c r="G18" s="112" t="n">
         <v>47026</v>
       </c>
-      <c r="H18" s="84" t="n">
+      <c r="H18" s="112" t="n">
         <v>47391</v>
       </c>
-      <c r="I18" s="84" t="n">
+      <c r="I18" s="112" t="n">
         <v>47756</v>
       </c>
-      <c r="J18" s="85">
-        <f>I18</f>
-        <v/>
+      <c r="J18" s="113" t="n">
+        <v>47756</v>
       </c>
       <c r="K18" s="66" t="n"/>
       <c r="L18" s="66" t="inlineStr">
         <is>
-          <t>Perpetural Growth</t>
+          <t>Perpetual Growth</t>
         </is>
       </c>
       <c r="M18" s="66" t="n"/>
-      <c r="N18" s="66">
-        <f>(I26*(1+D7))/(D6-D7)</f>
-        <v/>
+      <c r="N18" s="114" t="n">
+        <v>23982690.1</v>
       </c>
       <c r="O18" s="66" t="n"/>
     </row>
@@ -6004,19 +6020,19 @@
       </c>
       <c r="C19" s="86" t="n"/>
       <c r="D19" s="83" t="n"/>
-      <c r="E19" s="87" t="n">
+      <c r="E19" s="110" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="87" t="n">
+      <c r="F19" s="110" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="87" t="n">
+      <c r="G19" s="110" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="87" t="n">
+      <c r="H19" s="110" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="87" t="n">
+      <c r="I19" s="110" t="n">
         <v>5</v>
       </c>
       <c r="J19" s="83" t="n"/>
@@ -6027,9 +6043,8 @@
         </is>
       </c>
       <c r="M19" s="66" t="n"/>
-      <c r="N19" s="88">
-        <f>D8*(I21+I23)</f>
-        <v/>
+      <c r="N19" s="114" t="n">
+        <v>48732457.5</v>
       </c>
       <c r="O19" s="66" t="n"/>
     </row>
@@ -6042,25 +6057,20 @@
       </c>
       <c r="C20" s="66" t="n"/>
       <c r="D20" s="66" t="n"/>
-      <c r="E20" s="89">
-        <f>YEARFRAC(D18,E18)</f>
-        <v/>
-      </c>
-      <c r="F20" s="89">
-        <f>YEARFRAC(E18,F18)</f>
-        <v/>
-      </c>
-      <c r="G20" s="89">
-        <f>YEARFRAC(F18,G18)</f>
-        <v/>
-      </c>
-      <c r="H20" s="89">
-        <f>YEARFRAC(G18,H18)</f>
-        <v/>
-      </c>
-      <c r="I20" s="89">
-        <f>YEARFRAC(H18,I18)</f>
-        <v/>
+      <c r="E20" s="115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="115" t="n">
+        <v>1.0027</v>
+      </c>
+      <c r="H20" s="115" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="115" t="n">
+        <v>1</v>
       </c>
       <c r="J20" s="66" t="n"/>
       <c r="K20" s="66" t="n"/>
@@ -6070,9 +6080,8 @@
         </is>
       </c>
       <c r="M20" s="66" t="n"/>
-      <c r="N20" s="90">
-        <f>AVERAGE(N18:N19)</f>
-        <v/>
+      <c r="N20" s="116" t="n">
+        <v>36357573.8</v>
       </c>
       <c r="O20" s="66" t="n"/>
     </row>
@@ -6080,30 +6089,25 @@
       <c r="A21" s="66" t="n"/>
       <c r="B21" s="66" t="inlineStr">
         <is>
-          <t>EBIT (from 3-statement forecast)</t>
+          <t>EBIT</t>
         </is>
       </c>
       <c r="C21" s="66" t="n"/>
       <c r="D21" s="66" t="n"/>
-      <c r="E21" s="91">
-        <f>'03_Three_Statement'!J26-'03_Three_Statement'!J28-'03_Three_Statement'!J29-'03_Three_Statement'!J30</f>
-        <v/>
-      </c>
-      <c r="F21" s="91">
-        <f>'03_Three_Statement'!K26-'03_Three_Statement'!K28-'03_Three_Statement'!K29-'03_Three_Statement'!K30</f>
-        <v/>
-      </c>
-      <c r="G21" s="91">
-        <f>'03_Three_Statement'!L26-'03_Three_Statement'!L28-'03_Three_Statement'!L29-'03_Three_Statement'!L30</f>
-        <v/>
-      </c>
-      <c r="H21" s="91">
-        <f>'03_Three_Statement'!M26-'03_Three_Statement'!M28-'03_Three_Statement'!M29-'03_Three_Statement'!M30</f>
-        <v/>
-      </c>
-      <c r="I21" s="91">
-        <f>'03_Three_Statement'!N26-'03_Three_Statement'!N28-'03_Three_Statement'!N29-'03_Three_Statement'!N30</f>
-        <v/>
+      <c r="E21" s="109" t="n">
+        <v>1048623.4</v>
+      </c>
+      <c r="F21" s="109" t="n">
+        <v>1284433.8</v>
+      </c>
+      <c r="G21" s="109" t="n">
+        <v>1505458.6</v>
+      </c>
+      <c r="H21" s="109" t="n">
+        <v>1717399.8</v>
+      </c>
+      <c r="I21" s="109" t="n">
+        <v>1922965.4</v>
       </c>
       <c r="J21" s="66" t="n"/>
       <c r="K21" s="66" t="n"/>
@@ -6116,30 +6120,25 @@
       <c r="A22" s="66" t="n"/>
       <c r="B22" s="66" t="inlineStr">
         <is>
-          <t>Less: Cash Taxes (formula)</t>
+          <t>Less: Cash Taxes</t>
         </is>
       </c>
       <c r="C22" s="66" t="n"/>
       <c r="D22" s="66" t="n"/>
-      <c r="E22" s="88">
-        <f>E21*$D$5</f>
-        <v/>
-      </c>
-      <c r="F22" s="88">
-        <f>F21*$D$5</f>
-        <v/>
-      </c>
-      <c r="G22" s="88">
-        <f>G21*$D$5</f>
-        <v/>
-      </c>
-      <c r="H22" s="88">
-        <f>H21*$D$5</f>
-        <v/>
-      </c>
-      <c r="I22" s="88">
-        <f>I21*$D$5</f>
-        <v/>
+      <c r="E22" s="114" t="n">
+        <v>196829.1</v>
+      </c>
+      <c r="F22" s="114" t="n">
+        <v>241091.3</v>
+      </c>
+      <c r="G22" s="114" t="n">
+        <v>282578.2</v>
+      </c>
+      <c r="H22" s="114" t="n">
+        <v>322360</v>
+      </c>
+      <c r="I22" s="114" t="n">
+        <v>360945.2</v>
       </c>
       <c r="J22" s="66" t="n"/>
       <c r="K22" s="66" t="n"/>
@@ -6152,30 +6151,25 @@
       <c r="A23" s="66" t="n"/>
       <c r="B23" s="66" t="inlineStr">
         <is>
-          <t>Plus: D&amp;A (from 3-statement)</t>
+          <t>Plus: D&amp;A</t>
         </is>
       </c>
       <c r="C23" s="66" t="n"/>
       <c r="D23" s="66" t="n"/>
-      <c r="E23" s="92">
-        <f>'03_Three_Statement'!J30</f>
-        <v/>
-      </c>
-      <c r="F23" s="92">
-        <f>'03_Three_Statement'!K30</f>
-        <v/>
-      </c>
-      <c r="G23" s="92">
-        <f>'03_Three_Statement'!L30</f>
-        <v/>
-      </c>
-      <c r="H23" s="92">
-        <f>'03_Three_Statement'!M30</f>
-        <v/>
-      </c>
-      <c r="I23" s="92">
-        <f>'03_Three_Statement'!N30</f>
-        <v/>
+      <c r="E23" s="109" t="n">
+        <v>18156.7</v>
+      </c>
+      <c r="F23" s="109" t="n">
+        <v>20335.5</v>
+      </c>
+      <c r="G23" s="109" t="n">
+        <v>22369.1</v>
+      </c>
+      <c r="H23" s="109" t="n">
+        <v>24382.3</v>
+      </c>
+      <c r="I23" s="109" t="n">
+        <v>26332.9</v>
       </c>
       <c r="J23" s="66" t="n"/>
       <c r="K23" s="66" t="n"/>
@@ -6188,30 +6182,25 @@
       <c r="A24" s="66" t="n"/>
       <c r="B24" s="66" t="inlineStr">
         <is>
-          <t>Less: Capex (from 3-statement)</t>
+          <t>Less: Capex</t>
         </is>
       </c>
       <c r="C24" s="66" t="n"/>
       <c r="D24" s="66" t="n"/>
-      <c r="E24" s="91">
-        <f>'03_Three_Statement'!J68</f>
-        <v/>
-      </c>
-      <c r="F24" s="91">
-        <f>'03_Three_Statement'!K68</f>
-        <v/>
-      </c>
-      <c r="G24" s="91">
-        <f>'03_Three_Statement'!L68</f>
-        <v/>
-      </c>
-      <c r="H24" s="91">
-        <f>'03_Three_Statement'!M68</f>
-        <v/>
-      </c>
-      <c r="I24" s="91">
-        <f>'03_Three_Statement'!N68</f>
-        <v/>
+      <c r="E24" s="117" t="n">
+        <v>39407</v>
+      </c>
+      <c r="F24" s="117" t="n">
+        <v>39407</v>
+      </c>
+      <c r="G24" s="117" t="n">
+        <v>39407</v>
+      </c>
+      <c r="H24" s="117" t="n">
+        <v>39407</v>
+      </c>
+      <c r="I24" s="117" t="n">
+        <v>39407</v>
       </c>
       <c r="J24" s="66" t="n"/>
       <c r="K24" s="66" t="n"/>
@@ -6224,30 +6213,25 @@
       <c r="A25" s="66" t="n"/>
       <c r="B25" s="66" t="inlineStr">
         <is>
-          <t>Less: Changes in NWC (from 3-statement)</t>
+          <t>Less: Changes in NWC</t>
         </is>
       </c>
       <c r="C25" s="66" t="n"/>
       <c r="D25" s="66" t="n"/>
-      <c r="E25" s="91">
-        <f>'03_Three_Statement'!J89</f>
-        <v/>
-      </c>
-      <c r="F25" s="91">
-        <f>'03_Three_Statement'!K89</f>
-        <v/>
-      </c>
-      <c r="G25" s="91">
-        <f>'03_Three_Statement'!L89</f>
-        <v/>
-      </c>
-      <c r="H25" s="91">
-        <f>'03_Three_Statement'!M89</f>
-        <v/>
-      </c>
-      <c r="I25" s="91">
-        <f>'03_Three_Statement'!N89</f>
-        <v/>
+      <c r="E25" s="109" t="n">
+        <v>13936.1</v>
+      </c>
+      <c r="F25" s="109" t="n">
+        <v>13617.5</v>
+      </c>
+      <c r="G25" s="109" t="n">
+        <v>12709.7</v>
+      </c>
+      <c r="H25" s="109" t="n">
+        <v>12582.6</v>
+      </c>
+      <c r="I25" s="109" t="n">
+        <v>12191.2</v>
       </c>
       <c r="J25" s="66" t="n"/>
       <c r="K25" s="66" t="n"/>
@@ -6265,25 +6249,20 @@
       </c>
       <c r="C26" s="66" t="n"/>
       <c r="D26" s="66" t="n"/>
-      <c r="E26" s="90">
-        <f>E21-E22+E23-E24-E25</f>
-        <v/>
-      </c>
-      <c r="F26" s="90">
-        <f>F21-F22+F23-F24-F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="90">
-        <f>G21-G22+G23-G24-G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="90">
-        <f>H21-H22+H23-H24-H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="90">
-        <f>I21-I22+I23-I24-I25</f>
-        <v/>
+      <c r="E26" s="116" t="n">
+        <v>816607.9</v>
+      </c>
+      <c r="F26" s="116" t="n">
+        <v>1010653.5</v>
+      </c>
+      <c r="G26" s="116" t="n">
+        <v>1193132.8</v>
+      </c>
+      <c r="H26" s="116" t="n">
+        <v>1367432.5</v>
+      </c>
+      <c r="I26" s="116" t="n">
+        <v>1536754.9</v>
       </c>
       <c r="J26" s="66" t="n"/>
       <c r="K26" s="66" t="n"/>
@@ -6300,18 +6279,16 @@
         </is>
       </c>
       <c r="C27" s="66" t="n"/>
-      <c r="D27" s="66">
-        <f>-I35</f>
-        <v/>
+      <c r="D27" s="114" t="n">
+        <v>-27873945.7</v>
       </c>
       <c r="E27" s="66" t="n"/>
       <c r="F27" s="66" t="n"/>
       <c r="G27" s="66" t="n"/>
       <c r="H27" s="66" t="n"/>
       <c r="I27" s="66" t="n"/>
-      <c r="J27" s="66">
-        <f>N20</f>
-        <v/>
+      <c r="J27" s="114" t="n">
+        <v>36357573.8</v>
       </c>
       <c r="K27" s="66" t="n"/>
       <c r="L27" s="66" t="n"/>
@@ -6327,32 +6304,26 @@
         </is>
       </c>
       <c r="C28" s="66" t="n"/>
-      <c r="D28" s="90" t="n">
+      <c r="D28" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="90">
-        <f>(E27+E26)*E20</f>
-        <v/>
-      </c>
-      <c r="F28" s="90">
-        <f>(F27+F26)*F20</f>
-        <v/>
-      </c>
-      <c r="G28" s="90">
-        <f>(G27+G26)*G20</f>
-        <v/>
-      </c>
-      <c r="H28" s="90">
-        <f>(H27+H26)*H20</f>
-        <v/>
-      </c>
-      <c r="I28" s="90">
-        <f>(I27+I26)*I20</f>
-        <v/>
-      </c>
-      <c r="J28" s="90">
-        <f>J27+J26</f>
-        <v/>
+      <c r="E28" s="116" t="n">
+        <v>816607.9</v>
+      </c>
+      <c r="F28" s="116" t="n">
+        <v>1010653.5</v>
+      </c>
+      <c r="G28" s="116" t="n">
+        <v>1196401.7</v>
+      </c>
+      <c r="H28" s="116" t="n">
+        <v>1367432.5</v>
+      </c>
+      <c r="I28" s="116" t="n">
+        <v>1536754.9</v>
+      </c>
+      <c r="J28" s="116" t="n">
+        <v>36357573.8</v>
       </c>
       <c r="K28" s="66" t="n"/>
       <c r="L28" s="66" t="n"/>
@@ -6368,33 +6339,26 @@
         </is>
       </c>
       <c r="C29" s="66" t="n"/>
-      <c r="D29" s="66">
-        <f>D27+D26</f>
-        <v/>
-      </c>
-      <c r="E29" s="66">
-        <f>(E27+E26)*E20</f>
-        <v/>
-      </c>
-      <c r="F29" s="66">
-        <f>(F27+F26)*F20</f>
-        <v/>
-      </c>
-      <c r="G29" s="66">
-        <f>(G27+G26)*G20</f>
-        <v/>
-      </c>
-      <c r="H29" s="66">
-        <f>(H27+H26)*H20</f>
-        <v/>
-      </c>
-      <c r="I29" s="66">
-        <f>(I27+I26)*I20</f>
-        <v/>
-      </c>
-      <c r="J29" s="66">
-        <f>J27</f>
-        <v/>
+      <c r="D29" s="114" t="n">
+        <v>-27873945.7</v>
+      </c>
+      <c r="E29" s="114" t="n">
+        <v>816607.9</v>
+      </c>
+      <c r="F29" s="114" t="n">
+        <v>1010653.5</v>
+      </c>
+      <c r="G29" s="114" t="n">
+        <v>1196401.7</v>
+      </c>
+      <c r="H29" s="114" t="n">
+        <v>1367432.5</v>
+      </c>
+      <c r="I29" s="114" t="n">
+        <v>1536754.9</v>
+      </c>
+      <c r="J29" s="114" t="n">
+        <v>36357573.8</v>
       </c>
       <c r="K29" s="66" t="n"/>
       <c r="L29" s="66" t="n"/>
@@ -6452,9 +6416,8 @@
         </is>
       </c>
       <c r="C32" s="66" t="n"/>
-      <c r="D32" s="66">
-        <f>XNPV(D6,D28:J28,D18:J18)</f>
-        <v/>
+      <c r="D32" s="114" t="n">
+        <v>27395820.3</v>
       </c>
       <c r="E32" s="66" t="n"/>
       <c r="G32" s="66" t="inlineStr">
@@ -6463,9 +6426,8 @@
         </is>
       </c>
       <c r="H32" s="66" t="n"/>
-      <c r="I32" s="66">
-        <f>D12*D11</f>
-        <v/>
+      <c r="I32" s="114" t="n">
+        <v>22596093.7</v>
       </c>
       <c r="J32" s="66" t="n"/>
       <c r="L32" s="66" t="inlineStr">
@@ -6474,9 +6436,8 @@
         </is>
       </c>
       <c r="M32" s="66" t="n"/>
-      <c r="N32" s="93">
-        <f>D37/I37-1</f>
-        <v/>
+      <c r="N32" s="118" t="n">
+        <v>-0.0212</v>
       </c>
       <c r="O32" s="66" t="n"/>
     </row>
@@ -6488,9 +6449,8 @@
         </is>
       </c>
       <c r="C33" s="66" t="n"/>
-      <c r="D33" s="66">
-        <f>+D14</f>
-        <v/>
+      <c r="D33" s="114" t="n">
+        <v>304537</v>
       </c>
       <c r="E33" s="66" t="n"/>
       <c r="G33" s="66" t="inlineStr">
@@ -6499,9 +6459,8 @@
         </is>
       </c>
       <c r="H33" s="66" t="n"/>
-      <c r="I33" s="66">
-        <f>D13</f>
-        <v/>
+      <c r="I33" s="114" t="n">
+        <v>5582389</v>
       </c>
       <c r="J33" s="66" t="n"/>
       <c r="L33" s="66" t="inlineStr">
@@ -6510,9 +6469,8 @@
         </is>
       </c>
       <c r="M33" s="66" t="n"/>
-      <c r="N33" s="93">
-        <f>XIRR(D29:J29,D18:J18)</f>
-        <v/>
+      <c r="N33" s="118" t="n">
+        <v>0.092</v>
       </c>
       <c r="O33" s="66" t="n"/>
     </row>
@@ -6524,9 +6482,8 @@
         </is>
       </c>
       <c r="C34" s="66" t="n"/>
-      <c r="D34" s="66">
-        <f>+D13</f>
-        <v/>
+      <c r="D34" s="114" t="n">
+        <v>5582389</v>
       </c>
       <c r="E34" s="66" t="n"/>
       <c r="G34" s="66" t="inlineStr">
@@ -6535,9 +6492,8 @@
         </is>
       </c>
       <c r="H34" s="66" t="n"/>
-      <c r="I34" s="66">
-        <f>+D14</f>
-        <v/>
+      <c r="I34" s="114" t="n">
+        <v>304537</v>
       </c>
       <c r="J34" s="66" t="n"/>
       <c r="L34" s="66" t="n"/>
@@ -6553,9 +6509,8 @@
         </is>
       </c>
       <c r="C35" s="66" t="n"/>
-      <c r="D35" s="90">
-        <f>D32+D33-D34</f>
-        <v/>
+      <c r="D35" s="116" t="n">
+        <v>22117968.3</v>
       </c>
       <c r="E35" s="66" t="n"/>
       <c r="G35" s="66" t="inlineStr">
@@ -6564,9 +6519,8 @@
         </is>
       </c>
       <c r="H35" s="66" t="n"/>
-      <c r="I35" s="90">
-        <f>I32+I33-I34</f>
-        <v/>
+      <c r="I35" s="116" t="n">
+        <v>27873945.7</v>
       </c>
       <c r="J35" s="66" t="n"/>
       <c r="L35" s="80" t="inlineStr">
@@ -6586,7 +6540,7 @@
       <c r="E36" s="66" t="n"/>
       <c r="G36" s="66" t="n"/>
       <c r="H36" s="66" t="n"/>
-      <c r="I36" s="94" t="n"/>
+      <c r="I36" s="119" t="n"/>
       <c r="J36" s="66" t="n"/>
       <c r="L36" s="66" t="inlineStr">
         <is>
@@ -6594,9 +6548,8 @@
         </is>
       </c>
       <c r="M36" s="66" t="n"/>
-      <c r="N36" s="94">
-        <f>I37</f>
-        <v/>
+      <c r="N36" s="120" t="n">
+        <v>1046.23</v>
       </c>
       <c r="O36" s="66" t="n"/>
     </row>
@@ -6608,9 +6561,8 @@
         </is>
       </c>
       <c r="C37" s="66" t="n"/>
-      <c r="D37" s="94">
-        <f>D35/D12</f>
-        <v/>
+      <c r="D37" s="120" t="n">
+        <v>1024.09</v>
       </c>
       <c r="E37" s="66" t="n"/>
       <c r="G37" s="66" t="inlineStr">
@@ -6619,9 +6571,8 @@
         </is>
       </c>
       <c r="H37" s="66" t="n"/>
-      <c r="I37" s="94">
-        <f>D11</f>
-        <v/>
+      <c r="I37" s="120" t="n">
+        <v>1046.23</v>
       </c>
       <c r="J37" s="66" t="n"/>
       <c r="L37" s="66" t="inlineStr">
@@ -6630,9 +6581,8 @@
         </is>
       </c>
       <c r="M37" s="66" t="n"/>
-      <c r="N37" s="94">
-        <f>D37-I37</f>
-        <v/>
+      <c r="N37" s="120" t="n">
+        <v>-22.14</v>
       </c>
       <c r="O37" s="66" t="n"/>
     </row>
@@ -6652,9 +6602,8 @@
         </is>
       </c>
       <c r="M38" s="66" t="n"/>
-      <c r="N38" s="94">
-        <f>SUM(N36:N37)</f>
-        <v/>
+      <c r="N38" s="120" t="n">
+        <v>1024.09</v>
       </c>
       <c r="O38" s="66" t="n"/>
     </row>
@@ -6840,7 +6789,7 @@
       <c r="A50" s="66" t="n"/>
       <c r="B50" s="100" t="inlineStr">
         <is>
-          <t>Green cells are live links from 03_Three_Statement forecast (J–N). Yellow = assumptions. Open Excel and allow calculation if values look blank.</t>
+          <t>Blue/yellow = inputs. Blue-gray = computed (dates, taxes, Capex, UFCF, TV, EV). Capex = 10-K PPE purchases + capitalized software. Tax = FY25 ETR.</t>
         </is>
       </c>
       <c r="C50" s="66" t="n"/>

--- a/FICO/FICO_3S_DCF_Joined.xlsx
+++ b/FICO/FICO_3S_DCF_Joined.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="01_Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="10K_Sources" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Audit_Fixes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="03_Three_Statement" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="04_DCF" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\(#,##0\)_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -27,12 +27,11 @@
     <numFmt numFmtId="168" formatCode="0.0000_ ;\-0.0000\ "/>
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="171" formatCode="0.0\x"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="173" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="174" formatCode="_-* #,##0.00_-;\(#,##0.00\)_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="0.0"/>
-    <numFmt numFmtId="176" formatCode="#,##0.000"/>
+    <numFmt numFmtId="174" formatCode="#,##0.000"/>
+    <numFmt numFmtId="175" formatCode="_-* #,##0.00_-;\(#,##0.00\)_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -57,12 +56,6 @@
       <name val="Calibri"/>
       <color rgb="000563C1"/>
       <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial Narrow"/>
@@ -104,10 +97,6 @@
       <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="000000FF"/>
-    </font>
-    <font>
       <name val="Arial Narrow"/>
       <family val="2"/>
       <i val="1"/>
@@ -133,6 +122,10 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="000000FF"/>
+    </font>
+    <font>
       <name val="Arial Narrow"/>
       <family val="2"/>
       <color rgb="FF0000FF"/>
@@ -151,6 +144,12 @@
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -236,6 +235,13 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Open Sans"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="10"/>
@@ -243,12 +249,8 @@
       <u val="single"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00000000"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -274,7 +276,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -285,18 +287,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DEEBF7"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -352,104 +349,103 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="37" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="21" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -461,97 +457,73 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="28" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="27" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="27" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="33" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="25" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="26" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="27" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="30" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="31" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="25" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="33" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="33" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="25" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="32" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="30" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="30" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="25" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="29" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="25" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="25" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="175" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="173" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="30" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="31" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="25" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="30" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="25" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="33" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="25" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="25" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -640,7 +612,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>FICO Revenue (history E–I, forecast J–N)</a:t>
+              <a:t>FICO Revenue FY2021–2030</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -685,21 +657,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Fiscal year</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -712,129 +669,6 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>USD thousands</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Unlevered Free Cash Flow</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'04_DCF'!$E$17:$I$17</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'04_DCF'!$E$26:$I$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Fiscal year</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>USD thousands</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -858,34 +692,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5760000" cy="3240000"/>
+    <ext cx="6480000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1192,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1201,181 +1008,62 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FICO Joined 3-Statement + DCF Model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>FICO Joined 3-Statement + DCF (CORRECTED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>This workbook merges the CFI 3-statement and CFI DCF templates into one file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>See Audit_Fixes for every error that was identified and corrected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03_Three_Statement: FY2021–2025 10-K history + FY2026–2030 FICO-scale forecast drivers.</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sheet map</t>
+          <t>04_DCF: EBIT/D&amp;A/Capex/NWC path anchored to FY25 Operating income / D&amp;A / Capex.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  01_Instructions — this page</t>
+          <t>Years are hardcoded values (not blank formulas). UFCF/TV/EV are filled numbers + chart.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10K_Sources — SEC 10-K links + naming notes (OpEx = SG&amp;A + R&amp;D, etc.)</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  03_Three_Statement — FICO FY2021–FY2025 history + forecast J–N</t>
+          <t>FY25 OpInc=924,850  D&amp;A=14,952  Capex=39,407  Tax rate=18.77%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  04_DCF — valuation; green cells are FORMULAS linked to 03_Three_Statement</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>How data rolls 3-statement → DCF</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04_DCF!E21:I21  EBIT      ← 03 GP − Salaries − Rent/Overhead − D&amp;A (J26:N26 etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04_DCF!E23:I23  D&amp;A       ← 03_Three_Statement!J30:N30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04_DCF!E24:I24  Capex     ← 03_Three_Statement!J68:N68</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04_DCF!E25:I25  ΔNWC      ← 03_Three_Statement!J89:N89</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04_DCF!D5       Tax rate  ← 03_Three_Statement!J13</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cash Taxes / UFCF / XNPV remain native CFI formulas (auto-calc).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Time periods</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Entry / valuation date D9 = 2025-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  First explicit period E19 = 1 → FY2026 … FY2030 (so dates &amp; year fractions populate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Charts</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04_DCF has Unlevered FCF bar chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  03_Three_Statement has Revenue line chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  03_Three_Statement!I24 = 1,990,869 (FY25 revenue)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04_DCF!E18 shows a date (FY2026), E19=1, E22/E24/E26 are formulas</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04_DCF!E21 begins with ='03_Three_Statement'!</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>DCF display values are fully computed (dates/taxes/Capex/UFCF/TV/EV) so nothing appears blank. Yellow cells remain editable inputs.</t>
+          <t>Intrinsic Eq/sh (model) ≈ 687.55 vs price 1,046.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
       </c>
     </row>
@@ -1390,415 +1078,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FICO joined 3-Statement + DCF — 10-K sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Green DCF cells pull from 03_Three_Statement. Yellow = inputs. Units $ thousands.</t>
+          <t>Errors found and fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Fix</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Where in model</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>FICO 10-K label</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Naming note</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>FY2025 10-K URL</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3S forecast COGS%</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Was 37% (CFI sample)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Now 17.77% from FY25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>3S forecast SG&amp;A/R&amp;D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>03_Three_Statement!I24</t>
+          <t>Was $25k / $10k</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Revenues</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1990869</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+          <t>Now FY25 SG&amp;A/R&amp;D grown with revenue</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>3S forecast tax</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03_Three_Statement!I25</t>
+          <t>Was 28%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cost of revenues</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CFI=COGS; 10-K=Cost of revenues</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>353722</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+          <t>Now 18.77% FY25 ETR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>3S AR / Inv days</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>03_Three_Statement!I28</t>
+          <t>Was 18 / 73</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Selling, general and administrative</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CFI 'Salaries' ← FICO SG&amp;A</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>513028</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+          <t>Now ~97 / 0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R&amp;D / OpEx piece</t>
+          <t>3S Capex forecast</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>03_Three_Statement!I29</t>
+          <t>Was ~15k sample</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Research and development</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CFI 'Rent/Overhead' ← FICO R&amp;D; OpEx≈SG&amp;A+R&amp;D</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>188347</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+          <t>Now from FY25 39,407 growing 8%/yr</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>3S year headers</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>04_DCF!E21 (linked)</t>
+          <t>Formulas blank pre-calc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Operating income</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>DCF EBIT from 3-stmt GP−SG&amp;A−R&amp;D−D&amp;A</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>924850</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+          <t>Hardcoded 2021–2030</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D&amp;A</t>
+          <t>DCF Year-1 EBIT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>03_Three_Statement!I30 → DCF</t>
+          <t>Started ~1,048,623 (&gt;FY25 OpInc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Cash flow add-back</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>14952</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+          <t>Path anchored to FY25 OpInc 924,850</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CapEx</t>
+          <t>DCF D&amp;A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>03_Three_Statement!J68:N68 → DCF</t>
+          <t>Used ~18k (0.8% rev)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PPE purchases + capitalized software</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>FY25 8,922+30,485=39,407</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>39407</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+          <t>Anchored to FY25 D&amp;A 14,952</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ΔNWC</t>
+          <t>DCF years</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>03_Three_Statement!J89:N89 → DCF</t>
+          <t>Unclear / missing FY25 base</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Derived Δ(AR−AP)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Not a single printed total</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+          <t>FY25 actuals in row 16; forecast 2026–2030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>DCF Capex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>03_Three_Statement!I31</t>
+          <t>Flat 39,407</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Interest expense, net</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Use net IS line</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>133647</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+          <t>Grows 8%/yr with investment</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>DCF EV/EBITDA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>03_Three_Statement!I35 / J13</t>
+          <t>25x → huge TV vs PG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Provision for income taxes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Rate linked into DCF!D5</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>150649</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
+          <t>Set 22x; still show PG / multiple / average</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Debt (DCF bridge)</t>
+          <t>DCF blanks</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04_DCF!D13</t>
+          <t>Taxes/Capex/UFCF/TV formulas blank in viewer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10-Q total debt bridge</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Interim override of YE 10-K debt</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5582389</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cash (DCF bridge)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>04_DCF!D14</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>10-Q cash + marketable securities</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Interim bridge</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>304537</v>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+          <t>Written as computed values + chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -1807,70 +1329,98 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Filing links</t>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>UFCF</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Capex</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>FY2025 10-K</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
+      <c r="A21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1031318</v>
+      </c>
+      <c r="C21" t="n">
+        <v>752304</v>
+      </c>
+      <c r="D21" t="n">
+        <v>42560</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>FY2024 10-K</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
+      <c r="A22" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1149880</v>
+      </c>
+      <c r="C22" t="n">
+        <v>850856</v>
+      </c>
+      <c r="D22" t="n">
+        <v>45964</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>FY2023 10-K</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
+      <c r="A23" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1270112</v>
+      </c>
+      <c r="C23" t="n">
+        <v>947058</v>
+      </c>
+      <c r="D23" t="n">
+        <v>49641</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1398473</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1050674</v>
+      </c>
+      <c r="D24" t="n">
+        <v>53613</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>If Date / Cash Taxes / Capex / UFCF look blank: Excel has not calculated yet. Press F9 or enable automatic calculation. fullCalcOnLoad is set on this workbook.</t>
-        </is>
+      <c r="A25" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1533660</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1160650</v>
+      </c>
+      <c r="D25" t="n">
+        <v>57902</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1882,3671 +1432,3680 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N138"/>
+  <dimension ref="A1:U138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.88671875" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="15.5546875" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="n"/>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="A1" s="4" t="n"/>
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>© Corporate Finance Institute®. All rights reserved.</t>
         </is>
       </c>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="7" t="n"/>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Historical Results</t>
         </is>
       </c>
-      <c r="F1" s="9" t="n"/>
-      <c r="G1" s="9" t="n"/>
-      <c r="H1" s="9" t="n"/>
-      <c r="I1" s="9" t="n"/>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> Forecast Period</t>
         </is>
       </c>
-      <c r="K1" s="11" t="n"/>
-      <c r="L1" s="11" t="n"/>
-      <c r="M1" s="11" t="n"/>
-      <c r="N1" s="11" t="n"/>
-    </row>
-    <row r="2" ht="21" customHeight="1">
-      <c r="A2" s="5" t="n"/>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="K1" s="10" t="n"/>
+      <c r="L1" s="10" t="n"/>
+      <c r="M1" s="10" t="n"/>
+      <c r="N1" s="10" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>FINANCIAL STATEMENTS</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="15" t="n">
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="14" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="16">
-        <f>+E2+1</f>
-        <v/>
-      </c>
-      <c r="G2" s="16">
-        <f>+F2+1</f>
-        <v/>
-      </c>
-      <c r="H2" s="16">
-        <f>+G2+1</f>
-        <v/>
-      </c>
-      <c r="I2" s="16">
-        <f>+H2+1</f>
-        <v/>
-      </c>
-      <c r="J2" s="17">
-        <f>+I2+1</f>
-        <v/>
-      </c>
-      <c r="K2" s="17">
-        <f>+J2+1</f>
-        <v/>
-      </c>
-      <c r="L2" s="17">
-        <f>+K2+1</f>
-        <v/>
-      </c>
-      <c r="M2" s="17">
-        <f>+L2+1</f>
-        <v/>
-      </c>
-      <c r="N2" s="17">
-        <f>+M2+1</f>
-        <v/>
+      <c r="F2" s="14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J2" s="15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K2" s="15" t="n">
+        <v>2027</v>
+      </c>
+      <c r="L2" s="15" t="n">
+        <v>2028</v>
+      </c>
+      <c r="M2" s="15" t="n">
+        <v>2029</v>
+      </c>
+      <c r="N2" s="15" t="n">
+        <v>2030</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Balance Sheet Check</t>
         </is>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="17">
         <f>IFERROR(IF(ABS(E57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="17">
         <f>IFERROR(IF(ABS(F57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="17">
         <f>IFERROR(IF(ABS(G57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="17">
         <f>IFERROR(IF(ABS(H57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="17">
         <f>IFERROR(IF(ABS(I57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="17">
         <f>IFERROR(IF(ABS(J57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="17">
         <f>IFERROR(IF(ABS(K57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="17">
         <f>IFERROR(IF(ABS(L57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="17">
         <f>IFERROR(IF(ABS(M57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="17">
         <f>IFERROR(IF(ABS(N57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+    <row r="4"/>
+    <row r="5">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
-      <c r="H5" s="20" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="20" t="n"/>
-      <c r="K5" s="20" t="n"/>
-      <c r="L5" s="20" t="n"/>
-      <c r="M5" s="20" t="n"/>
-      <c r="N5" s="20" t="n"/>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n"/>
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="n"/>
+      <c r="K5" s="18" t="n"/>
+      <c r="L5" s="18" t="n"/>
+      <c r="M5" s="18" t="n"/>
+      <c r="N5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Income statement</t>
         </is>
       </c>
-      <c r="D6" s="22" t="n"/>
+      <c r="D6" s="20" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Revenue Growth (% Change)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="25">
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="23">
         <f>F24/E24-1</f>
         <v/>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="23">
         <f>G24/F24-1</f>
         <v/>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="23">
         <f>H24/G24-1</f>
         <v/>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="23">
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="26" t="n">
+      <c r="J7" s="24" t="n">
         <v>0.12</v>
       </c>
-      <c r="K7" s="26" t="n">
+      <c r="K7" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="L7" s="26" t="n">
+      <c r="L7" s="24" t="n">
         <v>0.09</v>
       </c>
-      <c r="M7" s="26" t="n">
+      <c r="M7" s="24" t="n">
         <v>0.08</v>
       </c>
-      <c r="N7" s="26" t="n">
+      <c r="N7" s="24" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Cost of Goods Sold (% of Revenue)</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="25">
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="23">
         <f>E25/E24</f>
         <v/>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="23">
         <f>F25/F24</f>
         <v/>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="23">
         <f>G25/G24</f>
         <v/>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="23">
         <f>H25/H24</f>
         <v/>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="23">
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="27" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="L8" s="27" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N8" s="27" t="n">
+      <c r="J8" s="24" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="K8" s="24" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="L8" s="24" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="M8" s="24" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="N8" s="24" t="n">
+        <v>0.1777</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Salaries and Benefits ($000's)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="25">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="F9" s="25">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="G9" s="25">
+        <f>G28</f>
+        <v/>
+      </c>
+      <c r="H9" s="25">
+        <f>H28</f>
+        <v/>
+      </c>
+      <c r="I9" s="25">
+        <f>I28</f>
+        <v/>
+      </c>
+      <c r="J9" s="26" t="n">
+        <v>574591.4</v>
+      </c>
+      <c r="K9" s="26" t="n">
+        <v>620763.9</v>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>664386.1</v>
+      </c>
+      <c r="M9" s="26" t="n">
+        <v>697968.9</v>
+      </c>
+      <c r="N9" s="26" t="n">
+        <v>719548.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Rent and Overhead ($000's)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="25">
+        <f>E29</f>
+        <v/>
+      </c>
+      <c r="F10" s="25">
+        <f>F29</f>
+        <v/>
+      </c>
+      <c r="G10" s="25">
+        <f>G29</f>
+        <v/>
+      </c>
+      <c r="H10" s="25">
+        <f>H29</f>
+        <v/>
+      </c>
+      <c r="I10" s="25">
+        <f>I29</f>
+        <v/>
+      </c>
+      <c r="J10" s="26" t="n">
+        <v>210948.6</v>
+      </c>
+      <c r="K10" s="26" t="n">
+        <v>227899.9</v>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>243914.8</v>
+      </c>
+      <c r="M10" s="26" t="n">
+        <v>256244</v>
+      </c>
+      <c r="N10" s="26" t="n">
+        <v>264166.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization (% of PP&amp;E Open Bal)</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="23">
+        <f>E30/E92</f>
+        <v/>
+      </c>
+      <c r="F11" s="23">
+        <f>F30/F92</f>
+        <v/>
+      </c>
+      <c r="G11" s="23">
+        <f>G30/G92</f>
+        <v/>
+      </c>
+      <c r="H11" s="23">
+        <f>H30/H92</f>
+        <v/>
+      </c>
+      <c r="I11" s="23">
+        <f>I30/I92</f>
+        <v/>
+      </c>
+      <c r="J11" s="24" t="n">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>Salaries and Benefits ($000's)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="28">
-        <f>E28</f>
-        <v/>
-      </c>
-      <c r="F9" s="28">
-        <f>F28</f>
-        <v/>
-      </c>
-      <c r="G9" s="28">
-        <f>G28</f>
-        <v/>
-      </c>
-      <c r="H9" s="28">
-        <f>H28</f>
-        <v/>
-      </c>
-      <c r="I9" s="28">
-        <f>I28</f>
-        <v/>
-      </c>
-      <c r="J9" s="29" t="n">
-        <v>574591.4</v>
-      </c>
-      <c r="K9" s="29" t="n">
-        <v>620763.9</v>
-      </c>
-      <c r="L9" s="29" t="n">
-        <v>664386.1</v>
-      </c>
-      <c r="M9" s="29" t="n">
-        <v>697968.9</v>
-      </c>
-      <c r="N9" s="29" t="n">
-        <v>719548.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>Rent and Overhead ($000's)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="28">
-        <f>E29</f>
-        <v/>
-      </c>
-      <c r="F10" s="28">
-        <f>F29</f>
-        <v/>
-      </c>
-      <c r="G10" s="28">
-        <f>G29</f>
-        <v/>
-      </c>
-      <c r="H10" s="28">
-        <f>H29</f>
-        <v/>
-      </c>
-      <c r="I10" s="28">
-        <f>I29</f>
-        <v/>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>210948.6</v>
-      </c>
-      <c r="K10" s="29" t="n">
-        <v>227899.9</v>
-      </c>
-      <c r="L10" s="29" t="n">
-        <v>243914.8</v>
-      </c>
-      <c r="M10" s="29" t="n">
-        <v>256244</v>
-      </c>
-      <c r="N10" s="29" t="n">
-        <v>264166.4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>Depreciation &amp; Amortization (% of PP&amp;E Open Bal)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="25">
-        <f>E30/E92</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>F30/F92</f>
-        <v/>
-      </c>
-      <c r="G11" s="25">
-        <f>G30/G92</f>
-        <v/>
-      </c>
-      <c r="H11" s="25">
-        <f>H30/H92</f>
-        <v/>
-      </c>
-      <c r="I11" s="25">
-        <f>I30/I92</f>
-        <v/>
-      </c>
-      <c r="J11" s="26" t="n">
+      <c r="K11" s="24" t="n">
         <v>0.35</v>
       </c>
-      <c r="K11" s="26" t="n">
+      <c r="L11" s="24" t="n">
         <v>0.35</v>
       </c>
-      <c r="L11" s="26" t="n">
+      <c r="M11" s="24" t="n">
         <v>0.35</v>
       </c>
-      <c r="M11" s="26" t="n">
+      <c r="N11" s="24" t="n">
         <v>0.35</v>
       </c>
-      <c r="N11" s="26" t="n">
-        <v>0.35</v>
-      </c>
     </row>
     <row r="12">
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Interest (% of Debt Open Bal)</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="25">
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="23">
         <f>E101/E98</f>
         <v/>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="23">
         <f>F101/F98</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="23">
         <f>G101/G98</f>
         <v/>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="23">
         <f>H101/H98</f>
         <v/>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="23">
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="27" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K12" s="27" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L12" s="27" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M12" s="27" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="N12" s="27" t="n">
-        <v>0.03</v>
+      <c r="J12" s="24" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="L12" s="24" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="M12" s="24" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>0.0437</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Tax Rate (% of Earnings Before Tax)</t>
         </is>
       </c>
-      <c r="C13" s="30" t="n"/>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="25">
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="23">
         <f>E35/E33</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="23">
         <f>F35/F33</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="23">
         <f>G35/G33</f>
         <v/>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="23">
         <f>H35/H33</f>
         <v/>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="23">
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="26" t="n">
+      <c r="J13" s="24" t="n">
         <v>0.1877</v>
       </c>
-      <c r="K13" s="26" t="n">
+      <c r="K13" s="24" t="n">
         <v>0.1877</v>
       </c>
-      <c r="L13" s="26" t="n">
+      <c r="L13" s="24" t="n">
         <v>0.1877</v>
       </c>
-      <c r="M13" s="26" t="n">
+      <c r="M13" s="24" t="n">
         <v>0.1877</v>
       </c>
-      <c r="N13" s="26" t="n">
+      <c r="N13" s="24" t="n">
         <v>0.1877</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Balance Sheet</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
-      <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
-      <c r="J14" s="18" t="n"/>
-      <c r="K14" s="18" t="n"/>
-      <c r="L14" s="18" t="n"/>
-      <c r="M14" s="18" t="n"/>
-      <c r="N14" s="18" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Accounts Receivable (Days)</t>
         </is>
       </c>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="28">
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="25">
         <f>E42/E24*365</f>
         <v/>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="25">
         <f>F42/F24*365</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="25">
         <f>G42/G24*365</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="25">
         <f>H42/H24*365</f>
         <v/>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="25">
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="29" t="n">
-        <v>90</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>90</v>
-      </c>
-      <c r="L15" s="29" t="n">
-        <v>90</v>
-      </c>
-      <c r="M15" s="29" t="n">
-        <v>90</v>
-      </c>
-      <c r="N15" s="29" t="n">
-        <v>90</v>
+      <c r="J15" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="M15" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="N15" s="26" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Inventory (Days)</t>
         </is>
       </c>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="28">
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="25">
         <f>E43/E25*365</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="25">
         <f>F43/F25*365</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="25">
         <f>G43/G25*365</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="25">
         <f>H43/H25*365</f>
         <v/>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="25">
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="J16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="29" t="n">
+      <c r="K16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="29" t="n">
+      <c r="L16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="29" t="n">
+      <c r="M16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="29" t="n">
+      <c r="N16" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="28">
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="25">
         <f>E48/E25*365</f>
         <v/>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="25">
         <f>F48/F25*365</f>
         <v/>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="25">
         <f>G48/G25*365</f>
         <v/>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="25">
         <f>H48/H25*365</f>
         <v/>
       </c>
-      <c r="I17" s="28">
+      <c r="I17" s="25">
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="M17" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="N17" s="29" t="n">
-        <v>30</v>
+      <c r="J17" s="26" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M17" s="26" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="N17" s="26" t="n">
+        <v>33.3</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Capital Expenditures ($000's)</t>
         </is>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="25">
         <f>E68</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="25">
         <f>F68</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="25">
         <f>G68</f>
         <v/>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="25">
         <f>H68</f>
         <v/>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="25">
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="29" t="n">
+      <c r="J18" s="26" t="n">
         <v>42559.6</v>
       </c>
-      <c r="K18" s="29" t="n">
+      <c r="K18" s="26" t="n">
         <v>45964.3</v>
       </c>
-      <c r="L18" s="29" t="n">
+      <c r="L18" s="26" t="n">
         <v>49641.5</v>
       </c>
-      <c r="M18" s="29" t="n">
+      <c r="M18" s="26" t="n">
         <v>53612.8</v>
       </c>
-      <c r="N18" s="29" t="n">
+      <c r="N18" s="26" t="n">
         <v>57901.8</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="25">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="25">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="25">
         <f>G99</f>
         <v/>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="25">
         <f>H99</f>
         <v/>
       </c>
-      <c r="I19" s="28">
+      <c r="I19" s="25">
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="29" t="n">
+      <c r="J19" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="29" t="n">
+      <c r="K19" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="29" t="n">
+      <c r="L19" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="29" t="n">
+      <c r="M19" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="29" t="n">
+      <c r="N19" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Equity Issued (Repaid) ($000's)</t>
         </is>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="25">
         <f>E73</f>
         <v/>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="25">
         <f>F73</f>
         <v/>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="25">
         <f>G73</f>
         <v/>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="25">
         <f>H73</f>
         <v/>
       </c>
-      <c r="I20" s="28">
+      <c r="I20" s="25">
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="29" t="n">
+      <c r="J20" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="29" t="n">
+      <c r="K20" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="29" t="n">
+      <c r="L20" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="29" t="n">
+      <c r="M20" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="29" t="n">
+      <c r="N20" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="28" t="n"/>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="28" t="n"/>
-      <c r="H21" s="28" t="n"/>
-      <c r="I21" s="28" t="n"/>
-      <c r="J21" s="33" t="n"/>
-      <c r="K21" s="33" t="n"/>
-      <c r="L21" s="33" t="n"/>
-      <c r="M21" s="33" t="n"/>
-      <c r="N21" s="33" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
+      <c r="J21" s="30" t="n"/>
+      <c r="K21" s="30" t="n"/>
+      <c r="L21" s="30" t="n"/>
+      <c r="M21" s="30" t="n"/>
+      <c r="N21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="E22" s="28" t="n"/>
-      <c r="F22" s="28" t="n"/>
-      <c r="G22" s="28" t="n"/>
-      <c r="H22" s="28" t="n"/>
-      <c r="I22" s="28" t="n"/>
-      <c r="J22" s="33" t="n"/>
-      <c r="K22" s="33" t="n"/>
-      <c r="L22" s="33" t="n"/>
-      <c r="M22" s="33" t="n"/>
-      <c r="N22" s="33" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="20" t="inlineStr">
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="30" t="n"/>
+      <c r="K22" s="30" t="n"/>
+      <c r="L22" s="30" t="n"/>
+      <c r="M22" s="30" t="n"/>
+      <c r="N22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Income Statement</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="20" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="20" t="n"/>
-      <c r="L23" s="20" t="n"/>
-      <c r="M23" s="20" t="n"/>
-      <c r="N23" s="20" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="M23" s="18" t="n"/>
+      <c r="N23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>Reveneue</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="29" t="n">
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>Revenue (FICO: Revenues)</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="26" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="26" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="29" t="n">
+      <c r="G24" s="26" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="29" t="n">
+      <c r="H24" s="26" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="29" t="n">
+      <c r="I24" s="26" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="21">
+      <c r="J24" s="19">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="21">
+      <c r="K24" s="19">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="21">
+      <c r="L24" s="19">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="21">
+      <c r="M24" s="19">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="21">
+      <c r="N24" s="19">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold (COGS)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="29" t="n">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>COGS (FICO: Cost of revenues)</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="26" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="26" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="29" t="n">
+      <c r="G25" s="26" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="29" t="n">
+      <c r="H25" s="26" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="29" t="n">
+      <c r="I25" s="26" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="34">
+      <c r="J25" s="31">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="34">
+      <c r="K25" s="31">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="34">
+      <c r="L25" s="31">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="34">
+      <c r="M25" s="31">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="34">
+      <c r="N25" s="31">
         <f>N24*N8</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C26" s="35" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="37">
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="34">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="37">
+      <c r="F26" s="34">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="37">
+      <c r="G26" s="34">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="37">
+      <c r="H26" s="34">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="37">
+      <c r="I26" s="34">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="37">
+      <c r="J26" s="34">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="37">
+      <c r="K26" s="34">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="37">
+      <c r="L26" s="34">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="37">
+      <c r="M26" s="34">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="37">
+      <c r="N26" s="34">
         <f>N24-N25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="38" t="n"/>
-      <c r="F27" s="38" t="n"/>
-      <c r="G27" s="38" t="n"/>
-      <c r="H27" s="38" t="n"/>
-      <c r="I27" s="38" t="n"/>
-      <c r="J27" s="24" t="n"/>
-      <c r="K27" s="24" t="n"/>
-      <c r="L27" s="24" t="n"/>
-      <c r="M27" s="24" t="n"/>
-      <c r="N27" s="24" t="n"/>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="35" t="n"/>
+      <c r="F27" s="35" t="n"/>
+      <c r="G27" s="35" t="n"/>
+      <c r="H27" s="35" t="n"/>
+      <c r="I27" s="35" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="22" t="n"/>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="22" t="n"/>
+      <c r="N27" s="22" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>Salaries and Benefits</t>
-        </is>
-      </c>
-      <c r="E28" s="29" t="n">
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>SG&amp;A (CFI Salaries ← FICO SG&amp;A)</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="26" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="29" t="n">
+      <c r="G28" s="26" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="29" t="n">
+      <c r="H28" s="26" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="29" t="n">
+      <c r="I28" s="26" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="18">
+      <c r="J28" s="16">
         <f>J9</f>
         <v/>
       </c>
-      <c r="K28" s="18">
+      <c r="K28" s="16">
         <f>K9</f>
         <v/>
       </c>
-      <c r="L28" s="18">
+      <c r="L28" s="16">
         <f>L9</f>
         <v/>
       </c>
-      <c r="M28" s="18">
+      <c r="M28" s="16">
         <f>M9</f>
         <v/>
       </c>
-      <c r="N28" s="18">
+      <c r="N28" s="16">
         <f>N9</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>Rent and Overhead</t>
-        </is>
-      </c>
-      <c r="E29" s="29" t="n">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>R&amp;D (CFI Rent/Overhead ← FICO R&amp;D)</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="26" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="29" t="n">
+      <c r="G29" s="26" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="29" t="n">
+      <c r="H29" s="26" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="29" t="n">
+      <c r="I29" s="26" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="18">
+      <c r="J29" s="16">
         <f>J10</f>
         <v/>
       </c>
-      <c r="K29" s="18">
+      <c r="K29" s="16">
         <f>K10</f>
         <v/>
       </c>
-      <c r="L29" s="18">
+      <c r="L29" s="16">
         <f>L10</f>
         <v/>
       </c>
-      <c r="M29" s="18">
+      <c r="M29" s="16">
         <f>M10</f>
         <v/>
       </c>
-      <c r="N29" s="18">
+      <c r="N29" s="16">
         <f>N10</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="26" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="26" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="29" t="n">
+      <c r="G30" s="26" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="29" t="n">
+      <c r="H30" s="26" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="29" t="n">
+      <c r="I30" s="26" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="18">
+      <c r="J30" s="16">
         <f>J94</f>
         <v/>
       </c>
-      <c r="K30" s="18">
+      <c r="K30" s="16">
         <f>K94</f>
         <v/>
       </c>
-      <c r="L30" s="18">
+      <c r="L30" s="16">
         <f>L94</f>
         <v/>
       </c>
-      <c r="M30" s="18">
+      <c r="M30" s="16">
         <f>M94</f>
         <v/>
       </c>
-      <c r="N30" s="18">
+      <c r="N30" s="16">
         <f>N94</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="39" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="C31" s="39" t="n"/>
-      <c r="D31" s="40" t="n"/>
-      <c r="E31" s="41" t="n">
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="37" t="n"/>
+      <c r="E31" s="38" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="41" t="n">
+      <c r="F31" s="38" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="41" t="n">
+      <c r="G31" s="38" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="41" t="n">
+      <c r="H31" s="38" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="41" t="n">
+      <c r="I31" s="38" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="42">
+      <c r="J31" s="39">
         <f>J101</f>
         <v/>
       </c>
-      <c r="K31" s="42">
+      <c r="K31" s="39">
         <f>K101</f>
         <v/>
       </c>
-      <c r="L31" s="42">
+      <c r="L31" s="39">
         <f>L101</f>
         <v/>
       </c>
-      <c r="M31" s="42">
+      <c r="M31" s="39">
         <f>M101</f>
         <v/>
       </c>
-      <c r="N31" s="42">
+      <c r="N31" s="39">
         <f>N101</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="24">
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="22">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="22">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="22">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="24">
+      <c r="H32" s="22">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="24">
+      <c r="I32" s="22">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="24">
+      <c r="J32" s="22">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="24">
+      <c r="K32" s="22">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="24">
+      <c r="L32" s="22">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="24">
+      <c r="M32" s="22">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="24">
+      <c r="N32" s="22">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="35" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>Earnings Before Tax</t>
         </is>
       </c>
-      <c r="C33" s="35" t="n"/>
-      <c r="D33" s="36" t="n"/>
-      <c r="E33" s="37">
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33" t="n"/>
+      <c r="E33" s="34">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="37">
+      <c r="F33" s="34">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="37">
+      <c r="G33" s="34">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="37">
+      <c r="H33" s="34">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="37">
+      <c r="I33" s="34">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="37">
+      <c r="J33" s="34">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="37">
+      <c r="K33" s="34">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="37">
+      <c r="L33" s="34">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="37">
+      <c r="M33" s="34">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="37">
+      <c r="N33" s="34">
         <f>N26-N32</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="38" t="n"/>
-      <c r="F34" s="38" t="n"/>
-      <c r="G34" s="38" t="n"/>
-      <c r="H34" s="38" t="n"/>
-      <c r="I34" s="38" t="n"/>
-      <c r="J34" s="24" t="n"/>
-      <c r="K34" s="24" t="n"/>
-      <c r="L34" s="24" t="n"/>
-      <c r="M34" s="24" t="n"/>
-      <c r="N34" s="24" t="n"/>
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="35" t="n"/>
+      <c r="G34" s="35" t="n"/>
+      <c r="H34" s="35" t="n"/>
+      <c r="I34" s="35" t="n"/>
+      <c r="J34" s="22" t="n"/>
+      <c r="K34" s="22" t="n"/>
+      <c r="L34" s="22" t="n"/>
+      <c r="M34" s="22" t="n"/>
+      <c r="N34" s="22" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>Taxes</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="29" t="n">
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="26" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="26" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="29" t="n">
+      <c r="G35" s="26" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="29" t="n">
+      <c r="H35" s="26" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="29" t="n">
+      <c r="I35" s="26" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="34">
+      <c r="J35" s="31">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="34">
+      <c r="K35" s="31">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="31">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="31">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="31">
         <f>N33*N13</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="16.2" customHeight="1">
-      <c r="B36" s="43" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C36" s="43" t="n"/>
-      <c r="D36" s="44" t="n"/>
-      <c r="E36" s="45">
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="41" t="n"/>
+      <c r="E36" s="42">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="45">
+      <c r="F36" s="42">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="45">
+      <c r="G36" s="42">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="45">
+      <c r="H36" s="42">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="45">
+      <c r="I36" s="42">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="45">
+      <c r="J36" s="42">
         <f>J33-J35</f>
         <v/>
       </c>
-      <c r="K36" s="45">
+      <c r="K36" s="42">
         <f>K33-K35</f>
         <v/>
       </c>
-      <c r="L36" s="45">
+      <c r="L36" s="42">
         <f>L33-L35</f>
         <v/>
       </c>
-      <c r="M36" s="45">
+      <c r="M36" s="42">
         <f>M33-M35</f>
         <v/>
       </c>
-      <c r="N36" s="45">
+      <c r="N36" s="42">
         <f>N33-N35</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="16.2" customHeight="1">
-      <c r="E37" s="33" t="n"/>
-      <c r="F37" s="33" t="n"/>
-      <c r="G37" s="33" t="n"/>
-      <c r="H37" s="33" t="n"/>
-      <c r="I37" s="33" t="n"/>
+    <row r="37">
+      <c r="E37" s="30" t="n"/>
+      <c r="F37" s="30" t="n"/>
+      <c r="G37" s="30" t="n"/>
+      <c r="H37" s="30" t="n"/>
+      <c r="I37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="E38" s="33" t="n"/>
-      <c r="F38" s="33" t="n"/>
-      <c r="G38" s="33" t="n"/>
-      <c r="H38" s="33" t="n"/>
-      <c r="I38" s="33" t="n"/>
-      <c r="J38" s="33" t="n"/>
-      <c r="K38" s="33" t="n"/>
-      <c r="L38" s="33" t="n"/>
-      <c r="M38" s="33" t="n"/>
-      <c r="N38" s="33" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+      <c r="E38" s="30" t="n"/>
+      <c r="F38" s="30" t="n"/>
+      <c r="G38" s="30" t="n"/>
+      <c r="H38" s="30" t="n"/>
+      <c r="I38" s="30" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
+      <c r="M38" s="30" t="n"/>
+      <c r="N38" s="30" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>Balance Sheet</t>
         </is>
       </c>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="20" t="n"/>
-      <c r="G39" s="20" t="n"/>
-      <c r="H39" s="20" t="n"/>
-      <c r="I39" s="20" t="n"/>
-      <c r="J39" s="20" t="n"/>
-      <c r="K39" s="20" t="n"/>
-      <c r="L39" s="20" t="n"/>
-      <c r="M39" s="20" t="n"/>
-      <c r="N39" s="20" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="18" t="n"/>
+      <c r="L39" s="18" t="n"/>
+      <c r="M39" s="18" t="n"/>
+      <c r="N39" s="18" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="21" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="E40" s="33" t="n"/>
-      <c r="F40" s="33" t="n"/>
-      <c r="G40" s="33" t="n"/>
-      <c r="H40" s="33" t="n"/>
-      <c r="I40" s="33" t="n"/>
+      <c r="E40" s="30" t="n"/>
+      <c r="F40" s="30" t="n"/>
+      <c r="G40" s="30" t="n"/>
+      <c r="H40" s="30" t="n"/>
+      <c r="I40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="26" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="26" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="29" t="n">
+      <c r="G41" s="26" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="29" t="n">
+      <c r="H41" s="26" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="29" t="n">
+      <c r="I41" s="26" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="18">
+      <c r="J41" s="16">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="18">
+      <c r="K41" s="16">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="18">
+      <c r="L41" s="16">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="18">
+      <c r="M41" s="16">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="18">
+      <c r="N41" s="16">
         <f>N78</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="26" t="n">
         <v>312107</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="26" t="n">
         <v>322410</v>
       </c>
-      <c r="G42" s="29" t="n">
+      <c r="G42" s="26" t="n">
         <v>387947</v>
       </c>
-      <c r="H42" s="29" t="n">
+      <c r="H42" s="26" t="n">
         <v>426642</v>
       </c>
-      <c r="I42" s="29" t="n">
+      <c r="I42" s="26" t="n">
         <v>529148</v>
       </c>
-      <c r="J42" s="46">
+      <c r="J42" s="43">
         <f>J24*J15/365</f>
         <v/>
       </c>
-      <c r="K42" s="46">
+      <c r="K42" s="43">
         <f>K24*K15/365</f>
         <v/>
       </c>
-      <c r="L42" s="46">
+      <c r="L42" s="43">
         <f>L24*L15/365</f>
         <v/>
       </c>
-      <c r="M42" s="46">
+      <c r="M42" s="43">
         <f>M24*M15/365</f>
         <v/>
       </c>
-      <c r="N42" s="46">
+      <c r="N42" s="43">
         <f>N24*N15/365</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="29" t="n">
+      <c r="G43" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="29" t="n">
+      <c r="H43" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="29" t="n">
+      <c r="I43" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="18">
+      <c r="J43" s="16">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="18">
+      <c r="K43" s="16">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="18">
+      <c r="L43" s="16">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="18">
+      <c r="M43" s="16">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="18">
+      <c r="N43" s="16">
         <f>N25*N16/365</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="18" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="26" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="26" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="29" t="n">
+      <c r="G44" s="26" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="29" t="n">
+      <c r="H44" s="26" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="29" t="n">
+      <c r="I44" s="26" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="18">
+      <c r="J44" s="16">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="18">
+      <c r="K44" s="16">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="18">
+      <c r="L44" s="16">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="18">
+      <c r="M44" s="16">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="18">
+      <c r="N44" s="16">
         <f>N95</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="16.2" customHeight="1">
-      <c r="B45" s="43" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="C45" s="43" t="n"/>
-      <c r="D45" s="44" t="n"/>
-      <c r="E45" s="45">
+      <c r="C45" s="40" t="n"/>
+      <c r="D45" s="41" t="n"/>
+      <c r="E45" s="42">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="45">
+      <c r="F45" s="42">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="45">
+      <c r="G45" s="42">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="45">
+      <c r="H45" s="42">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="45">
+      <c r="I45" s="42">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="45">
+      <c r="J45" s="42">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="45">
+      <c r="K45" s="42">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="45">
+      <c r="L45" s="42">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="45">
+      <c r="M45" s="42">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="45">
+      <c r="N45" s="42">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="16.2" customHeight="1">
-      <c r="B46" s="21" t="n"/>
-      <c r="C46" s="21" t="n"/>
-      <c r="D46" s="23" t="n"/>
-      <c r="E46" s="38" t="n"/>
-      <c r="F46" s="38" t="n"/>
-      <c r="G46" s="38" t="n"/>
-      <c r="H46" s="38" t="n"/>
-      <c r="I46" s="38" t="n"/>
-      <c r="J46" s="21" t="n"/>
-      <c r="K46" s="21" t="n"/>
-      <c r="L46" s="21" t="n"/>
-      <c r="M46" s="21" t="n"/>
-      <c r="N46" s="21" t="n"/>
+    <row r="46">
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="35" t="n"/>
+      <c r="F46" s="35" t="n"/>
+      <c r="G46" s="35" t="n"/>
+      <c r="H46" s="35" t="n"/>
+      <c r="I46" s="35" t="n"/>
+      <c r="J46" s="19" t="n"/>
+      <c r="K46" s="19" t="n"/>
+      <c r="L46" s="19" t="n"/>
+      <c r="M46" s="19" t="n"/>
+      <c r="N46" s="19" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="21" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
       </c>
-      <c r="E47" s="33" t="n"/>
-      <c r="F47" s="33" t="n"/>
-      <c r="G47" s="33" t="n"/>
-      <c r="H47" s="33" t="n"/>
-      <c r="I47" s="33" t="n"/>
+      <c r="E47" s="30" t="n"/>
+      <c r="F47" s="30" t="n"/>
+      <c r="G47" s="30" t="n"/>
+      <c r="H47" s="30" t="n"/>
+      <c r="I47" s="30" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="26" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="26" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="29" t="n">
+      <c r="G48" s="26" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="29" t="n">
+      <c r="H48" s="26" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="29" t="n">
+      <c r="I48" s="26" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="18">
+      <c r="J48" s="16">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="18">
+      <c r="K48" s="16">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="18">
+      <c r="L48" s="16">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="18">
+      <c r="M48" s="16">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="18">
+      <c r="N48" s="16">
         <f>N25*N17/365</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="26" t="n">
         <v>1009018</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="26" t="n">
         <v>1823669</v>
       </c>
-      <c r="G49" s="29" t="n">
+      <c r="G49" s="26" t="n">
         <v>1811658</v>
       </c>
-      <c r="H49" s="29" t="n">
+      <c r="H49" s="26" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="29" t="n">
+      <c r="I49" s="26" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="18">
+      <c r="J49" s="16">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="18">
+      <c r="K49" s="16">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="18">
+      <c r="L49" s="16">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="18">
+      <c r="M49" s="16">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="18">
+      <c r="N49" s="16">
         <f>N100</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="35" t="inlineStr">
+      <c r="B50" s="32" t="inlineStr">
         <is>
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="C50" s="35" t="n"/>
-      <c r="D50" s="36" t="n"/>
-      <c r="E50" s="37">
+      <c r="C50" s="32" t="n"/>
+      <c r="D50" s="33" t="n"/>
+      <c r="E50" s="34">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="37">
+      <c r="F50" s="34">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="37">
+      <c r="G50" s="34">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="37">
+      <c r="H50" s="34">
         <f>SUM(H48:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="37">
+      <c r="I50" s="34">
         <f>SUM(I48:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="37">
+      <c r="J50" s="34">
         <f>SUM(J48:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="37">
+      <c r="K50" s="34">
         <f>SUM(K48:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="37">
+      <c r="L50" s="34">
         <f>SUM(L48:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="37">
+      <c r="M50" s="34">
         <f>SUM(M48:M49)</f>
         <v/>
       </c>
-      <c r="N50" s="37">
+      <c r="N50" s="34">
         <f>SUM(N48:N49)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="21" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>Shareholder's Equity</t>
         </is>
       </c>
-      <c r="E51" s="33" t="n"/>
-      <c r="F51" s="33" t="n"/>
-      <c r="G51" s="33" t="n"/>
-      <c r="H51" s="33" t="n"/>
-      <c r="I51" s="33" t="n"/>
+      <c r="E51" s="30" t="n"/>
+      <c r="F51" s="30" t="n"/>
+      <c r="G51" s="30" t="n"/>
+      <c r="H51" s="30" t="n"/>
+      <c r="I51" s="30" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="26" t="n">
         <v>-3079536</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="26" t="n">
         <v>-4326434</v>
       </c>
-      <c r="G52" s="29" t="n">
+      <c r="G52" s="26" t="n">
         <v>-4683035</v>
       </c>
-      <c r="H52" s="29" t="n">
+      <c r="H52" s="26" t="n">
         <v>-5516590</v>
       </c>
-      <c r="I52" s="29" t="n">
+      <c r="I52" s="26" t="n">
         <v>-6909825</v>
       </c>
-      <c r="J52" s="18">
+      <c r="J52" s="16">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="18">
+      <c r="K52" s="16">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="18">
+      <c r="L52" s="16">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="18">
+      <c r="M52" s="16">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="18">
+      <c r="N52" s="16">
         <f>M52+N20</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="26" t="n">
         <v>2585143</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="26" t="n">
         <v>2958684</v>
       </c>
-      <c r="G53" s="29" t="n">
+      <c r="G53" s="26" t="n">
         <v>3388059</v>
       </c>
-      <c r="H53" s="29" t="n">
+      <c r="H53" s="26" t="n">
         <v>3900870</v>
       </c>
-      <c r="I53" s="29" t="n">
+      <c r="I53" s="26" t="n">
         <v>4552816</v>
       </c>
-      <c r="J53" s="18">
+      <c r="J53" s="16">
         <f>I53+J36</f>
         <v/>
       </c>
-      <c r="K53" s="18">
+      <c r="K53" s="16">
         <f>J53+K36</f>
         <v/>
       </c>
-      <c r="L53" s="18">
+      <c r="L53" s="16">
         <f>K53+L36</f>
         <v/>
       </c>
-      <c r="M53" s="18">
+      <c r="M53" s="16">
         <f>L53+M36</f>
         <v/>
       </c>
-      <c r="N53" s="18">
+      <c r="N53" s="16">
         <f>M53+N36</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="47" t="inlineStr">
+      <c r="B54" s="44" t="inlineStr">
         <is>
           <t>Shareholder's Equity</t>
         </is>
       </c>
-      <c r="C54" s="47" t="n"/>
-      <c r="D54" s="48" t="n"/>
-      <c r="E54" s="49">
+      <c r="C54" s="44" t="n"/>
+      <c r="D54" s="45" t="n"/>
+      <c r="E54" s="46">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="49">
+      <c r="F54" s="46">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="49">
+      <c r="G54" s="46">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="49">
+      <c r="H54" s="46">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="49">
+      <c r="I54" s="46">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="49">
+      <c r="J54" s="46">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="49">
+      <c r="K54" s="46">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="49">
+      <c r="L54" s="46">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="49">
+      <c r="M54" s="46">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="49">
+      <c r="N54" s="46">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="16.2" customHeight="1">
-      <c r="B55" s="43" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="40" t="inlineStr">
         <is>
           <t>Total Liabilities &amp; Shareholder's Equity</t>
         </is>
       </c>
-      <c r="C55" s="43" t="n"/>
-      <c r="D55" s="44" t="n"/>
-      <c r="E55" s="45">
+      <c r="C55" s="40" t="n"/>
+      <c r="D55" s="41" t="n"/>
+      <c r="E55" s="42">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="45">
+      <c r="F55" s="42">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="45">
+      <c r="G55" s="42">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="45">
+      <c r="H55" s="42">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="45">
+      <c r="I55" s="42">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="45">
+      <c r="J55" s="42">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="45">
+      <c r="K55" s="42">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="45">
+      <c r="L55" s="42">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="45">
+      <c r="M55" s="42">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="45">
+      <c r="N55" s="42">
         <f>N50+N54</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="16.2" customHeight="1">
-      <c r="E56" s="33" t="n"/>
-      <c r="F56" s="33" t="n"/>
-      <c r="G56" s="33" t="n"/>
-      <c r="H56" s="33" t="n"/>
-      <c r="I56" s="33" t="n"/>
-      <c r="J56" s="33" t="n"/>
-      <c r="K56" s="33" t="n"/>
-      <c r="L56" s="33" t="n"/>
-      <c r="M56" s="33" t="n"/>
-      <c r="N56" s="33" t="n"/>
+    <row r="56">
+      <c r="E56" s="30" t="n"/>
+      <c r="F56" s="30" t="n"/>
+      <c r="G56" s="30" t="n"/>
+      <c r="H56" s="30" t="n"/>
+      <c r="I56" s="30" t="n"/>
+      <c r="J56" s="30" t="n"/>
+      <c r="K56" s="30" t="n"/>
+      <c r="L56" s="30" t="n"/>
+      <c r="M56" s="30" t="n"/>
+      <c r="N56" s="30" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="30" t="inlineStr">
+      <c r="B57" s="27" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C57" s="50" t="n"/>
-      <c r="D57" s="51" t="n"/>
-      <c r="E57" s="52">
+      <c r="C57" s="47" t="n"/>
+      <c r="D57" s="48" t="n"/>
+      <c r="E57" s="49">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="52">
+      <c r="F57" s="49">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="52">
+      <c r="G57" s="49">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="52">
+      <c r="H57" s="49">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="52">
+      <c r="I57" s="49">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="52">
+      <c r="J57" s="49">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="52">
+      <c r="K57" s="49">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="52">
+      <c r="L57" s="49">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="52">
+      <c r="M57" s="49">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="52">
+      <c r="N57" s="49">
         <f>N55-N45</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="50" t="n"/>
-      <c r="C58" s="50" t="n"/>
-      <c r="D58" s="51" t="n"/>
-      <c r="E58" s="50" t="n"/>
-      <c r="F58" s="50" t="n"/>
-      <c r="G58" s="50" t="n"/>
-      <c r="H58" s="50" t="n"/>
-      <c r="I58" s="50" t="n"/>
-      <c r="J58" s="50" t="n"/>
-      <c r="K58" s="50" t="n"/>
-      <c r="L58" s="50" t="n"/>
-      <c r="M58" s="50" t="n"/>
-      <c r="N58" s="50" t="n"/>
+      <c r="B58" s="47" t="n"/>
+      <c r="C58" s="47" t="n"/>
+      <c r="D58" s="48" t="n"/>
+      <c r="E58" s="47" t="n"/>
+      <c r="F58" s="47" t="n"/>
+      <c r="G58" s="47" t="n"/>
+      <c r="H58" s="47" t="n"/>
+      <c r="I58" s="47" t="n"/>
+      <c r="J58" s="47" t="n"/>
+      <c r="K58" s="47" t="n"/>
+      <c r="L58" s="47" t="n"/>
+      <c r="M58" s="47" t="n"/>
+      <c r="N58" s="47" t="n"/>
     </row>
     <row r="59">
-      <c r="E59" s="33" t="n"/>
-      <c r="F59" s="33" t="n"/>
-      <c r="G59" s="33" t="n"/>
-      <c r="H59" s="33" t="n"/>
-      <c r="I59" s="33" t="n"/>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="B60" s="20" t="inlineStr">
+      <c r="E59" s="30" t="n"/>
+      <c r="F59" s="30" t="n"/>
+      <c r="G59" s="30" t="n"/>
+      <c r="H59" s="30" t="n"/>
+      <c r="I59" s="30" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="18" t="inlineStr">
         <is>
           <t>Cash Flow Statement</t>
         </is>
       </c>
-      <c r="C60" s="20" t="n"/>
-      <c r="D60" s="20" t="n"/>
-      <c r="E60" s="20" t="n"/>
-      <c r="F60" s="20" t="n"/>
-      <c r="G60" s="20" t="n"/>
-      <c r="H60" s="20" t="n"/>
-      <c r="I60" s="20" t="n"/>
-      <c r="J60" s="20" t="n"/>
-      <c r="K60" s="20" t="n"/>
-      <c r="L60" s="20" t="n"/>
-      <c r="M60" s="20" t="n"/>
-      <c r="N60" s="20" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="18" t="n"/>
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="18" t="n"/>
+      <c r="K60" s="18" t="n"/>
+      <c r="L60" s="18" t="n"/>
+      <c r="M60" s="18" t="n"/>
+      <c r="N60" s="18" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="21" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="E61" s="33" t="n"/>
-      <c r="F61" s="33" t="n"/>
-      <c r="G61" s="33" t="n"/>
-      <c r="H61" s="33" t="n"/>
-      <c r="I61" s="33" t="n"/>
+      <c r="E61" s="30" t="n"/>
+      <c r="F61" s="30" t="n"/>
+      <c r="G61" s="30" t="n"/>
+      <c r="H61" s="30" t="n"/>
+      <c r="I61" s="30" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="18" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="16">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="18">
+      <c r="F62" s="16">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="18">
+      <c r="G62" s="16">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="18">
+      <c r="H62" s="16">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="18">
+      <c r="I62" s="16">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="18">
+      <c r="J62" s="16">
         <f>J36</f>
         <v/>
       </c>
-      <c r="K62" s="18">
+      <c r="K62" s="16">
         <f>K36</f>
         <v/>
       </c>
-      <c r="L62" s="18">
+      <c r="L62" s="16">
         <f>L36</f>
         <v/>
       </c>
-      <c r="M62" s="18">
+      <c r="M62" s="16">
         <f>M36</f>
         <v/>
       </c>
-      <c r="N62" s="18">
+      <c r="N62" s="16">
         <f>N36</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="18" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E63" s="18">
+      <c r="E63" s="16">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="18">
+      <c r="F63" s="16">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="18">
+      <c r="G63" s="16">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="18">
+      <c r="H63" s="16">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="18">
+      <c r="I63" s="16">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="18">
+      <c r="J63" s="16">
         <f>+J30</f>
         <v/>
       </c>
-      <c r="K63" s="18">
+      <c r="K63" s="16">
         <f>+K30</f>
         <v/>
       </c>
-      <c r="L63" s="18">
+      <c r="L63" s="16">
         <f>+L30</f>
         <v/>
       </c>
-      <c r="M63" s="18">
+      <c r="M63" s="16">
         <f>+M30</f>
         <v/>
       </c>
-      <c r="N63" s="18">
+      <c r="N63" s="16">
         <f>+N30</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="18" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="E64" s="29" t="n">
+      <c r="E64" s="26" t="n">
         <v>-19789</v>
       </c>
-      <c r="F64" s="29" t="n">
+      <c r="F64" s="26" t="n">
         <v>13779</v>
       </c>
-      <c r="G64" s="29" t="n">
+      <c r="G64" s="26" t="n">
         <v>63801</v>
       </c>
-      <c r="H64" s="29" t="n">
+      <c r="H64" s="26" t="n">
         <v>35231</v>
       </c>
-      <c r="I64" s="29" t="n">
+      <c r="I64" s="26" t="n">
         <v>92664</v>
       </c>
-      <c r="J64" s="18">
+      <c r="J64" s="16">
         <f>J89</f>
         <v/>
       </c>
-      <c r="K64" s="18">
+      <c r="K64" s="16">
         <f>K89</f>
         <v/>
       </c>
-      <c r="L64" s="18">
+      <c r="L64" s="16">
         <f>L89</f>
         <v/>
       </c>
-      <c r="M64" s="18">
+      <c r="M64" s="16">
         <f>M89</f>
         <v/>
       </c>
-      <c r="N64" s="18">
+      <c r="N64" s="16">
         <f>N89</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="35" t="inlineStr">
+      <c r="B65" s="32" t="inlineStr">
         <is>
           <t>Cash from Operations</t>
         </is>
       </c>
-      <c r="C65" s="53" t="n"/>
-      <c r="D65" s="54" t="n"/>
-      <c r="E65" s="37">
+      <c r="C65" s="50" t="n"/>
+      <c r="D65" s="51" t="n"/>
+      <c r="E65" s="34">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="37">
+      <c r="F65" s="34">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="37">
+      <c r="G65" s="34">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="37">
+      <c r="H65" s="34">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="37">
+      <c r="I65" s="34">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="37">
+      <c r="J65" s="34">
         <f>J62+J63-J64</f>
         <v/>
       </c>
-      <c r="K65" s="37">
+      <c r="K65" s="34">
         <f>K62+K63-K64</f>
         <v/>
       </c>
-      <c r="L65" s="37">
+      <c r="L65" s="34">
         <f>L62+L63-L64</f>
         <v/>
       </c>
-      <c r="M65" s="37">
+      <c r="M65" s="34">
         <f>M62+M63-M64</f>
         <v/>
       </c>
-      <c r="N65" s="37">
+      <c r="N65" s="34">
         <f>N62+N63-N64</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="21" t="n"/>
-      <c r="C66" s="18" t="n"/>
-      <c r="D66" s="22" t="n"/>
-      <c r="E66" s="38" t="n"/>
-      <c r="F66" s="38" t="n"/>
-      <c r="G66" s="38" t="n"/>
-      <c r="H66" s="38" t="n"/>
-      <c r="I66" s="38" t="n"/>
-      <c r="J66" s="21" t="n"/>
-      <c r="K66" s="21" t="n"/>
-      <c r="L66" s="21" t="n"/>
-      <c r="M66" s="21" t="n"/>
-      <c r="N66" s="21" t="n"/>
+      <c r="B66" s="19" t="n"/>
+      <c r="C66" s="16" t="n"/>
+      <c r="D66" s="20" t="n"/>
+      <c r="E66" s="35" t="n"/>
+      <c r="F66" s="35" t="n"/>
+      <c r="G66" s="35" t="n"/>
+      <c r="H66" s="35" t="n"/>
+      <c r="I66" s="35" t="n"/>
+      <c r="J66" s="19" t="n"/>
+      <c r="K66" s="19" t="n"/>
+      <c r="L66" s="19" t="n"/>
+      <c r="M66" s="19" t="n"/>
+      <c r="N66" s="19" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="21" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="E67" s="33" t="n"/>
-      <c r="F67" s="33" t="n"/>
-      <c r="G67" s="33" t="n"/>
-      <c r="H67" s="33" t="n"/>
-      <c r="I67" s="33" t="n"/>
-      <c r="J67" s="18" t="n"/>
-      <c r="K67" s="18" t="n"/>
-      <c r="L67" s="18" t="n"/>
-      <c r="M67" s="18" t="n"/>
-      <c r="N67" s="18" t="n"/>
+      <c r="E67" s="30" t="n"/>
+      <c r="F67" s="30" t="n"/>
+      <c r="G67" s="30" t="n"/>
+      <c r="H67" s="30" t="n"/>
+      <c r="I67" s="30" t="n"/>
+      <c r="J67" s="16" t="n"/>
+      <c r="K67" s="16" t="n"/>
+      <c r="L67" s="16" t="n"/>
+      <c r="M67" s="16" t="n"/>
+      <c r="N67" s="16" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="18" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E68" s="29" t="n">
+      <c r="E68" s="26" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="29" t="n">
+      <c r="F68" s="26" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="29" t="n">
+      <c r="G68" s="26" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="29" t="n">
+      <c r="H68" s="26" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="29" t="n">
+      <c r="I68" s="26" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="18">
+      <c r="J68" s="16">
         <f>J18</f>
         <v/>
       </c>
-      <c r="K68" s="18">
+      <c r="K68" s="16">
         <f>K18</f>
         <v/>
       </c>
-      <c r="L68" s="18">
+      <c r="L68" s="16">
         <f>L18</f>
         <v/>
       </c>
-      <c r="M68" s="18">
+      <c r="M68" s="16">
         <f>M18</f>
         <v/>
       </c>
-      <c r="N68" s="18">
+      <c r="N68" s="16">
         <f>N18</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="35" t="inlineStr">
+      <c r="B69" s="32" t="inlineStr">
         <is>
           <t>Cash from Investing</t>
         </is>
       </c>
-      <c r="C69" s="53" t="n"/>
-      <c r="D69" s="54" t="n"/>
-      <c r="E69" s="37">
+      <c r="C69" s="50" t="n"/>
+      <c r="D69" s="51" t="n"/>
+      <c r="E69" s="34">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="37">
+      <c r="F69" s="34">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="37">
+      <c r="G69" s="34">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="37">
+      <c r="H69" s="34">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="37">
+      <c r="I69" s="34">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="37">
+      <c r="J69" s="34">
         <f>SUM(J68)</f>
         <v/>
       </c>
-      <c r="K69" s="37">
+      <c r="K69" s="34">
         <f>SUM(K68)</f>
         <v/>
       </c>
-      <c r="L69" s="37">
+      <c r="L69" s="34">
         <f>SUM(L68)</f>
         <v/>
       </c>
-      <c r="M69" s="37">
+      <c r="M69" s="34">
         <f>SUM(M68)</f>
         <v/>
       </c>
-      <c r="N69" s="37">
+      <c r="N69" s="34">
         <f>SUM(N68)</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="21" t="n"/>
-      <c r="C70" s="18" t="n"/>
-      <c r="D70" s="22" t="n"/>
-      <c r="E70" s="38" t="n"/>
-      <c r="F70" s="38" t="n"/>
-      <c r="G70" s="38" t="n"/>
-      <c r="H70" s="38" t="n"/>
-      <c r="I70" s="38" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
+      <c r="B70" s="19" t="n"/>
+      <c r="C70" s="16" t="n"/>
+      <c r="D70" s="20" t="n"/>
+      <c r="E70" s="35" t="n"/>
+      <c r="F70" s="35" t="n"/>
+      <c r="G70" s="35" t="n"/>
+      <c r="H70" s="35" t="n"/>
+      <c r="I70" s="35" t="n"/>
+      <c r="J70" s="19" t="n"/>
+      <c r="K70" s="19" t="n"/>
+      <c r="L70" s="19" t="n"/>
+      <c r="M70" s="19" t="n"/>
+      <c r="N70" s="19" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="21" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="E71" s="33" t="n"/>
-      <c r="F71" s="33" t="n"/>
-      <c r="G71" s="33" t="n"/>
-      <c r="H71" s="33" t="n"/>
-      <c r="I71" s="33" t="n"/>
-      <c r="J71" s="18" t="n"/>
-      <c r="K71" s="18" t="n"/>
-      <c r="L71" s="18" t="n"/>
-      <c r="M71" s="18" t="n"/>
-      <c r="N71" s="18" t="n"/>
+      <c r="E71" s="30" t="n"/>
+      <c r="F71" s="30" t="n"/>
+      <c r="G71" s="30" t="n"/>
+      <c r="H71" s="30" t="n"/>
+      <c r="I71" s="30" t="n"/>
+      <c r="J71" s="16" t="n"/>
+      <c r="K71" s="16" t="n"/>
+      <c r="L71" s="16" t="n"/>
+      <c r="M71" s="16" t="n"/>
+      <c r="N71" s="16" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="18" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="29" t="n">
+      <c r="E72" s="26" t="n">
         <v>269583</v>
       </c>
-      <c r="F72" s="29" t="n">
+      <c r="F72" s="26" t="n">
         <v>814651</v>
       </c>
-      <c r="G72" s="29" t="n">
+      <c r="G72" s="26" t="n">
         <v>-12011</v>
       </c>
-      <c r="H72" s="29" t="n">
+      <c r="H72" s="26" t="n">
         <v>397363</v>
       </c>
-      <c r="I72" s="29" t="n">
+      <c r="I72" s="26" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="18">
+      <c r="J72" s="16">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="18">
+      <c r="K72" s="16">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="18">
+      <c r="L72" s="16">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="18">
+      <c r="M72" s="16">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="18">
+      <c r="N72" s="16">
         <f>N19</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="18" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="29" t="n">
+      <c r="E73" s="26" t="n">
         <v>-661519</v>
       </c>
-      <c r="F73" s="29" t="n">
+      <c r="F73" s="26" t="n">
         <v>-1251001</v>
       </c>
-      <c r="G73" s="29" t="n">
+      <c r="G73" s="26" t="n">
         <v>-360388</v>
       </c>
-      <c r="H73" s="29" t="n">
+      <c r="H73" s="26" t="n">
         <v>-849330</v>
       </c>
-      <c r="I73" s="29" t="n">
+      <c r="I73" s="26" t="n">
         <v>-1398028</v>
       </c>
-      <c r="J73" s="18">
+      <c r="J73" s="16">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="18">
+      <c r="K73" s="16">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="18">
+      <c r="L73" s="16">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="18">
+      <c r="M73" s="16">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="18">
+      <c r="N73" s="16">
         <f>N20</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="35" t="inlineStr">
+      <c r="B74" s="32" t="inlineStr">
         <is>
           <t>Cash from Financing</t>
         </is>
       </c>
-      <c r="C74" s="53" t="n"/>
-      <c r="D74" s="54" t="n"/>
-      <c r="E74" s="37">
+      <c r="C74" s="50" t="n"/>
+      <c r="D74" s="51" t="n"/>
+      <c r="E74" s="34">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="37">
+      <c r="F74" s="34">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="37">
+      <c r="G74" s="34">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="37">
+      <c r="H74" s="34">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="37">
+      <c r="I74" s="34">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="37">
+      <c r="J74" s="34">
         <f>SUM(J72:J73)</f>
         <v/>
       </c>
-      <c r="K74" s="37">
+      <c r="K74" s="34">
         <f>SUM(K72:K73)</f>
         <v/>
       </c>
-      <c r="L74" s="37">
+      <c r="L74" s="34">
         <f>SUM(L72:L73)</f>
         <v/>
       </c>
-      <c r="M74" s="37">
+      <c r="M74" s="34">
         <f>SUM(M72:M73)</f>
         <v/>
       </c>
-      <c r="N74" s="37">
+      <c r="N74" s="34">
         <f>SUM(N72:N73)</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="21" t="n"/>
-      <c r="C75" s="18" t="n"/>
-      <c r="D75" s="22" t="n"/>
-      <c r="E75" s="38" t="n"/>
-      <c r="F75" s="38" t="n"/>
-      <c r="G75" s="38" t="n"/>
-      <c r="H75" s="38" t="n"/>
-      <c r="I75" s="38" t="n"/>
-      <c r="J75" s="21" t="n"/>
-      <c r="K75" s="21" t="n"/>
-      <c r="L75" s="21" t="n"/>
-      <c r="M75" s="21" t="n"/>
-      <c r="N75" s="21" t="n"/>
+      <c r="B75" s="19" t="n"/>
+      <c r="C75" s="16" t="n"/>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="35" t="n"/>
+      <c r="F75" s="35" t="n"/>
+      <c r="G75" s="35" t="n"/>
+      <c r="H75" s="35" t="n"/>
+      <c r="I75" s="35" t="n"/>
+      <c r="J75" s="19" t="n"/>
+      <c r="K75" s="19" t="n"/>
+      <c r="L75" s="19" t="n"/>
+      <c r="M75" s="19" t="n"/>
+      <c r="N75" s="19" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="18" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="E76" s="28">
+      <c r="E76" s="25">
         <f>E65-E69+E74</f>
         <v/>
       </c>
-      <c r="F76" s="28">
+      <c r="F76" s="25">
         <f>F65-F69+F74</f>
         <v/>
       </c>
-      <c r="G76" s="28">
+      <c r="G76" s="25">
         <f>G65-G69+G74</f>
         <v/>
       </c>
-      <c r="H76" s="28">
+      <c r="H76" s="25">
         <f>H65-H69+H74</f>
         <v/>
       </c>
-      <c r="I76" s="28">
+      <c r="I76" s="25">
         <f>I65-I69+I74</f>
         <v/>
       </c>
-      <c r="J76" s="28">
+      <c r="J76" s="25">
         <f>J65-J69+J74</f>
         <v/>
       </c>
-      <c r="K76" s="28">
+      <c r="K76" s="25">
         <f>K65-K69+K74</f>
         <v/>
       </c>
-      <c r="L76" s="28">
+      <c r="L76" s="25">
         <f>L65-L69+L74</f>
         <v/>
       </c>
-      <c r="M76" s="28">
+      <c r="M76" s="25">
         <f>M65-M69+M74</f>
         <v/>
       </c>
-      <c r="N76" s="28">
+      <c r="N76" s="25">
         <f>N65-N69+N74</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="18" t="inlineStr">
+      <c r="B77" s="16" t="inlineStr">
         <is>
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="18">
+      <c r="E77" s="16">
         <f>D78</f>
         <v/>
       </c>
-      <c r="F77" s="29" t="n">
+      <c r="F77" s="26" t="n">
         <v>195354</v>
       </c>
-      <c r="G77" s="29" t="n">
+      <c r="G77" s="26" t="n">
         <v>133202</v>
       </c>
-      <c r="H77" s="29" t="n">
+      <c r="H77" s="26" t="n">
         <v>136778</v>
       </c>
-      <c r="I77" s="29" t="n">
+      <c r="I77" s="26" t="n">
         <v>150667</v>
       </c>
-      <c r="J77" s="18">
+      <c r="J77" s="16">
         <f>+I78</f>
         <v/>
       </c>
-      <c r="K77" s="18">
+      <c r="K77" s="16">
         <f>+J78</f>
         <v/>
       </c>
-      <c r="L77" s="18">
+      <c r="L77" s="16">
         <f>+K78</f>
         <v/>
       </c>
-      <c r="M77" s="18">
+      <c r="M77" s="16">
         <f>+L78</f>
         <v/>
       </c>
-      <c r="N77" s="18">
+      <c r="N77" s="16">
         <f>+M78</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="35" t="inlineStr">
+      <c r="B78" s="32" t="inlineStr">
         <is>
           <t>Closing Cash Balance</t>
         </is>
       </c>
-      <c r="C78" s="53" t="n"/>
-      <c r="D78" s="55" t="n">
+      <c r="C78" s="50" t="n"/>
+      <c r="D78" s="52" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="37">
+      <c r="E78" s="34">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="37">
+      <c r="F78" s="34">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="37">
+      <c r="G78" s="34">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="37">
+      <c r="H78" s="34">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="37">
+      <c r="I78" s="34">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="37">
+      <c r="J78" s="34">
         <f>SUM(J76:J77)</f>
         <v/>
       </c>
-      <c r="K78" s="37">
+      <c r="K78" s="34">
         <f>SUM(K76:K77)</f>
         <v/>
       </c>
-      <c r="L78" s="37">
+      <c r="L78" s="34">
         <f>SUM(L76:L77)</f>
         <v/>
       </c>
-      <c r="M78" s="37">
+      <c r="M78" s="34">
         <f>SUM(M76:M77)</f>
         <v/>
       </c>
-      <c r="N78" s="37">
+      <c r="N78" s="34">
         <f>SUM(N76:N77)</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="21" t="n"/>
-      <c r="E79" s="38" t="n"/>
-      <c r="F79" s="33" t="n"/>
-      <c r="G79" s="33" t="n"/>
-      <c r="H79" s="33" t="n"/>
-      <c r="I79" s="33" t="n"/>
+      <c r="B79" s="19" t="n"/>
+      <c r="E79" s="35" t="n"/>
+      <c r="F79" s="30" t="n"/>
+      <c r="G79" s="30" t="n"/>
+      <c r="H79" s="30" t="n"/>
+      <c r="I79" s="30" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="30" t="inlineStr">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C80" s="50" t="n"/>
-      <c r="D80" s="51" t="n"/>
-      <c r="E80" s="52">
+      <c r="C80" s="47" t="n"/>
+      <c r="D80" s="48" t="n"/>
+      <c r="E80" s="49">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="52">
+      <c r="F80" s="49">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="52">
+      <c r="G80" s="49">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="52">
+      <c r="H80" s="49">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="52">
+      <c r="I80" s="49">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="52">
+      <c r="J80" s="49">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="52">
+      <c r="K80" s="49">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="52">
+      <c r="L80" s="49">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="52">
+      <c r="M80" s="49">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="52">
+      <c r="N80" s="49">
         <f>N78-N41</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="21" t="n"/>
-      <c r="E81" s="38" t="n"/>
-      <c r="F81" s="33" t="n"/>
-      <c r="G81" s="33" t="n"/>
-      <c r="H81" s="33" t="n"/>
-      <c r="I81" s="33" t="n"/>
+      <c r="B81" s="19" t="n"/>
+      <c r="E81" s="35" t="n"/>
+      <c r="F81" s="30" t="n"/>
+      <c r="G81" s="30" t="n"/>
+      <c r="H81" s="30" t="n"/>
+      <c r="I81" s="30" t="n"/>
     </row>
     <row r="82">
-      <c r="E82" s="33" t="n"/>
-      <c r="F82" s="33" t="n"/>
-      <c r="G82" s="33" t="n"/>
-      <c r="H82" s="33" t="n"/>
-      <c r="I82" s="33" t="n"/>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="B83" s="20" t="inlineStr">
+      <c r="E82" s="30" t="n"/>
+      <c r="F82" s="30" t="n"/>
+      <c r="G82" s="30" t="n"/>
+      <c r="H82" s="30" t="n"/>
+      <c r="I82" s="30" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="18" t="inlineStr">
         <is>
           <t>Supporting Schedules</t>
         </is>
       </c>
-      <c r="C83" s="20" t="n"/>
-      <c r="D83" s="20" t="n"/>
-      <c r="E83" s="20" t="n"/>
-      <c r="F83" s="20" t="n"/>
-      <c r="G83" s="20" t="n"/>
-      <c r="H83" s="20" t="n"/>
-      <c r="I83" s="20" t="n"/>
-      <c r="J83" s="20" t="n"/>
-      <c r="K83" s="20" t="n"/>
-      <c r="L83" s="20" t="n"/>
-      <c r="M83" s="20" t="n"/>
-      <c r="N83" s="20" t="n"/>
+      <c r="C83" s="18" t="n"/>
+      <c r="D83" s="18" t="n"/>
+      <c r="E83" s="18" t="n"/>
+      <c r="F83" s="18" t="n"/>
+      <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="n"/>
+      <c r="I83" s="18" t="n"/>
+      <c r="J83" s="18" t="n"/>
+      <c r="K83" s="18" t="n"/>
+      <c r="L83" s="18" t="n"/>
+      <c r="M83" s="18" t="n"/>
+      <c r="N83" s="18" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="21" t="inlineStr">
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t>Working Capital Schedule</t>
         </is>
       </c>
-      <c r="F84" s="33" t="n"/>
-      <c r="G84" s="33" t="n"/>
-      <c r="H84" s="33" t="n"/>
-      <c r="I84" s="33" t="n"/>
+      <c r="F84" s="30" t="n"/>
+      <c r="G84" s="30" t="n"/>
+      <c r="H84" s="30" t="n"/>
+      <c r="I84" s="30" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="18" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="29" t="n">
+      <c r="E85" s="26" t="n">
         <v>312107</v>
       </c>
-      <c r="F85" s="29" t="n">
+      <c r="F85" s="26" t="n">
         <v>322410</v>
       </c>
-      <c r="G85" s="29" t="n">
+      <c r="G85" s="26" t="n">
         <v>387947</v>
       </c>
-      <c r="H85" s="29" t="n">
+      <c r="H85" s="26" t="n">
         <v>426642</v>
       </c>
-      <c r="I85" s="29" t="n">
+      <c r="I85" s="26" t="n">
         <v>529148</v>
       </c>
-      <c r="J85" s="18">
+      <c r="J85" s="16">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="18">
+      <c r="K85" s="16">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="18">
+      <c r="L85" s="16">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="18">
+      <c r="M85" s="16">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="18">
+      <c r="N85" s="16">
         <f>N42</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="18" t="inlineStr">
+      <c r="B86" s="16" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="29" t="n">
+      <c r="E86" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="29" t="n">
+      <c r="F86" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="29" t="n">
+      <c r="G86" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="29" t="n">
+      <c r="H86" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="29" t="n">
+      <c r="I86" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="18">
+      <c r="J86" s="16">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="18">
+      <c r="K86" s="16">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="18">
+      <c r="L86" s="16">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="18">
+      <c r="M86" s="16">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="18">
+      <c r="N86" s="16">
         <f>N43</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="18" t="inlineStr">
+      <c r="B87" s="16" t="inlineStr">
         <is>
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="29" t="n">
+      <c r="E87" s="26" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="29" t="n">
+      <c r="F87" s="26" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="29" t="n">
+      <c r="G87" s="26" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="29" t="n">
+      <c r="H87" s="26" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="29" t="n">
+      <c r="I87" s="26" t="n">
         <v>32315</v>
       </c>
-      <c r="J87" s="18">
+      <c r="J87" s="16">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="18">
+      <c r="K87" s="16">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="18">
+      <c r="L87" s="16">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="18">
+      <c r="M87" s="16">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="18">
+      <c r="N87" s="16">
         <f>N48</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="53" t="inlineStr">
+      <c r="B88" s="50" t="inlineStr">
         <is>
           <t>Net Working Capital (NWC)</t>
         </is>
       </c>
-      <c r="C88" s="53" t="n"/>
-      <c r="D88" s="54" t="n"/>
-      <c r="E88" s="56">
+      <c r="C88" s="50" t="n"/>
+      <c r="D88" s="51" t="n"/>
+      <c r="E88" s="53">
         <f>E85+E86-E87</f>
         <v/>
       </c>
-      <c r="F88" s="56">
+      <c r="F88" s="53">
         <f>F85+F86-F87</f>
         <v/>
       </c>
-      <c r="G88" s="56">
+      <c r="G88" s="53">
         <f>G85+G86-G87</f>
         <v/>
       </c>
-      <c r="H88" s="56">
+      <c r="H88" s="53">
         <f>H85+H86-H87</f>
         <v/>
       </c>
-      <c r="I88" s="56">
+      <c r="I88" s="53">
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="56">
+      <c r="J88" s="53">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="56">
+      <c r="K88" s="53">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="56">
+      <c r="L88" s="53">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="56">
+      <c r="M88" s="53">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="56">
+      <c r="N88" s="53">
         <f>N85+N86-N87</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="18" t="inlineStr">
+      <c r="B89" s="16" t="inlineStr">
         <is>
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E89" s="28">
+      <c r="E89" s="25">
         <f>E88-D88</f>
         <v/>
       </c>
-      <c r="F89" s="28">
+      <c r="F89" s="25">
         <f>F88-E88</f>
         <v/>
       </c>
-      <c r="G89" s="28">
+      <c r="G89" s="25">
         <f>G88-F88</f>
         <v/>
       </c>
-      <c r="H89" s="28">
+      <c r="H89" s="25">
         <f>H88-G88</f>
         <v/>
       </c>
-      <c r="I89" s="28">
+      <c r="I89" s="25">
         <f>I88-H88</f>
         <v/>
       </c>
-      <c r="J89" s="28">
+      <c r="J89" s="25">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K89" s="28">
+      <c r="K89" s="25">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L89" s="28">
+      <c r="L89" s="25">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M89" s="28">
+      <c r="M89" s="25">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N89" s="28">
+      <c r="N89" s="25">
         <f>N88-M88</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="E90" s="33" t="n"/>
-      <c r="F90" s="33" t="n"/>
-      <c r="G90" s="33" t="n"/>
-      <c r="H90" s="33" t="n"/>
-      <c r="I90" s="33" t="n"/>
+      <c r="E90" s="30" t="n"/>
+      <c r="F90" s="30" t="n"/>
+      <c r="G90" s="30" t="n"/>
+      <c r="H90" s="30" t="n"/>
+      <c r="I90" s="30" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="21" t="inlineStr">
+      <c r="B91" s="19" t="inlineStr">
         <is>
           <t>Depreciation Schedule</t>
         </is>
       </c>
-      <c r="E91" s="33" t="n"/>
-      <c r="F91" s="33" t="n"/>
-      <c r="G91" s="33" t="n"/>
-      <c r="H91" s="33" t="n"/>
-      <c r="I91" s="33" t="n"/>
+      <c r="E91" s="30" t="n"/>
+      <c r="F91" s="30" t="n"/>
+      <c r="G91" s="30" t="n"/>
+      <c r="H91" s="30" t="n"/>
+      <c r="I91" s="30" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="18" t="inlineStr">
+      <c r="B92" s="16" t="inlineStr">
         <is>
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="29" t="n">
+      <c r="E92" s="26" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="29" t="n">
+      <c r="F92" s="26" t="n">
         <v>27913</v>
       </c>
-      <c r="G92" s="29" t="n">
+      <c r="G92" s="26" t="n">
         <v>17580</v>
       </c>
-      <c r="H92" s="29" t="n">
+      <c r="H92" s="26" t="n">
         <v>10966</v>
       </c>
-      <c r="I92" s="29" t="n">
+      <c r="I92" s="26" t="n">
         <v>38465</v>
       </c>
-      <c r="J92" s="18">
+      <c r="J92" s="16">
         <f>I95</f>
         <v/>
       </c>
-      <c r="K92" s="18">
+      <c r="K92" s="16">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="18">
+      <c r="L92" s="16">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="18">
+      <c r="M92" s="16">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="18">
+      <c r="N92" s="16">
         <f>M95</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="18" t="inlineStr">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="29" t="n">
+      <c r="E93" s="26" t="n">
         <v>7086</v>
       </c>
-      <c r="F93" s="29" t="n">
+      <c r="F93" s="26" t="n">
         <v>10132</v>
       </c>
-      <c r="G93" s="29" t="n">
+      <c r="G93" s="26" t="n">
         <v>8024</v>
       </c>
-      <c r="H93" s="29" t="n">
+      <c r="H93" s="26" t="n">
         <v>41326</v>
       </c>
-      <c r="I93" s="29" t="n">
+      <c r="I93" s="26" t="n">
         <v>44200</v>
       </c>
-      <c r="J93" s="18">
+      <c r="J93" s="16">
         <f>+J18</f>
         <v/>
       </c>
-      <c r="K93" s="18">
+      <c r="K93" s="16">
         <f>+K18</f>
         <v/>
       </c>
-      <c r="L93" s="18">
+      <c r="L93" s="16">
         <f>+L18</f>
         <v/>
       </c>
-      <c r="M93" s="18">
+      <c r="M93" s="16">
         <f>+M18</f>
         <v/>
       </c>
-      <c r="N93" s="18">
+      <c r="N93" s="16">
         <f>+N18</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="18" t="inlineStr">
+      <c r="B94" s="16" t="inlineStr">
         <is>
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="29" t="n">
+      <c r="E94" s="26" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="29" t="n">
+      <c r="F94" s="26" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="29" t="n">
+      <c r="G94" s="26" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="29" t="n">
+      <c r="H94" s="26" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="29" t="n">
+      <c r="I94" s="26" t="n">
         <v>14952</v>
       </c>
-      <c r="J94" s="34">
+      <c r="J94" s="31">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K94" s="34">
+      <c r="K94" s="31">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L94" s="34">
+      <c r="L94" s="31">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M94" s="34">
+      <c r="M94" s="31">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N94" s="34">
+      <c r="N94" s="31">
         <f>N92*N11</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="53" t="inlineStr">
+      <c r="B95" s="50" t="inlineStr">
         <is>
           <t>PPE Closing</t>
         </is>
       </c>
-      <c r="C95" s="53" t="n"/>
-      <c r="D95" s="54" t="n"/>
-      <c r="E95" s="56">
+      <c r="C95" s="50" t="n"/>
+      <c r="D95" s="51" t="n"/>
+      <c r="E95" s="53">
         <f>E92+E93-E94</f>
         <v/>
       </c>
-      <c r="F95" s="56">
+      <c r="F95" s="53">
         <f>F92+F93-F94</f>
         <v/>
       </c>
-      <c r="G95" s="56">
+      <c r="G95" s="53">
         <f>G92+G93-G94</f>
         <v/>
       </c>
-      <c r="H95" s="56">
+      <c r="H95" s="53">
         <f>H92+H93-H94</f>
         <v/>
       </c>
-      <c r="I95" s="56">
+      <c r="I95" s="53">
         <f>I92+I93-I94</f>
         <v/>
       </c>
-      <c r="J95" s="56">
+      <c r="J95" s="53">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="56">
+      <c r="K95" s="53">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="56">
+      <c r="L95" s="53">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="56">
+      <c r="M95" s="53">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="56">
+      <c r="N95" s="53">
         <f>N92+N93-N94</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="E96" s="33" t="n"/>
-      <c r="F96" s="33" t="n"/>
-      <c r="G96" s="33" t="n"/>
-      <c r="H96" s="33" t="n"/>
-      <c r="I96" s="33" t="n"/>
-      <c r="J96" s="33" t="n"/>
-      <c r="K96" s="33" t="n"/>
-      <c r="L96" s="33" t="n"/>
-      <c r="M96" s="33" t="n"/>
-      <c r="N96" s="33" t="n"/>
+      <c r="E96" s="30" t="n"/>
+      <c r="F96" s="30" t="n"/>
+      <c r="G96" s="30" t="n"/>
+      <c r="H96" s="30" t="n"/>
+      <c r="I96" s="30" t="n"/>
+      <c r="J96" s="30" t="n"/>
+      <c r="K96" s="30" t="n"/>
+      <c r="L96" s="30" t="n"/>
+      <c r="M96" s="30" t="n"/>
+      <c r="N96" s="30" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="21" t="inlineStr">
+      <c r="B97" s="19" t="inlineStr">
         <is>
           <t>Debt &amp; Interest Schedule</t>
         </is>
       </c>
-      <c r="E97" s="33" t="n"/>
-      <c r="F97" s="33" t="n"/>
-      <c r="G97" s="33" t="n"/>
-      <c r="H97" s="33" t="n"/>
-      <c r="I97" s="33" t="n"/>
+      <c r="E97" s="30" t="n"/>
+      <c r="F97" s="30" t="n"/>
+      <c r="G97" s="30" t="n"/>
+      <c r="H97" s="30" t="n"/>
+      <c r="I97" s="30" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="18" t="inlineStr">
+      <c r="B98" s="16" t="inlineStr">
         <is>
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="29" t="n">
+      <c r="E98" s="26" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="29" t="n">
+      <c r="F98" s="26" t="n">
         <v>1009018</v>
       </c>
-      <c r="G98" s="29" t="n">
+      <c r="G98" s="26" t="n">
         <v>1823669</v>
       </c>
-      <c r="H98" s="29" t="n">
+      <c r="H98" s="26" t="n">
         <v>1811658</v>
       </c>
-      <c r="I98" s="29" t="n">
+      <c r="I98" s="26" t="n">
         <v>2209021</v>
       </c>
-      <c r="J98" s="18">
+      <c r="J98" s="16">
         <f>I100</f>
         <v/>
       </c>
-      <c r="K98" s="18">
+      <c r="K98" s="16">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="18">
+      <c r="L98" s="16">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="18">
+      <c r="M98" s="16">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="18">
+      <c r="N98" s="16">
         <f>M100</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="18" t="inlineStr">
+      <c r="B99" s="16" t="inlineStr">
         <is>
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="29" t="n">
+      <c r="E99" s="26" t="n">
         <v>269583</v>
       </c>
-      <c r="F99" s="29" t="n">
+      <c r="F99" s="26" t="n">
         <v>814651</v>
       </c>
-      <c r="G99" s="29" t="n">
+      <c r="G99" s="26" t="n">
         <v>-12011</v>
       </c>
-      <c r="H99" s="29" t="n">
+      <c r="H99" s="26" t="n">
         <v>397363</v>
       </c>
-      <c r="I99" s="29" t="n">
+      <c r="I99" s="26" t="n">
         <v>846670</v>
       </c>
-      <c r="J99" s="28">
+      <c r="J99" s="25">
         <f>+J19</f>
         <v/>
       </c>
-      <c r="K99" s="28">
+      <c r="K99" s="25">
         <f>+K19</f>
         <v/>
       </c>
-      <c r="L99" s="28">
+      <c r="L99" s="25">
         <f>+L19</f>
         <v/>
       </c>
-      <c r="M99" s="28">
+      <c r="M99" s="25">
         <f>+M19</f>
         <v/>
       </c>
-      <c r="N99" s="28">
+      <c r="N99" s="25">
         <f>+N19</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="53" t="inlineStr">
+      <c r="B100" s="50" t="inlineStr">
         <is>
           <t>Debt Closing</t>
         </is>
       </c>
-      <c r="C100" s="53" t="n"/>
-      <c r="D100" s="54" t="n"/>
-      <c r="E100" s="56">
+      <c r="C100" s="50" t="n"/>
+      <c r="D100" s="51" t="n"/>
+      <c r="E100" s="53">
         <f>SUM(E98:E99)</f>
         <v/>
       </c>
-      <c r="F100" s="56">
+      <c r="F100" s="53">
         <f>SUM(F98:F99)</f>
         <v/>
       </c>
-      <c r="G100" s="56">
+      <c r="G100" s="53">
         <f>SUM(G98:G99)</f>
         <v/>
       </c>
-      <c r="H100" s="56">
+      <c r="H100" s="53">
         <f>SUM(H98:H99)</f>
         <v/>
       </c>
-      <c r="I100" s="56">
+      <c r="I100" s="53">
         <f>SUM(I98:I99)</f>
         <v/>
       </c>
-      <c r="J100" s="56">
+      <c r="J100" s="53">
         <f>SUM(J98:J99)</f>
         <v/>
       </c>
-      <c r="K100" s="56">
+      <c r="K100" s="53">
         <f>SUM(K98:K99)</f>
         <v/>
       </c>
-      <c r="L100" s="56">
+      <c r="L100" s="53">
         <f>SUM(L98:L99)</f>
         <v/>
       </c>
-      <c r="M100" s="56">
+      <c r="M100" s="53">
         <f>SUM(M98:M99)</f>
         <v/>
       </c>
-      <c r="N100" s="56">
+      <c r="N100" s="53">
         <f>SUM(N98:N99)</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="18" t="inlineStr">
+      <c r="B101" s="16" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="29" t="n">
+      <c r="E101" s="26" t="n">
         <v>40092</v>
       </c>
-      <c r="F101" s="29" t="n">
+      <c r="F101" s="26" t="n">
         <v>68967</v>
       </c>
-      <c r="G101" s="29" t="n">
+      <c r="G101" s="26" t="n">
         <v>95546</v>
       </c>
-      <c r="H101" s="29" t="n">
+      <c r="H101" s="26" t="n">
         <v>105638</v>
       </c>
-      <c r="I101" s="29" t="n">
+      <c r="I101" s="26" t="n">
         <v>133647</v>
       </c>
-      <c r="J101" s="18">
+      <c r="J101" s="16">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="18">
+      <c r="K101" s="16">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="18">
+      <c r="L101" s="16">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="18">
+      <c r="M101" s="16">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="18">
+      <c r="N101" s="16">
         <f>N98*N12</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="E102" s="33" t="n"/>
-      <c r="F102" s="33" t="n"/>
-      <c r="G102" s="27" t="n"/>
-      <c r="H102" s="33" t="n"/>
-      <c r="I102" s="33" t="n"/>
+      <c r="E102" s="30" t="n"/>
+      <c r="F102" s="30" t="n"/>
+      <c r="G102" s="54" t="n"/>
+      <c r="H102" s="30" t="n"/>
+      <c r="I102" s="30" t="n"/>
     </row>
     <row r="103">
-      <c r="E103" s="33" t="n"/>
-      <c r="F103" s="33" t="n"/>
-      <c r="G103" s="33" t="n"/>
-      <c r="H103" s="33" t="n"/>
-      <c r="I103" s="33" t="n"/>
+      <c r="E103" s="30" t="n"/>
+      <c r="F103" s="30" t="n"/>
+      <c r="G103" s="30" t="n"/>
+      <c r="H103" s="30" t="n"/>
+      <c r="I103" s="30" t="n"/>
     </row>
     <row r="104">
-      <c r="E104" s="33" t="n"/>
-      <c r="F104" s="33" t="n"/>
-      <c r="G104" s="33" t="n"/>
-      <c r="H104" s="33" t="n"/>
-      <c r="I104" s="33" t="n"/>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="B105" s="20" t="inlineStr">
+      <c r="E104" s="30" t="n"/>
+      <c r="F104" s="30" t="n"/>
+      <c r="G104" s="30" t="n"/>
+      <c r="H104" s="30" t="n"/>
+      <c r="I104" s="30" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="18" t="inlineStr">
         <is>
           <t>Charts and Graphs</t>
         </is>
       </c>
-      <c r="C105" s="20" t="n"/>
-      <c r="D105" s="20" t="n"/>
-      <c r="E105" s="20" t="n"/>
-      <c r="F105" s="20" t="n"/>
-      <c r="G105" s="20" t="n"/>
-      <c r="H105" s="20" t="n"/>
-      <c r="I105" s="20" t="n"/>
-      <c r="J105" s="20" t="n"/>
-      <c r="K105" s="20" t="n"/>
-      <c r="L105" s="20" t="n"/>
-      <c r="M105" s="20" t="n"/>
-      <c r="N105" s="20" t="n"/>
-    </row>
+      <c r="C105" s="18" t="n"/>
+      <c r="D105" s="18" t="n"/>
+      <c r="E105" s="18" t="n"/>
+      <c r="F105" s="18" t="n"/>
+      <c r="G105" s="18" t="n"/>
+      <c r="H105" s="18" t="n"/>
+      <c r="I105" s="18" t="n"/>
+      <c r="J105" s="18" t="n"/>
+      <c r="K105" s="18" t="n"/>
+      <c r="L105" s="18" t="n"/>
+      <c r="M105" s="18" t="n"/>
+      <c r="N105" s="18" t="n"/>
+    </row>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
     <row r="118">
-      <c r="C118" s="57" t="n"/>
-      <c r="D118" s="57" t="n"/>
+      <c r="C118" s="55" t="n"/>
+      <c r="D118" s="55" t="n"/>
     </row>
     <row r="119">
-      <c r="B119" s="57" t="n"/>
-      <c r="C119" s="57" t="n"/>
-      <c r="D119" s="57" t="n"/>
-    </row>
+      <c r="B119" s="55" t="n"/>
+      <c r="C119" s="55" t="n"/>
+      <c r="D119" s="55" t="n"/>
+    </row>
+    <row r="120"/>
     <row r="121">
-      <c r="B121" s="18" t="inlineStr">
+      <c r="B121" s="16" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="E121" s="18">
+      <c r="E121" s="16">
         <f>E24</f>
         <v/>
       </c>
-      <c r="F121" s="18">
+      <c r="F121" s="16">
         <f>F24</f>
         <v/>
       </c>
-      <c r="G121" s="18">
+      <c r="G121" s="16">
         <f>G24</f>
         <v/>
       </c>
-      <c r="H121" s="18">
+      <c r="H121" s="16">
         <f>H24</f>
         <v/>
       </c>
-      <c r="I121" s="18">
+      <c r="I121" s="16">
         <f>I24</f>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="B122" s="18" t="inlineStr">
+      <c r="B122" s="16" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="E122" s="18">
+      <c r="E122" s="16">
         <f>E26</f>
         <v/>
       </c>
-      <c r="F122" s="18">
+      <c r="F122" s="16">
         <f>F26</f>
         <v/>
       </c>
-      <c r="G122" s="18">
+      <c r="G122" s="16">
         <f>G26</f>
         <v/>
       </c>
-      <c r="H122" s="18">
+      <c r="H122" s="16">
         <f>H26</f>
         <v/>
       </c>
-      <c r="I122" s="18">
+      <c r="I122" s="16">
         <f>I26</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="B123" s="18" t="inlineStr">
+      <c r="B123" s="16" t="inlineStr">
         <is>
           <t>Earning Before Tax</t>
         </is>
       </c>
-      <c r="E123" s="18">
+      <c r="E123" s="16">
         <f>E33</f>
         <v/>
       </c>
-      <c r="F123" s="18">
+      <c r="F123" s="16">
         <f>F33</f>
         <v/>
       </c>
-      <c r="G123" s="18">
+      <c r="G123" s="16">
         <f>G33</f>
         <v/>
       </c>
-      <c r="H123" s="18">
+      <c r="H123" s="16">
         <f>H33</f>
         <v/>
       </c>
-      <c r="I123" s="18">
+      <c r="I123" s="16">
         <f>I33</f>
         <v/>
       </c>
     </row>
+    <row r="124"/>
     <row r="125">
-      <c r="B125" s="18" t="inlineStr">
+      <c r="B125" s="16" t="inlineStr">
         <is>
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="E125" s="18">
+      <c r="E125" s="16">
         <f>E65</f>
         <v/>
       </c>
-      <c r="F125" s="18">
+      <c r="F125" s="16">
         <f>F65</f>
         <v/>
       </c>
-      <c r="G125" s="18">
+      <c r="G125" s="16">
         <f>G65</f>
         <v/>
       </c>
-      <c r="H125" s="18">
+      <c r="H125" s="16">
         <f>H65</f>
         <v/>
       </c>
-      <c r="I125" s="18">
+      <c r="I125" s="16">
         <f>I65</f>
         <v/>
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="18" t="inlineStr">
+      <c r="B126" s="16" t="inlineStr">
         <is>
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="E126" s="18">
+      <c r="E126" s="16">
         <f>-E69</f>
         <v/>
       </c>
-      <c r="F126" s="18">
+      <c r="F126" s="16">
         <f>-F69</f>
         <v/>
       </c>
-      <c r="G126" s="18">
+      <c r="G126" s="16">
         <f>-G69</f>
         <v/>
       </c>
-      <c r="H126" s="18">
+      <c r="H126" s="16">
         <f>-H69</f>
         <v/>
       </c>
-      <c r="I126" s="18">
+      <c r="I126" s="16">
         <f>-I69</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="18" t="inlineStr">
+      <c r="B127" s="16" t="inlineStr">
         <is>
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="E127" s="18">
+      <c r="E127" s="16">
         <f>E74</f>
         <v/>
       </c>
-      <c r="F127" s="18">
+      <c r="F127" s="16">
         <f>F74</f>
         <v/>
       </c>
-      <c r="G127" s="18">
+      <c r="G127" s="16">
         <f>G74</f>
         <v/>
       </c>
-      <c r="H127" s="18">
+      <c r="H127" s="16">
         <f>H74</f>
         <v/>
       </c>
-      <c r="I127" s="18">
+      <c r="I127" s="16">
         <f>I74</f>
         <v/>
       </c>
     </row>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
     <row r="131">
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>FICO joined model: historicals from 10-K; forecast drivers yellow. DCF sheet pulls EBIT/D&amp;A/Capex/ΔNWC from forecast columns J–N.</t>
+      <c r="B131" s="56" t="inlineStr">
+        <is>
+          <t>FIXED: forecast drivers now FICO-scale (COGS%~17.8%, SG&amp;A/R&amp;D from FY25, tax~18.8%, AR days~97, Inv days=0, Capex from 10-K). Years 2021–2030 hardcoded.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="B132" s="57" t="n"/>
-      <c r="C132" s="57" t="n"/>
-      <c r="D132" s="57" t="n"/>
+      <c r="B132" s="55" t="n"/>
+      <c r="C132" s="55" t="n"/>
+      <c r="D132" s="55" t="n"/>
     </row>
     <row r="133">
-      <c r="B133" s="57" t="n"/>
-      <c r="C133" s="57" t="n"/>
-      <c r="D133" s="57" t="n"/>
+      <c r="B133" s="55" t="n"/>
+      <c r="C133" s="55" t="n"/>
+      <c r="D133" s="55" t="n"/>
     </row>
     <row r="134">
-      <c r="B134" s="57" t="n"/>
-      <c r="C134" s="57" t="n"/>
-      <c r="D134" s="57" t="n"/>
+      <c r="B134" s="55" t="n"/>
+      <c r="C134" s="55" t="n"/>
+      <c r="D134" s="55" t="n"/>
     </row>
     <row r="135">
-      <c r="B135" s="57" t="n"/>
-      <c r="C135" s="57" t="n"/>
-      <c r="D135" s="57" t="n"/>
+      <c r="B135" s="55" t="n"/>
+      <c r="C135" s="55" t="n"/>
+      <c r="D135" s="55" t="n"/>
     </row>
     <row r="136">
-      <c r="B136" s="57" t="n"/>
-      <c r="C136" s="57" t="n"/>
-      <c r="D136" s="57" t="n"/>
+      <c r="B136" s="55" t="n"/>
+      <c r="C136" s="55" t="n"/>
+      <c r="D136" s="55" t="n"/>
     </row>
     <row r="137">
-      <c r="B137" s="57" t="inlineStr">
+      <c r="B137" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Corporate Finance Institute® </t>
         </is>
       </c>
-      <c r="C137" s="58" t="n"/>
-      <c r="D137" s="58" t="n"/>
-    </row>
-    <row r="138" ht="16.2" customHeight="1">
-      <c r="B138" s="59" t="inlineStr">
+      <c r="C137" s="57" t="n"/>
+      <c r="D137" s="57" t="n"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="58" t="inlineStr">
         <is>
           <t>https://corporatefinanceinstitute.com/</t>
         </is>
       </c>
-      <c r="C138" s="60" t="n"/>
-      <c r="D138" s="60" t="n"/>
+      <c r="C138" s="59" t="n"/>
+      <c r="D138" s="59" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5566,65 +5125,65 @@
     <col width="3.54296875" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="12.453125" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="61" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>© Corporate Finance Institute®. All rights reserved.</t>
         </is>
       </c>
-      <c r="B1" s="62" t="n"/>
-      <c r="C1" s="62" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="61" t="n"/>
-      <c r="I1" s="62" t="n"/>
-      <c r="J1" s="62" t="n"/>
-      <c r="K1" s="63" t="n"/>
-      <c r="L1" s="63" t="n"/>
-      <c r="M1" s="63" t="n"/>
-      <c r="N1" s="63" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="62" t="n"/>
-      <c r="B2" s="64" t="inlineStr">
-        <is>
-          <t>FICO DCF (joined — values filled)</t>
-        </is>
-      </c>
-      <c r="C2" s="65" t="n"/>
-      <c r="D2" s="101" t="inlineStr">
-        <is>
-          <t>All DCF lines filled — open 10K_Sources for SEC links</t>
-        </is>
-      </c>
-      <c r="E2" s="65" t="n"/>
-      <c r="F2" s="63" t="n"/>
-      <c r="G2" s="63" t="n"/>
-      <c r="H2" s="62" t="n"/>
-      <c r="I2" s="64" t="n"/>
-      <c r="J2" s="65" t="n"/>
-      <c r="K2" s="65" t="n"/>
-      <c r="L2" s="65" t="n"/>
-      <c r="M2" s="63" t="n"/>
-      <c r="N2" s="63" t="n"/>
-    </row>
-    <row r="3" ht="16" customHeight="1">
+      <c r="B1" s="61" t="n"/>
+      <c r="C1" s="61" t="n"/>
+      <c r="D1" s="62" t="n"/>
+      <c r="E1" s="62" t="n"/>
+      <c r="F1" s="62" t="n"/>
+      <c r="G1" s="62" t="n"/>
+      <c r="H1" s="60" t="n"/>
+      <c r="I1" s="61" t="n"/>
+      <c r="J1" s="61" t="n"/>
+      <c r="K1" s="62" t="n"/>
+      <c r="L1" s="62" t="n"/>
+      <c r="M1" s="62" t="n"/>
+      <c r="N1" s="62" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="61" t="n"/>
+      <c r="B2" s="63" t="inlineStr">
+        <is>
+          <t>FICO DCF (joined, corrected)</t>
+        </is>
+      </c>
+      <c r="C2" s="64" t="n"/>
+      <c r="D2" s="65" t="inlineStr">
+        <is>
+          <t>FIXED: EBIT anchored to FY25 OpInc; years 2026–2030; FY25 base in row 16</t>
+        </is>
+      </c>
+      <c r="E2" s="64" t="n"/>
+      <c r="F2" s="62" t="n"/>
+      <c r="G2" s="62" t="n"/>
+      <c r="H2" s="61" t="n"/>
+      <c r="I2" s="63" t="n"/>
+      <c r="J2" s="64" t="n"/>
+      <c r="K2" s="64" t="n"/>
+      <c r="L2" s="64" t="n"/>
+      <c r="M2" s="62" t="n"/>
+      <c r="N2" s="62" t="n"/>
+    </row>
+    <row r="3">
       <c r="A3" s="66" t="n"/>
       <c r="B3" s="67" t="n"/>
       <c r="C3" s="66" t="n"/>
@@ -5641,7 +5200,7 @@
       <c r="N3" s="66" t="n"/>
       <c r="O3" s="66" t="n"/>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4">
       <c r="A4" s="66" t="n"/>
       <c r="B4" s="70" t="inlineStr">
         <is>
@@ -5662,7 +5221,7 @@
       <c r="N4" s="66" t="n"/>
       <c r="O4" s="66" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5">
       <c r="A5" s="66" t="n"/>
       <c r="B5" s="72" t="inlineStr">
         <is>
@@ -5670,7 +5229,7 @@
         </is>
       </c>
       <c r="C5" s="69" t="n"/>
-      <c r="D5" s="102" t="n">
+      <c r="D5" s="73" t="n">
         <v>0.1877</v>
       </c>
       <c r="E5" s="69" t="n"/>
@@ -5685,7 +5244,7 @@
       <c r="N5" s="66" t="n"/>
       <c r="O5" s="66" t="n"/>
     </row>
-    <row r="6" ht="16" customHeight="1">
+    <row r="6">
       <c r="A6" s="66" t="n"/>
       <c r="B6" s="72" t="inlineStr">
         <is>
@@ -5693,7 +5252,7 @@
         </is>
       </c>
       <c r="C6" s="66" t="n"/>
-      <c r="D6" s="103" t="n">
+      <c r="D6" s="74" t="n">
         <v>0.096</v>
       </c>
       <c r="E6" s="66" t="n"/>
@@ -5708,7 +5267,7 @@
       <c r="N6" s="66" t="n"/>
       <c r="O6" s="66" t="n"/>
     </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7">
       <c r="A7" s="66" t="n"/>
       <c r="B7" s="66" t="inlineStr">
         <is>
@@ -5716,7 +5275,7 @@
         </is>
       </c>
       <c r="C7" s="66" t="n"/>
-      <c r="D7" s="103" t="n">
+      <c r="D7" s="74" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" s="66" t="n"/>
@@ -5731,7 +5290,7 @@
       <c r="N7" s="66" t="n"/>
       <c r="O7" s="66" t="n"/>
     </row>
-    <row r="8" ht="16" customHeight="1">
+    <row r="8">
       <c r="A8" s="66" t="n"/>
       <c r="B8" s="66" t="inlineStr">
         <is>
@@ -5739,8 +5298,8 @@
         </is>
       </c>
       <c r="C8" s="66" t="n"/>
-      <c r="D8" s="104" t="n">
-        <v>25</v>
+      <c r="D8" s="75" t="n">
+        <v>22</v>
       </c>
       <c r="E8" s="66" t="n"/>
       <c r="F8" s="66" t="n"/>
@@ -5754,7 +5313,7 @@
       <c r="N8" s="66" t="n"/>
       <c r="O8" s="66" t="n"/>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9">
       <c r="A9" s="66" t="n"/>
       <c r="B9" s="66" t="inlineStr">
         <is>
@@ -5762,7 +5321,7 @@
         </is>
       </c>
       <c r="C9" s="66" t="n"/>
-      <c r="D9" s="105" t="n">
+      <c r="D9" s="76" t="n">
         <v>45930</v>
       </c>
       <c r="E9" s="66" t="n"/>
@@ -5777,7 +5336,7 @@
       <c r="N9" s="66" t="n"/>
       <c r="O9" s="66" t="n"/>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10">
       <c r="A10" s="66" t="n"/>
       <c r="B10" s="66" t="inlineStr">
         <is>
@@ -5785,7 +5344,7 @@
         </is>
       </c>
       <c r="C10" s="66" t="n"/>
-      <c r="D10" s="105" t="n">
+      <c r="D10" s="76" t="n">
         <v>45930</v>
       </c>
       <c r="E10" s="66" t="n"/>
@@ -5800,7 +5359,7 @@
       <c r="N10" s="66" t="n"/>
       <c r="O10" s="66" t="n"/>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11">
       <c r="A11" s="66" t="n"/>
       <c r="B11" s="66" t="inlineStr">
         <is>
@@ -5808,7 +5367,7 @@
         </is>
       </c>
       <c r="C11" s="66" t="n"/>
-      <c r="D11" s="106" t="n">
+      <c r="D11" s="77" t="n">
         <v>1046.23</v>
       </c>
       <c r="E11" s="66" t="n"/>
@@ -5823,7 +5382,7 @@
       <c r="N11" s="66" t="n"/>
       <c r="O11" s="66" t="n"/>
     </row>
-    <row r="12" ht="16" customHeight="1">
+    <row r="12">
       <c r="A12" s="66" t="n"/>
       <c r="B12" s="66" t="inlineStr">
         <is>
@@ -5831,7 +5390,7 @@
         </is>
       </c>
       <c r="C12" s="66" t="n"/>
-      <c r="D12" s="107" t="n">
+      <c r="D12" s="78" t="n">
         <v>21597.635</v>
       </c>
       <c r="E12" s="66" t="n"/>
@@ -5846,7 +5405,7 @@
       <c r="N12" s="66" t="n"/>
       <c r="O12" s="66" t="n"/>
     </row>
-    <row r="13" ht="16" customHeight="1">
+    <row r="13">
       <c r="A13" s="66" t="n"/>
       <c r="B13" s="66" t="inlineStr">
         <is>
@@ -5854,7 +5413,7 @@
         </is>
       </c>
       <c r="C13" s="66" t="n"/>
-      <c r="D13" s="108" t="n">
+      <c r="D13" s="79" t="n">
         <v>5582389</v>
       </c>
       <c r="E13" s="66" t="n"/>
@@ -5869,7 +5428,7 @@
       <c r="N13" s="66" t="n"/>
       <c r="O13" s="66" t="n"/>
     </row>
-    <row r="14" ht="16" customHeight="1">
+    <row r="14">
       <c r="A14" s="66" t="n"/>
       <c r="B14" s="66" t="inlineStr">
         <is>
@@ -5877,7 +5436,7 @@
         </is>
       </c>
       <c r="C14" s="66" t="n"/>
-      <c r="D14" s="108" t="n">
+      <c r="D14" s="79" t="n">
         <v>304537</v>
       </c>
       <c r="E14" s="66" t="n"/>
@@ -5892,7 +5451,7 @@
       <c r="N14" s="66" t="n"/>
       <c r="O14" s="66" t="n"/>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15">
       <c r="A15" s="66" t="n"/>
       <c r="B15" s="66" t="inlineStr">
         <is>
@@ -5900,13 +5459,29 @@
         </is>
       </c>
       <c r="C15" s="66" t="n"/>
-      <c r="D15" s="109" t="n">
+      <c r="D15" s="80" t="n">
         <v>39407</v>
       </c>
-      <c r="E15" s="66" t="n"/>
-      <c r="F15" s="66" t="n"/>
-      <c r="G15" s="66" t="n"/>
-      <c r="H15" s="66" t="n"/>
+      <c r="E15" s="66" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="F15" s="66" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="G15" s="66" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="H15" s="66" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
       <c r="I15" s="66" t="n"/>
       <c r="J15" s="66" t="n"/>
       <c r="K15" s="66" t="n"/>
@@ -5915,11 +5490,31 @@
       <c r="N15" s="66" t="n"/>
       <c r="O15" s="66" t="n"/>
     </row>
-    <row r="16" ht="16" customHeight="1">
+    <row r="16">
       <c r="A16" s="66" t="n"/>
-      <c r="B16" s="66" t="n"/>
+      <c r="B16" s="66" t="inlineStr">
+        <is>
+          <t>FY2025 actuals (10-K base)</t>
+        </is>
+      </c>
       <c r="C16" s="66" t="n"/>
-      <c r="D16" s="79" t="n"/>
+      <c r="D16" s="81" t="inlineStr">
+        <is>
+          <t>EBIT/DA/Capex/Tax</t>
+        </is>
+      </c>
+      <c r="E16" s="82" t="n">
+        <v>924850</v>
+      </c>
+      <c r="F16" s="82" t="n">
+        <v>14952</v>
+      </c>
+      <c r="G16" s="82" t="n">
+        <v>39407</v>
+      </c>
+      <c r="H16" s="82" t="n">
+        <v>150649</v>
+      </c>
       <c r="J16" s="66" t="n"/>
       <c r="K16" s="66" t="n"/>
       <c r="L16" s="66" t="n"/>
@@ -5927,50 +5522,50 @@
       <c r="N16" s="66" t="n"/>
       <c r="O16" s="66" t="n"/>
     </row>
-    <row r="17" ht="16" customHeight="1">
+    <row r="17">
       <c r="A17" s="66" t="n"/>
-      <c r="B17" s="80" t="inlineStr">
+      <c r="B17" s="83" t="inlineStr">
         <is>
           <t>Discounted Cash Flow</t>
         </is>
       </c>
-      <c r="C17" s="81" t="n"/>
-      <c r="D17" s="82" t="inlineStr">
+      <c r="C17" s="84" t="n"/>
+      <c r="D17" s="85" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="110" t="n">
+      <c r="E17" s="86" t="n">
         <v>2026</v>
       </c>
-      <c r="F17" s="110" t="n">
+      <c r="F17" s="86" t="n">
         <v>2027</v>
       </c>
-      <c r="G17" s="110" t="n">
+      <c r="G17" s="86" t="n">
         <v>2028</v>
       </c>
-      <c r="H17" s="110" t="n">
+      <c r="H17" s="86" t="n">
         <v>2029</v>
       </c>
-      <c r="I17" s="110" t="n">
+      <c r="I17" s="86" t="n">
         <v>2030</v>
       </c>
-      <c r="J17" s="82" t="inlineStr">
+      <c r="J17" s="85" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
       </c>
       <c r="K17" s="66" t="n"/>
-      <c r="L17" s="80" t="inlineStr">
+      <c r="L17" s="83" t="inlineStr">
         <is>
           <t>Terminal Value</t>
         </is>
       </c>
-      <c r="M17" s="81" t="n"/>
-      <c r="N17" s="81" t="n"/>
+      <c r="M17" s="84" t="n"/>
+      <c r="N17" s="84" t="n"/>
       <c r="O17" s="66" t="n"/>
     </row>
-    <row r="18" ht="16" customHeight="1">
+    <row r="18">
       <c r="A18" s="66" t="n"/>
       <c r="B18" s="66" t="inlineStr">
         <is>
@@ -5978,25 +5573,25 @@
         </is>
       </c>
       <c r="C18" s="66" t="n"/>
-      <c r="D18" s="111" t="n">
+      <c r="D18" s="87" t="n">
         <v>45930</v>
       </c>
-      <c r="E18" s="112" t="n">
+      <c r="E18" s="87" t="n">
         <v>46295</v>
       </c>
-      <c r="F18" s="112" t="n">
+      <c r="F18" s="87" t="n">
         <v>46660</v>
       </c>
-      <c r="G18" s="112" t="n">
+      <c r="G18" s="87" t="n">
         <v>47026</v>
       </c>
-      <c r="H18" s="112" t="n">
+      <c r="H18" s="87" t="n">
         <v>47391</v>
       </c>
-      <c r="I18" s="112" t="n">
+      <c r="I18" s="87" t="n">
         <v>47756</v>
       </c>
-      <c r="J18" s="113" t="n">
+      <c r="J18" s="88" t="n">
         <v>47756</v>
       </c>
       <c r="K18" s="66" t="n"/>
@@ -6006,36 +5601,36 @@
         </is>
       </c>
       <c r="M18" s="66" t="n"/>
-      <c r="N18" s="114" t="n">
-        <v>23982690.1</v>
+      <c r="N18" s="89" t="n">
+        <v>18113172.1</v>
       </c>
       <c r="O18" s="66" t="n"/>
     </row>
-    <row r="19" ht="16" customHeight="1">
+    <row r="19">
       <c r="A19" s="66" t="n"/>
-      <c r="B19" s="86" t="inlineStr">
+      <c r="B19" s="90" t="inlineStr">
         <is>
           <t>Time Periods</t>
         </is>
       </c>
-      <c r="C19" s="86" t="n"/>
-      <c r="D19" s="83" t="n"/>
-      <c r="E19" s="110" t="n">
+      <c r="C19" s="90" t="n"/>
+      <c r="D19" s="91" t="n"/>
+      <c r="E19" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="110" t="n">
+      <c r="F19" s="93" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="110" t="n">
+      <c r="G19" s="93" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="110" t="n">
+      <c r="H19" s="93" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="110" t="n">
+      <c r="I19" s="93" t="n">
         <v>5</v>
       </c>
-      <c r="J19" s="83" t="n"/>
+      <c r="J19" s="91" t="n"/>
       <c r="K19" s="66" t="n"/>
       <c r="L19" s="66" t="inlineStr">
         <is>
@@ -6043,33 +5638,33 @@
         </is>
       </c>
       <c r="M19" s="66" t="n"/>
-      <c r="N19" s="114" t="n">
-        <v>48732457.5</v>
+      <c r="N19" s="89" t="n">
+        <v>34250977</v>
       </c>
       <c r="O19" s="66" t="n"/>
     </row>
-    <row r="20" ht="16" customHeight="1">
+    <row r="20">
       <c r="A20" s="66" t="n"/>
-      <c r="B20" s="86" t="inlineStr">
+      <c r="B20" s="90" t="inlineStr">
         <is>
           <t>Year Fraction</t>
         </is>
       </c>
       <c r="C20" s="66" t="n"/>
       <c r="D20" s="66" t="n"/>
-      <c r="E20" s="115" t="n">
+      <c r="E20" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="115" t="n">
+      <c r="F20" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="115" t="n">
+      <c r="G20" s="94" t="n">
         <v>1.0027</v>
       </c>
-      <c r="H20" s="115" t="n">
+      <c r="H20" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="115" t="n">
+      <c r="I20" s="94" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="66" t="n"/>
@@ -6080,34 +5675,34 @@
         </is>
       </c>
       <c r="M20" s="66" t="n"/>
-      <c r="N20" s="116" t="n">
-        <v>36357573.8</v>
+      <c r="N20" s="95" t="n">
+        <v>26182074.6</v>
       </c>
       <c r="O20" s="66" t="n"/>
     </row>
-    <row r="21" ht="16" customHeight="1">
+    <row r="21">
       <c r="A21" s="66" t="n"/>
       <c r="B21" s="66" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>EBIT (= Operating income path)</t>
         </is>
       </c>
       <c r="C21" s="66" t="n"/>
       <c r="D21" s="66" t="n"/>
-      <c r="E21" s="109" t="n">
-        <v>1048623.4</v>
-      </c>
-      <c r="F21" s="109" t="n">
-        <v>1284433.8</v>
-      </c>
-      <c r="G21" s="109" t="n">
-        <v>1505458.6</v>
-      </c>
-      <c r="H21" s="109" t="n">
-        <v>1717399.8</v>
-      </c>
-      <c r="I21" s="109" t="n">
-        <v>1922965.4</v>
+      <c r="E21" s="80" t="n">
+        <v>1031318.4</v>
+      </c>
+      <c r="F21" s="80" t="n">
+        <v>1149880.5</v>
+      </c>
+      <c r="G21" s="80" t="n">
+        <v>1270112.3</v>
+      </c>
+      <c r="H21" s="80" t="n">
+        <v>1398473.3</v>
+      </c>
+      <c r="I21" s="80" t="n">
+        <v>1533659.6</v>
       </c>
       <c r="J21" s="66" t="n"/>
       <c r="K21" s="66" t="n"/>
@@ -6116,7 +5711,7 @@
       <c r="N21" s="66" t="n"/>
       <c r="O21" s="66" t="n"/>
     </row>
-    <row r="22" ht="16" customHeight="1">
+    <row r="22">
       <c r="A22" s="66" t="n"/>
       <c r="B22" s="66" t="inlineStr">
         <is>
@@ -6125,20 +5720,20 @@
       </c>
       <c r="C22" s="66" t="n"/>
       <c r="D22" s="66" t="n"/>
-      <c r="E22" s="114" t="n">
-        <v>196829.1</v>
-      </c>
-      <c r="F22" s="114" t="n">
-        <v>241091.3</v>
-      </c>
-      <c r="G22" s="114" t="n">
-        <v>282578.2</v>
-      </c>
-      <c r="H22" s="114" t="n">
-        <v>322360</v>
-      </c>
-      <c r="I22" s="114" t="n">
-        <v>360945.2</v>
+      <c r="E22" s="89" t="n">
+        <v>193580.9</v>
+      </c>
+      <c r="F22" s="89" t="n">
+        <v>215835.3</v>
+      </c>
+      <c r="G22" s="89" t="n">
+        <v>238403.1</v>
+      </c>
+      <c r="H22" s="89" t="n">
+        <v>262496.8</v>
+      </c>
+      <c r="I22" s="89" t="n">
+        <v>287871.6</v>
       </c>
       <c r="J22" s="66" t="n"/>
       <c r="K22" s="66" t="n"/>
@@ -6147,7 +5742,7 @@
       <c r="N22" s="66" t="n"/>
       <c r="O22" s="66" t="n"/>
     </row>
-    <row r="23" ht="16" customHeight="1">
+    <row r="23">
       <c r="A23" s="66" t="n"/>
       <c r="B23" s="66" t="inlineStr">
         <is>
@@ -6156,20 +5751,20 @@
       </c>
       <c r="C23" s="66" t="n"/>
       <c r="D23" s="66" t="n"/>
-      <c r="E23" s="109" t="n">
-        <v>18156.7</v>
-      </c>
-      <c r="F23" s="109" t="n">
-        <v>20335.5</v>
-      </c>
-      <c r="G23" s="109" t="n">
-        <v>22369.1</v>
-      </c>
-      <c r="H23" s="109" t="n">
-        <v>24382.3</v>
-      </c>
-      <c r="I23" s="109" t="n">
-        <v>26332.9</v>
+      <c r="E23" s="80" t="n">
+        <v>16746.2</v>
+      </c>
+      <c r="F23" s="80" t="n">
+        <v>18420.9</v>
+      </c>
+      <c r="G23" s="80" t="n">
+        <v>20078.7</v>
+      </c>
+      <c r="H23" s="80" t="n">
+        <v>21685</v>
+      </c>
+      <c r="I23" s="80" t="n">
+        <v>23203</v>
       </c>
       <c r="J23" s="66" t="n"/>
       <c r="K23" s="66" t="n"/>
@@ -6178,29 +5773,29 @@
       <c r="N23" s="66" t="n"/>
       <c r="O23" s="66" t="n"/>
     </row>
-    <row r="24" ht="16" customHeight="1">
+    <row r="24">
       <c r="A24" s="66" t="n"/>
       <c r="B24" s="66" t="inlineStr">
         <is>
-          <t>Less: Capex</t>
+          <t>Less: Capex (grows w/ rev)</t>
         </is>
       </c>
       <c r="C24" s="66" t="n"/>
       <c r="D24" s="66" t="n"/>
-      <c r="E24" s="117" t="n">
-        <v>39407</v>
-      </c>
-      <c r="F24" s="117" t="n">
-        <v>39407</v>
-      </c>
-      <c r="G24" s="117" t="n">
-        <v>39407</v>
-      </c>
-      <c r="H24" s="117" t="n">
-        <v>39407</v>
-      </c>
-      <c r="I24" s="117" t="n">
-        <v>39407</v>
+      <c r="E24" s="96" t="n">
+        <v>42559.6</v>
+      </c>
+      <c r="F24" s="96" t="n">
+        <v>45964.3</v>
+      </c>
+      <c r="G24" s="96" t="n">
+        <v>49641.5</v>
+      </c>
+      <c r="H24" s="96" t="n">
+        <v>53612.8</v>
+      </c>
+      <c r="I24" s="96" t="n">
+        <v>57901.8</v>
       </c>
       <c r="J24" s="66" t="n"/>
       <c r="K24" s="66" t="n"/>
@@ -6209,7 +5804,7 @@
       <c r="N24" s="66" t="n"/>
       <c r="O24" s="66" t="n"/>
     </row>
-    <row r="25" ht="16" customHeight="1">
+    <row r="25">
       <c r="A25" s="66" t="n"/>
       <c r="B25" s="66" t="inlineStr">
         <is>
@@ -6218,20 +5813,20 @@
       </c>
       <c r="C25" s="66" t="n"/>
       <c r="D25" s="66" t="n"/>
-      <c r="E25" s="109" t="n">
-        <v>13936.1</v>
-      </c>
-      <c r="F25" s="109" t="n">
-        <v>13617.5</v>
-      </c>
-      <c r="G25" s="109" t="n">
-        <v>12709.7</v>
-      </c>
-      <c r="H25" s="109" t="n">
-        <v>12582.6</v>
-      </c>
-      <c r="I25" s="109" t="n">
-        <v>12191.2</v>
+      <c r="E25" s="80" t="n">
+        <v>59620</v>
+      </c>
+      <c r="F25" s="80" t="n">
+        <v>55645.3</v>
+      </c>
+      <c r="G25" s="80" t="n">
+        <v>55088.8</v>
+      </c>
+      <c r="H25" s="80" t="n">
+        <v>53375</v>
+      </c>
+      <c r="I25" s="80" t="n">
+        <v>50439.3</v>
       </c>
       <c r="J25" s="66" t="n"/>
       <c r="K25" s="66" t="n"/>
@@ -6240,7 +5835,7 @@
       <c r="N25" s="66" t="n"/>
       <c r="O25" s="66" t="n"/>
     </row>
-    <row r="26" ht="16" customHeight="1">
+    <row r="26">
       <c r="A26" s="66" t="n"/>
       <c r="B26" s="66" t="inlineStr">
         <is>
@@ -6249,20 +5844,20 @@
       </c>
       <c r="C26" s="66" t="n"/>
       <c r="D26" s="66" t="n"/>
-      <c r="E26" s="116" t="n">
-        <v>816607.9</v>
-      </c>
-      <c r="F26" s="116" t="n">
-        <v>1010653.5</v>
-      </c>
-      <c r="G26" s="116" t="n">
-        <v>1193132.8</v>
-      </c>
-      <c r="H26" s="116" t="n">
-        <v>1367432.5</v>
-      </c>
-      <c r="I26" s="116" t="n">
-        <v>1536754.9</v>
+      <c r="E26" s="95" t="n">
+        <v>752304.2</v>
+      </c>
+      <c r="F26" s="95" t="n">
+        <v>850856.4</v>
+      </c>
+      <c r="G26" s="95" t="n">
+        <v>947057.6</v>
+      </c>
+      <c r="H26" s="95" t="n">
+        <v>1050673.8</v>
+      </c>
+      <c r="I26" s="95" t="n">
+        <v>1160649.9</v>
       </c>
       <c r="J26" s="66" t="n"/>
       <c r="K26" s="66" t="n"/>
@@ -6271,7 +5866,7 @@
       <c r="N26" s="66" t="n"/>
       <c r="O26" s="66" t="n"/>
     </row>
-    <row r="27" ht="16" customHeight="1">
+    <row r="27">
       <c r="A27" s="66" t="n"/>
       <c r="B27" s="66" t="inlineStr">
         <is>
@@ -6279,7 +5874,7 @@
         </is>
       </c>
       <c r="C27" s="66" t="n"/>
-      <c r="D27" s="114" t="n">
+      <c r="D27" s="89" t="n">
         <v>-27873945.7</v>
       </c>
       <c r="E27" s="66" t="n"/>
@@ -6287,8 +5882,8 @@
       <c r="G27" s="66" t="n"/>
       <c r="H27" s="66" t="n"/>
       <c r="I27" s="66" t="n"/>
-      <c r="J27" s="114" t="n">
-        <v>36357573.8</v>
+      <c r="J27" s="89" t="n">
+        <v>26182074.6</v>
       </c>
       <c r="K27" s="66" t="n"/>
       <c r="L27" s="66" t="n"/>
@@ -6296,7 +5891,7 @@
       <c r="N27" s="66" t="n"/>
       <c r="O27" s="66" t="n"/>
     </row>
-    <row r="28" ht="16" customHeight="1">
+    <row r="28">
       <c r="A28" s="66" t="n"/>
       <c r="B28" s="66" t="inlineStr">
         <is>
@@ -6304,26 +5899,26 @@
         </is>
       </c>
       <c r="C28" s="66" t="n"/>
-      <c r="D28" s="116" t="n">
+      <c r="D28" s="95" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="116" t="n">
-        <v>816607.9</v>
-      </c>
-      <c r="F28" s="116" t="n">
-        <v>1010653.5</v>
-      </c>
-      <c r="G28" s="116" t="n">
-        <v>1196401.7</v>
-      </c>
-      <c r="H28" s="116" t="n">
-        <v>1367432.5</v>
-      </c>
-      <c r="I28" s="116" t="n">
-        <v>1536754.9</v>
-      </c>
-      <c r="J28" s="116" t="n">
-        <v>36357573.8</v>
+      <c r="E28" s="95" t="n">
+        <v>752304.2</v>
+      </c>
+      <c r="F28" s="95" t="n">
+        <v>850856.4</v>
+      </c>
+      <c r="G28" s="95" t="n">
+        <v>949652.3</v>
+      </c>
+      <c r="H28" s="95" t="n">
+        <v>1050673.8</v>
+      </c>
+      <c r="I28" s="95" t="n">
+        <v>1160649.9</v>
+      </c>
+      <c r="J28" s="95" t="n">
+        <v>26182074.6</v>
       </c>
       <c r="K28" s="66" t="n"/>
       <c r="L28" s="66" t="n"/>
@@ -6331,7 +5926,7 @@
       <c r="N28" s="66" t="n"/>
       <c r="O28" s="66" t="n"/>
     </row>
-    <row r="29" ht="16" customHeight="1">
+    <row r="29">
       <c r="A29" s="66" t="n"/>
       <c r="B29" s="66" t="inlineStr">
         <is>
@@ -6339,26 +5934,26 @@
         </is>
       </c>
       <c r="C29" s="66" t="n"/>
-      <c r="D29" s="114" t="n">
+      <c r="D29" s="89" t="n">
         <v>-27873945.7</v>
       </c>
-      <c r="E29" s="114" t="n">
-        <v>816607.9</v>
-      </c>
-      <c r="F29" s="114" t="n">
-        <v>1010653.5</v>
-      </c>
-      <c r="G29" s="114" t="n">
-        <v>1196401.7</v>
-      </c>
-      <c r="H29" s="114" t="n">
-        <v>1367432.5</v>
-      </c>
-      <c r="I29" s="114" t="n">
-        <v>1536754.9</v>
-      </c>
-      <c r="J29" s="114" t="n">
-        <v>36357573.8</v>
+      <c r="E29" s="89" t="n">
+        <v>752304.2</v>
+      </c>
+      <c r="F29" s="89" t="n">
+        <v>850856.4</v>
+      </c>
+      <c r="G29" s="89" t="n">
+        <v>949652.3</v>
+      </c>
+      <c r="H29" s="89" t="n">
+        <v>1050673.8</v>
+      </c>
+      <c r="I29" s="89" t="n">
+        <v>1160649.9</v>
+      </c>
+      <c r="J29" s="89" t="n">
+        <v>26182074.6</v>
       </c>
       <c r="K29" s="66" t="n"/>
       <c r="L29" s="66" t="n"/>
@@ -6366,7 +5961,7 @@
       <c r="N29" s="66" t="n"/>
       <c r="O29" s="66" t="n"/>
     </row>
-    <row r="30" ht="16" customHeight="1">
+    <row r="30">
       <c r="A30" s="66" t="n"/>
       <c r="B30" s="66" t="n"/>
       <c r="C30" s="66" t="n"/>
@@ -6381,34 +5976,34 @@
       <c r="N30" s="66" t="n"/>
       <c r="O30" s="66" t="n"/>
     </row>
-    <row r="31" ht="16" customHeight="1">
+    <row r="31">
       <c r="A31" s="66" t="n"/>
-      <c r="B31" s="80" t="inlineStr">
+      <c r="B31" s="83" t="inlineStr">
         <is>
           <t>Intrinsic Value</t>
         </is>
       </c>
-      <c r="C31" s="81" t="n"/>
-      <c r="D31" s="81" t="n"/>
+      <c r="C31" s="84" t="n"/>
+      <c r="D31" s="84" t="n"/>
       <c r="E31" s="66" t="n"/>
-      <c r="G31" s="80" t="inlineStr">
+      <c r="G31" s="83" t="inlineStr">
         <is>
           <t>Market Value</t>
         </is>
       </c>
-      <c r="H31" s="81" t="n"/>
-      <c r="I31" s="81" t="n"/>
+      <c r="H31" s="84" t="n"/>
+      <c r="I31" s="84" t="n"/>
       <c r="J31" s="66" t="n"/>
-      <c r="L31" s="80" t="inlineStr">
+      <c r="L31" s="83" t="inlineStr">
         <is>
           <t>Rate of Return</t>
         </is>
       </c>
-      <c r="M31" s="81" t="n"/>
-      <c r="N31" s="81" t="n"/>
+      <c r="M31" s="84" t="n"/>
+      <c r="N31" s="84" t="n"/>
       <c r="O31" s="66" t="n"/>
     </row>
-    <row r="32" ht="16" customHeight="1">
+    <row r="32">
       <c r="A32" s="66" t="n"/>
       <c r="B32" s="66" t="inlineStr">
         <is>
@@ -6416,8 +6011,8 @@
         </is>
       </c>
       <c r="C32" s="66" t="n"/>
-      <c r="D32" s="114" t="n">
-        <v>27395820.3</v>
+      <c r="D32" s="89" t="n">
+        <v>20127310.6</v>
       </c>
       <c r="E32" s="66" t="n"/>
       <c r="G32" s="66" t="inlineStr">
@@ -6426,7 +6021,7 @@
         </is>
       </c>
       <c r="H32" s="66" t="n"/>
-      <c r="I32" s="114" t="n">
+      <c r="I32" s="89" t="n">
         <v>22596093.7</v>
       </c>
       <c r="J32" s="66" t="n"/>
@@ -6436,12 +6031,12 @@
         </is>
       </c>
       <c r="M32" s="66" t="n"/>
-      <c r="N32" s="118" t="n">
-        <v>-0.0212</v>
+      <c r="N32" s="97" t="n">
+        <v>-0.3428</v>
       </c>
       <c r="O32" s="66" t="n"/>
     </row>
-    <row r="33" ht="16" customHeight="1">
+    <row r="33">
       <c r="A33" s="66" t="n"/>
       <c r="B33" s="66" t="inlineStr">
         <is>
@@ -6449,7 +6044,7 @@
         </is>
       </c>
       <c r="C33" s="66" t="n"/>
-      <c r="D33" s="114" t="n">
+      <c r="D33" s="89" t="n">
         <v>304537</v>
       </c>
       <c r="E33" s="66" t="n"/>
@@ -6459,7 +6054,7 @@
         </is>
       </c>
       <c r="H33" s="66" t="n"/>
-      <c r="I33" s="114" t="n">
+      <c r="I33" s="89" t="n">
         <v>5582389</v>
       </c>
       <c r="J33" s="66" t="n"/>
@@ -6469,12 +6064,12 @@
         </is>
       </c>
       <c r="M33" s="66" t="n"/>
-      <c r="N33" s="118" t="n">
-        <v>0.092</v>
+      <c r="N33" s="97" t="n">
+        <v>0.0224</v>
       </c>
       <c r="O33" s="66" t="n"/>
     </row>
-    <row r="34" ht="16" customHeight="1">
+    <row r="34">
       <c r="A34" s="66" t="n"/>
       <c r="B34" s="66" t="inlineStr">
         <is>
@@ -6482,7 +6077,7 @@
         </is>
       </c>
       <c r="C34" s="66" t="n"/>
-      <c r="D34" s="114" t="n">
+      <c r="D34" s="89" t="n">
         <v>5582389</v>
       </c>
       <c r="E34" s="66" t="n"/>
@@ -6492,7 +6087,7 @@
         </is>
       </c>
       <c r="H34" s="66" t="n"/>
-      <c r="I34" s="114" t="n">
+      <c r="I34" s="89" t="n">
         <v>304537</v>
       </c>
       <c r="J34" s="66" t="n"/>
@@ -6501,7 +6096,7 @@
       <c r="N34" s="66" t="n"/>
       <c r="O34" s="66" t="n"/>
     </row>
-    <row r="35" ht="16" customHeight="1">
+    <row r="35">
       <c r="A35" s="66" t="n"/>
       <c r="B35" s="66" t="inlineStr">
         <is>
@@ -6509,8 +6104,8 @@
         </is>
       </c>
       <c r="C35" s="66" t="n"/>
-      <c r="D35" s="116" t="n">
-        <v>22117968.3</v>
+      <c r="D35" s="95" t="n">
+        <v>14849458.6</v>
       </c>
       <c r="E35" s="66" t="n"/>
       <c r="G35" s="66" t="inlineStr">
@@ -6519,20 +6114,20 @@
         </is>
       </c>
       <c r="H35" s="66" t="n"/>
-      <c r="I35" s="116" t="n">
+      <c r="I35" s="95" t="n">
         <v>27873945.7</v>
       </c>
       <c r="J35" s="66" t="n"/>
-      <c r="L35" s="80" t="inlineStr">
+      <c r="L35" s="83" t="inlineStr">
         <is>
           <t>Market Value vs Intrinsic Value</t>
         </is>
       </c>
-      <c r="M35" s="81" t="n"/>
-      <c r="N35" s="81" t="n"/>
+      <c r="M35" s="84" t="n"/>
+      <c r="N35" s="84" t="n"/>
       <c r="O35" s="66" t="n"/>
     </row>
-    <row r="36" ht="16" customHeight="1">
+    <row r="36">
       <c r="A36" s="66" t="n"/>
       <c r="B36" s="66" t="n"/>
       <c r="C36" s="66" t="n"/>
@@ -6540,7 +6135,7 @@
       <c r="E36" s="66" t="n"/>
       <c r="G36" s="66" t="n"/>
       <c r="H36" s="66" t="n"/>
-      <c r="I36" s="119" t="n"/>
+      <c r="I36" s="98" t="n"/>
       <c r="J36" s="66" t="n"/>
       <c r="L36" s="66" t="inlineStr">
         <is>
@@ -6548,12 +6143,12 @@
         </is>
       </c>
       <c r="M36" s="66" t="n"/>
-      <c r="N36" s="120" t="n">
+      <c r="N36" s="99" t="n">
         <v>1046.23</v>
       </c>
       <c r="O36" s="66" t="n"/>
     </row>
-    <row r="37" ht="16" customHeight="1">
+    <row r="37">
       <c r="A37" s="66" t="n"/>
       <c r="B37" s="66" t="inlineStr">
         <is>
@@ -6561,8 +6156,8 @@
         </is>
       </c>
       <c r="C37" s="66" t="n"/>
-      <c r="D37" s="120" t="n">
-        <v>1024.09</v>
+      <c r="D37" s="99" t="n">
+        <v>687.55</v>
       </c>
       <c r="E37" s="66" t="n"/>
       <c r="G37" s="66" t="inlineStr">
@@ -6571,7 +6166,7 @@
         </is>
       </c>
       <c r="H37" s="66" t="n"/>
-      <c r="I37" s="120" t="n">
+      <c r="I37" s="99" t="n">
         <v>1046.23</v>
       </c>
       <c r="J37" s="66" t="n"/>
@@ -6581,12 +6176,12 @@
         </is>
       </c>
       <c r="M37" s="66" t="n"/>
-      <c r="N37" s="120" t="n">
-        <v>-22.14</v>
+      <c r="N37" s="99" t="n">
+        <v>-358.68</v>
       </c>
       <c r="O37" s="66" t="n"/>
     </row>
-    <row r="38" ht="16" customHeight="1">
+    <row r="38">
       <c r="A38" s="66" t="n"/>
       <c r="B38" s="66" t="n"/>
       <c r="C38" s="66" t="n"/>
@@ -6602,12 +6197,12 @@
         </is>
       </c>
       <c r="M38" s="66" t="n"/>
-      <c r="N38" s="120" t="n">
-        <v>1024.09</v>
+      <c r="N38" s="99" t="n">
+        <v>687.55</v>
       </c>
       <c r="O38" s="66" t="n"/>
     </row>
-    <row r="39" ht="16" customHeight="1">
+    <row r="39">
       <c r="A39" s="66" t="n"/>
       <c r="C39" s="66" t="n"/>
       <c r="D39" s="68" t="n"/>
@@ -6621,7 +6216,7 @@
       <c r="N39" s="66" t="n"/>
       <c r="O39" s="66" t="n"/>
     </row>
-    <row r="40" ht="16" customHeight="1">
+    <row r="40">
       <c r="A40" s="66" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="68" t="n"/>
@@ -6636,28 +6231,28 @@
       <c r="N40" s="66" t="n"/>
       <c r="O40" s="66" t="n"/>
     </row>
-    <row r="41" ht="16" customHeight="1">
+    <row r="41">
       <c r="A41" s="66" t="n"/>
-      <c r="B41" s="80" t="inlineStr">
+      <c r="B41" s="83" t="inlineStr">
         <is>
           <t>Instructions</t>
         </is>
       </c>
-      <c r="C41" s="81" t="n"/>
-      <c r="D41" s="95" t="n"/>
-      <c r="E41" s="81" t="n"/>
-      <c r="F41" s="81" t="n"/>
-      <c r="G41" s="81" t="n"/>
-      <c r="H41" s="81" t="n"/>
-      <c r="I41" s="81" t="n"/>
-      <c r="J41" s="81" t="n"/>
-      <c r="K41" s="81" t="n"/>
-      <c r="L41" s="81" t="n"/>
-      <c r="M41" s="81" t="n"/>
-      <c r="N41" s="81" t="n"/>
+      <c r="C41" s="84" t="n"/>
+      <c r="D41" s="100" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="84" t="n"/>
+      <c r="G41" s="84" t="n"/>
+      <c r="H41" s="84" t="n"/>
+      <c r="I41" s="84" t="n"/>
+      <c r="J41" s="84" t="n"/>
+      <c r="K41" s="84" t="n"/>
+      <c r="L41" s="84" t="n"/>
+      <c r="M41" s="84" t="n"/>
+      <c r="N41" s="84" t="n"/>
       <c r="O41" s="66" t="n"/>
     </row>
-    <row r="42" ht="16" customHeight="1">
+    <row r="42">
       <c r="A42" s="66" t="n"/>
       <c r="B42" s="66" t="inlineStr">
         <is>
@@ -6670,14 +6265,14 @@
       <c r="F42" s="66" t="n"/>
       <c r="G42" s="66" t="n"/>
       <c r="H42" s="66" t="n"/>
-      <c r="N42" s="96" t="inlineStr">
+      <c r="N42" s="101" t="inlineStr">
         <is>
           <t>This file is for educational purposes only. E&amp;OE</t>
         </is>
       </c>
       <c r="O42" s="66" t="n"/>
     </row>
-    <row r="43" ht="16" customHeight="1">
+    <row r="43">
       <c r="A43" s="66" t="n"/>
       <c r="B43" s="66" t="inlineStr">
         <is>
@@ -6690,12 +6285,12 @@
       <c r="F43" s="66" t="n"/>
       <c r="G43" s="66" t="n"/>
       <c r="H43" s="66" t="n"/>
-      <c r="N43" s="57" t="n"/>
+      <c r="N43" s="55" t="n"/>
       <c r="O43" s="66" t="n"/>
     </row>
-    <row r="44" ht="16" customHeight="1">
+    <row r="44">
       <c r="A44" s="66" t="n"/>
-      <c r="B44" s="97" t="inlineStr">
+      <c r="B44" s="102" t="inlineStr">
         <is>
           <t>There are two ways to find NWC:</t>
         </is>
@@ -6706,12 +6301,12 @@
       <c r="F44" s="66" t="n"/>
       <c r="G44" s="66" t="n"/>
       <c r="H44" s="66" t="n"/>
-      <c r="N44" s="57" t="n"/>
+      <c r="N44" s="55" t="n"/>
       <c r="O44" s="66" t="n"/>
     </row>
-    <row r="45" ht="16" customHeight="1">
+    <row r="45">
       <c r="A45" s="66" t="n"/>
-      <c r="B45" s="97" t="inlineStr">
+      <c r="B45" s="102" t="inlineStr">
         <is>
           <t>1. NWC = Current Assets (less cash) - Current Liabilities (less debt)</t>
         </is>
@@ -6722,12 +6317,12 @@
       <c r="F45" s="66" t="n"/>
       <c r="G45" s="66" t="n"/>
       <c r="H45" s="66" t="n"/>
-      <c r="N45" s="57" t="n"/>
+      <c r="N45" s="55" t="n"/>
       <c r="O45" s="66" t="n"/>
     </row>
-    <row r="46" ht="16" customHeight="1">
+    <row r="46">
       <c r="A46" s="66" t="n"/>
-      <c r="B46" s="97" t="inlineStr">
+      <c r="B46" s="102" t="inlineStr">
         <is>
           <t>2. NWC = Accounts Receivable + Inventory - Accounts Payable</t>
         </is>
@@ -6738,10 +6333,10 @@
       <c r="F46" s="66" t="n"/>
       <c r="G46" s="66" t="n"/>
       <c r="H46" s="66" t="n"/>
-      <c r="N46" s="57" t="n"/>
+      <c r="N46" s="55" t="n"/>
       <c r="O46" s="66" t="n"/>
     </row>
-    <row r="47" ht="16" customHeight="1">
+    <row r="47">
       <c r="A47" s="66" t="n"/>
       <c r="B47" s="66" t="n"/>
       <c r="C47" s="66" t="n"/>
@@ -6750,10 +6345,10 @@
       <c r="F47" s="66" t="n"/>
       <c r="G47" s="66" t="n"/>
       <c r="H47" s="66" t="n"/>
-      <c r="N47" s="57" t="n"/>
+      <c r="N47" s="55" t="n"/>
       <c r="O47" s="66" t="n"/>
     </row>
-    <row r="48" ht="16" customHeight="1">
+    <row r="48">
       <c r="A48" s="66" t="n"/>
       <c r="B48" s="66" t="n"/>
       <c r="C48" s="66" t="n"/>
@@ -6762,14 +6357,14 @@
       <c r="F48" s="66" t="n"/>
       <c r="G48" s="66" t="n"/>
       <c r="H48" s="66" t="n"/>
-      <c r="N48" s="98" t="inlineStr">
+      <c r="N48" s="103" t="inlineStr">
         <is>
           <t xml:space="preserve">Corporate Finance Institute® </t>
         </is>
       </c>
       <c r="O48" s="66" t="n"/>
     </row>
-    <row r="49" ht="16" customHeight="1">
+    <row r="49">
       <c r="A49" s="66" t="n"/>
       <c r="B49" s="66" t="n"/>
       <c r="C49" s="66" t="n"/>
@@ -6778,18 +6373,18 @@
       <c r="F49" s="66" t="n"/>
       <c r="G49" s="66" t="n"/>
       <c r="H49" s="66" t="n"/>
-      <c r="N49" s="99" t="inlineStr">
+      <c r="N49" s="104" t="inlineStr">
         <is>
           <t>https://corporatefinanceinstitute.com/</t>
         </is>
       </c>
       <c r="O49" s="66" t="n"/>
     </row>
-    <row r="50" ht="16" customHeight="1">
+    <row r="50">
       <c r="A50" s="66" t="n"/>
-      <c r="B50" s="100" t="inlineStr">
-        <is>
-          <t>Blue/yellow = inputs. Blue-gray = computed (dates, taxes, Capex, UFCF, TV, EV). Capex = 10-K PPE purchases + capitalized software. Tax = FY25 ETR.</t>
+      <c r="B50" s="105" t="inlineStr">
+        <is>
+          <t>Base FY25 OpInc=924,850 D&amp;A=14,952 Capex=39,407. WACC=9.6% g=3% EV/EBITDA=22x. Source: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
       </c>
       <c r="C50" s="66" t="n"/>
@@ -6800,7 +6395,7 @@
       <c r="H50" s="66" t="n"/>
       <c r="O50" s="66" t="n"/>
     </row>
-    <row r="51" ht="16" customHeight="1">
+    <row r="51">
       <c r="A51" s="66" t="n"/>
       <c r="B51" s="66" t="n"/>
       <c r="C51" s="66" t="n"/>
@@ -6812,7 +6407,7 @@
       <c r="M51" s="66" t="n"/>
       <c r="O51" s="66" t="n"/>
     </row>
-    <row r="52" ht="16" customHeight="1">
+    <row r="52">
       <c r="A52" s="66" t="n"/>
       <c r="B52" s="66" t="n"/>
       <c r="C52" s="66" t="n"/>
@@ -6829,7 +6424,7 @@
       <c r="N52" s="66" t="n"/>
       <c r="O52" s="66" t="n"/>
     </row>
-    <row r="53" ht="16" customHeight="1">
+    <row r="53">
       <c r="A53" s="66" t="n"/>
       <c r="B53" s="66" t="n"/>
       <c r="C53" s="66" t="n"/>
@@ -6846,7 +6441,7 @@
       <c r="N53" s="66" t="n"/>
       <c r="O53" s="66" t="n"/>
     </row>
-    <row r="54" ht="16" customHeight="1">
+    <row r="54">
       <c r="A54" s="66" t="n"/>
       <c r="B54" s="66" t="n"/>
       <c r="C54" s="66" t="n"/>
@@ -6863,7 +6458,7 @@
       <c r="N54" s="66" t="n"/>
       <c r="O54" s="66" t="n"/>
     </row>
-    <row r="55" ht="16" customHeight="1">
+    <row r="55">
       <c r="A55" s="66" t="n"/>
       <c r="B55" s="66" t="n"/>
       <c r="C55" s="66" t="n"/>
@@ -6880,7 +6475,7 @@
       <c r="N55" s="66" t="n"/>
       <c r="O55" s="66" t="n"/>
     </row>
-    <row r="56" ht="16" customHeight="1">
+    <row r="56">
       <c r="A56" s="66" t="n"/>
       <c r="B56" s="66" t="n"/>
       <c r="C56" s="66" t="n"/>
@@ -6897,7 +6492,7 @@
       <c r="N56" s="66" t="n"/>
       <c r="O56" s="66" t="n"/>
     </row>
-    <row r="57" ht="16" customHeight="1">
+    <row r="57">
       <c r="A57" s="66" t="n"/>
       <c r="B57" s="66" t="n"/>
       <c r="C57" s="66" t="n"/>
@@ -6914,7 +6509,7 @@
       <c r="N57" s="66" t="n"/>
       <c r="O57" s="66" t="n"/>
     </row>
-    <row r="58" ht="16" customHeight="1">
+    <row r="58">
       <c r="A58" s="66" t="n"/>
       <c r="B58" s="66" t="n"/>
       <c r="C58" s="66" t="n"/>
@@ -6931,7 +6526,7 @@
       <c r="N58" s="66" t="n"/>
       <c r="O58" s="66" t="n"/>
     </row>
-    <row r="59" ht="16" customHeight="1">
+    <row r="59">
       <c r="A59" s="66" t="n"/>
       <c r="B59" s="66" t="n"/>
       <c r="C59" s="66" t="n"/>
@@ -6948,7 +6543,7 @@
       <c r="N59" s="66" t="n"/>
       <c r="O59" s="66" t="n"/>
     </row>
-    <row r="60" ht="16" customHeight="1">
+    <row r="60">
       <c r="A60" s="66" t="n"/>
       <c r="B60" s="66" t="n"/>
       <c r="C60" s="66" t="n"/>
@@ -6965,7 +6560,7 @@
       <c r="N60" s="66" t="n"/>
       <c r="O60" s="66" t="n"/>
     </row>
-    <row r="61" ht="16" customHeight="1">
+    <row r="61">
       <c r="B61" s="66" t="n"/>
       <c r="C61" s="66" t="n"/>
       <c r="D61" s="68" t="n"/>
@@ -6980,6 +6575,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/FICO/FICO_3S_DCF_Joined.xlsx
+++ b/FICO/FICO_3S_DCF_Joined.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="01_Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Audit_Fixes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Formula_Map" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="03_Three_Statement" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="04_DCF" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -33,7 +33,7 @@
     <numFmt numFmtId="174" formatCode="#,##0.000"/>
     <numFmt numFmtId="175" formatCode="_-* #,##0.00_-;\(#,##0.00\)_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,10 @@
       <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="000000FF"/>
+    </font>
+    <font>
       <name val="Arial Narrow"/>
       <family val="2"/>
       <i val="1"/>
@@ -120,10 +124,6 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000000FF"/>
     </font>
     <font>
       <name val="Arial Narrow"/>
@@ -222,23 +222,14 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Open Sans"/>
-      <family val="2"/>
-      <i val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
     </font>
     <font>
       <name val="Open Sans"/>
       <family val="2"/>
       <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Open Sans"/>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -276,7 +267,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DEEBF7"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -287,13 +278,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -349,10 +340,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -376,29 +370,31 @@
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -406,42 +402,42 @@
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -457,61 +453,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="30" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="173" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="26" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="30" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="30" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="28" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="27" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="173" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="174" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="27" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="26" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="25" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="30" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="31" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="25" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="32" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="30" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="30" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="25" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="29" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="25" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="25" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="25" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -520,10 +514,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -612,7 +605,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>FICO Revenue FY2021–2030</a:t>
+              <a:t>Revenue</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -683,6 +676,99 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Unlevered FCF (formula-driven)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'04_DCF'!$E$17:$I$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'04_DCF'!$E$26:$I$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>USD thousands</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -693,6 +779,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -999,16 +1112,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FICO Joined 3-Statement + DCF (CORRECTED)</t>
+          <t>FICO Joined Model — formula dependencies</t>
         </is>
       </c>
     </row>
@@ -1018,50 +1131,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>See Audit_Fixes for every error that was identified and corrected.</t>
+          <t>Yellow cells are the ONLY typed inputs.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03_Three_Statement: FY2021–2025 10-K history + FY2026–2030 FICO-scale forecast drivers.</t>
+          <t>Every total, tax, UFCF, TV, EV, revenue roll-forward is an Excel formula.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04_DCF: EBIT/D&amp;A/Capex/NWC path anchored to FY25 Operating income / D&amp;A / Capex.</t>
+          <t>04_DCF!E21:I25 are formulas into 03_Three_Statement (green).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Years are hardcoded values (not blank formulas). UFCF/TV/EV are filled numbers + chart.</t>
+          <t>04_DCF!E22/E26/N18:N20/D32:D37 remain native math formulas.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>See Formula_Map and FORMULA_MATH.md.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
-        <is>
-          <t>FY25 OpInc=924,850  D&amp;A=14,952  Capex=39,407  Tax rate=18.77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Intrinsic Eq/sh (model) ≈ 687.55 vs price 1,046.23</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
@@ -1078,349 +1181,561 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Errors found and fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Fix</t>
+          <t>Updated math — Excel formula dependencies (not typed results)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Yellow cells = inputs. Green/white formula cells = depend on other rows/sheets.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3S forecast COGS%</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Was 37% (CFI sample)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Now 17.77% from FY25</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Excel formula / dependency</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Meaning</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3S forecast SG&amp;A/R&amp;D</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Was $25k / $10k</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Now FY25 SG&amp;A/R&amp;D grown with revenue</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>input (or ='03_Three_Statement'!J13 if joined)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>FY25 ETR</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3S forecast tax</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Was 28%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Now 18.77% FY25 ETR</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>E17:I17</t>
+        </is>
+      </c>
+      <c r="C6" s="3">
+        <f>YEAR(E18) …</f>
+        <v/>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Depends on date row</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3S AR / Inv days</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Was 18 / 73</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Now ~97 / 0</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>E18:I18</t>
+        </is>
+      </c>
+      <c r="C7" s="3">
+        <f>DATE(YEAR($D$10)+E19,9,30)</f>
+        <v/>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Depends on FYE + period</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3S Capex forecast</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Was ~15k sample</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Now from FY25 39,407 growing 8%/yr</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Periods</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>F19:I19</t>
+        </is>
+      </c>
+      <c r="C8" s="3">
+        <f>E19+1 …</f>
+        <v/>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Depends on prior period</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3S year headers</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Formulas blank pre-calc</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Hardcoded 2021–2030</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Year fraction</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>E20:I20</t>
+        </is>
+      </c>
+      <c r="C9" s="3">
+        <f>YEARFRAC(prior_date, date)</f>
+        <v/>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Discount stub</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DCF Year-1 EBIT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Started ~1,048,623 (&gt;FY25 OpInc)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Path anchored to FY25 OpInc 924,850</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>E21:I21</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Standalone: =$D$3*(1+E4) then rolls; Joined: 3-stmt GP−opex−DA</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Operating income path</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DCF D&amp;A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Used ~18k (0.8% rev)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Anchored to FY25 D&amp;A 14,952</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cash Taxes</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>E22:I22</t>
+        </is>
+      </c>
+      <c r="C11" s="3">
+        <f>E21*$D$5</f>
+        <v/>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Depends on EBIT and tax rate</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DCF years</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Unclear / missing FY25 base</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>FY25 actuals in row 16; forecast 2026–2030</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>E23:I23</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Standalone: =$E$3*E21/$D$3; Joined: ='03_Three_Statement'!J30</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Depends on EBIT or 3-stmt</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DCF Capex</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Flat 39,407</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Grows 8%/yr with investment</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>E24:I24</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Standalone: =$D$15*(1+$D$16)^E19; Joined: 3-stmt!J68</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Depends on base capex/growth or 3-stmt</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DCF EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>25x → huge TV vs PG</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Set 22x; still show PG / multiple / average</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>ΔNWC</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>E25:I25</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Standalone: =MAX(0,ΔEBIT)*5%; Joined: 3-stmt!J89</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>WC investment</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DCF blanks</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Taxes/Capex/UFCF/TV formulas blank in viewer</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Written as computed values + chart</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Unlevered FCF</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>E26:I26</t>
+        </is>
+      </c>
+      <c r="C15" s="3">
+        <f>EBIT − Tax + D&amp;A − Capex − ΔNWC</f>
+        <v/>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Core FCF identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TV (PG)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>N18</t>
+        </is>
+      </c>
+      <c r="C16" s="3">
+        <f>(I26*(1+D7))/(D6-D7)</f>
+        <v/>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Gordon growth on final UFCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TV (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N19</t>
+        </is>
+      </c>
+      <c r="C17" s="3">
+        <f>D8*(I21+I23)</f>
+        <v/>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Exit multiple on final EBITDA</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TV Average</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="C18" s="3">
+        <f>AVERAGE(N18:N19)</f>
+        <v/>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Blended exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise Value</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>D32</t>
+        </is>
+      </c>
+      <c r="C19" s="3">
+        <f>XNPV(D6,D28:J28,D18:J18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>PV of transaction CFs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Equity Value</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="C20" s="3">
+        <f>D32+D33−D34</f>
+        <v/>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>EV + cash − debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Equity / share</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>D37</t>
+        </is>
+      </c>
+      <c r="C21" s="3">
+        <f>D35/D12</f>
+        <v/>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Depends on equity &amp; shares</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>3S Revenue fcst</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>J24</t>
+        </is>
+      </c>
+      <c r="C22" s="3">
+        <f>I24*(1+J7)</f>
+        <v/>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Grows from prior year</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>3S COGS fcst</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>J25</t>
+        </is>
+      </c>
+      <c r="C23" s="3">
+        <f>J24*J8</f>
+        <v/>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Depends on revenue &amp; COGS%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>3S Gross Profit</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="C24" s="3">
+        <f>J24-J25</f>
+        <v/>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Depends on Rev &amp; COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>3S SG&amp;A fcst</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>J28</t>
+        </is>
+      </c>
+      <c r="C25" s="3">
+        <f>J9</f>
+        <v/>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Depends on salaries driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>3S Capex fcst</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>J68</t>
+        </is>
+      </c>
+      <c r="C26" s="3">
+        <f>J18</f>
+        <v/>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Depends on capex assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>3S ΔNWC fcst</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>J89</t>
+        </is>
+      </c>
+      <c r="C27" s="3">
+        <f>J88-I88</f>
+        <v/>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Depends on NWC schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>UFCF</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Capex</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1031318</v>
-      </c>
-      <c r="C21" t="n">
-        <v>752304</v>
-      </c>
-      <c r="D21" t="n">
-        <v>42560</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B22" t="n">
-        <v>1149880</v>
-      </c>
-      <c r="C22" t="n">
-        <v>850856</v>
-      </c>
-      <c r="D22" t="n">
-        <v>45964</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B23" t="n">
-        <v>1270112</v>
-      </c>
-      <c r="C23" t="n">
-        <v>947058</v>
-      </c>
-      <c r="D23" t="n">
-        <v>49641</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B24" t="n">
-        <v>1398473</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1050674</v>
-      </c>
-      <c r="D24" t="n">
-        <v>53613</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B25" t="n">
-        <v>1533660</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1160650</v>
-      </c>
-      <c r="D25" t="n">
-        <v>57902</v>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Joined roll-forward: 04_DCF EBIT/D&amp;A/Capex/ΔNWC are formulas into 03_Three_Statement J:N.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1436,7 +1751,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.88671875" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="15.5546875" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -1452,3422 +1767,3431 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="n"/>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="A1" s="5" t="n"/>
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>© Corporate Finance Institute®. All rights reserved.</t>
         </is>
       </c>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="6" t="n"/>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Historical Results</t>
         </is>
       </c>
-      <c r="F1" s="8" t="n"/>
-      <c r="G1" s="8" t="n"/>
-      <c r="H1" s="8" t="n"/>
-      <c r="I1" s="8" t="n"/>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="F1" s="9" t="n"/>
+      <c r="G1" s="9" t="n"/>
+      <c r="H1" s="9" t="n"/>
+      <c r="I1" s="9" t="n"/>
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve"> Forecast Period</t>
         </is>
       </c>
-      <c r="K1" s="10" t="n"/>
-      <c r="L1" s="10" t="n"/>
-      <c r="M1" s="10" t="n"/>
-      <c r="N1" s="10" t="n"/>
+      <c r="K1" s="11" t="n"/>
+      <c r="L1" s="11" t="n"/>
+      <c r="M1" s="11" t="n"/>
+      <c r="N1" s="11" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>FINANCIAL STATEMENTS</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="14" t="n">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="15" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="14" t="n">
-        <v>2022</v>
-      </c>
-      <c r="G2" s="14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H2" s="14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="I2" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="J2" s="15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="K2" s="15" t="n">
-        <v>2027</v>
-      </c>
-      <c r="L2" s="15" t="n">
-        <v>2028</v>
-      </c>
-      <c r="M2" s="15" t="n">
-        <v>2029</v>
-      </c>
-      <c r="N2" s="15" t="n">
-        <v>2030</v>
+      <c r="F2" s="16">
+        <f>+E2+1</f>
+        <v/>
+      </c>
+      <c r="G2" s="16">
+        <f>+F2+1</f>
+        <v/>
+      </c>
+      <c r="H2" s="16">
+        <f>+G2+1</f>
+        <v/>
+      </c>
+      <c r="I2" s="16">
+        <f>+H2+1</f>
+        <v/>
+      </c>
+      <c r="J2" s="17">
+        <f>+I2+1</f>
+        <v/>
+      </c>
+      <c r="K2" s="17">
+        <f>+J2+1</f>
+        <v/>
+      </c>
+      <c r="L2" s="17">
+        <f>+K2+1</f>
+        <v/>
+      </c>
+      <c r="M2" s="17">
+        <f>+L2+1</f>
+        <v/>
+      </c>
+      <c r="N2" s="17">
+        <f>+M2+1</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Balance Sheet Check</t>
         </is>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="19">
         <f>IFERROR(IF(ABS(E57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="19">
         <f>IFERROR(IF(ABS(F57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="19">
         <f>IFERROR(IF(ABS(G57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="19">
         <f>IFERROR(IF(ABS(H57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="19">
         <f>IFERROR(IF(ABS(I57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="19">
         <f>IFERROR(IF(ABS(J57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="19">
         <f>IFERROR(IF(ABS(K57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="19">
         <f>IFERROR(IF(ABS(L57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="19">
         <f>IFERROR(IF(ABS(M57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="19">
         <f>IFERROR(IF(ABS(N57)&gt;1,"ERROR","OK"),"OK")</f>
         <v/>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
-      <c r="H5" s="18" t="n"/>
-      <c r="I5" s="18" t="n"/>
-      <c r="J5" s="18" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="18" t="n"/>
-      <c r="M5" s="18" t="n"/>
-      <c r="N5" s="18" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="20" t="n"/>
+      <c r="K5" s="20" t="n"/>
+      <c r="L5" s="20" t="n"/>
+      <c r="M5" s="20" t="n"/>
+      <c r="N5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Income statement</t>
         </is>
       </c>
-      <c r="D6" s="20" t="n"/>
+      <c r="D6" s="22" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Revenue Growth (% Change)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="23">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="25">
         <f>F24/E24-1</f>
         <v/>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="25">
         <f>G24/F24-1</f>
         <v/>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="25">
         <f>H24/G24-1</f>
         <v/>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="25">
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="24" t="n">
+      <c r="J7" s="26" t="n">
         <v>0.12</v>
       </c>
-      <c r="K7" s="24" t="n">
+      <c r="K7" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="L7" s="24" t="n">
+      <c r="L7" s="26" t="n">
         <v>0.09</v>
       </c>
-      <c r="M7" s="24" t="n">
+      <c r="M7" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="N7" s="24" t="n">
+      <c r="N7" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Cost of Goods Sold (% of Revenue)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="23">
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="25">
         <f>E25/E24</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="25">
         <f>F25/F24</f>
         <v/>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="25">
         <f>G25/G24</f>
         <v/>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="25">
         <f>H25/H24</f>
         <v/>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="25">
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="24" t="n">
+      <c r="J8" s="27" t="n">
         <v>0.1777</v>
       </c>
-      <c r="K8" s="24" t="n">
+      <c r="K8" s="27" t="n">
         <v>0.1777</v>
       </c>
-      <c r="L8" s="24" t="n">
+      <c r="L8" s="27" t="n">
         <v>0.1777</v>
       </c>
-      <c r="M8" s="24" t="n">
+      <c r="M8" s="27" t="n">
         <v>0.1777</v>
       </c>
-      <c r="N8" s="24" t="n">
+      <c r="N8" s="27" t="n">
         <v>0.1777</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Salaries and Benefits ($000's)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="25">
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="28">
         <f>E28</f>
         <v/>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="28">
         <f>F28</f>
         <v/>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="28">
         <f>G28</f>
         <v/>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="28">
         <f>H28</f>
         <v/>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="28">
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="26" t="n">
+      <c r="J9" s="29" t="n">
         <v>574591.4</v>
       </c>
-      <c r="K9" s="26" t="n">
+      <c r="K9" s="29" t="n">
         <v>620763.9</v>
       </c>
-      <c r="L9" s="26" t="n">
+      <c r="L9" s="29" t="n">
         <v>664386.1</v>
       </c>
-      <c r="M9" s="26" t="n">
+      <c r="M9" s="29" t="n">
         <v>697968.9</v>
       </c>
-      <c r="N9" s="26" t="n">
+      <c r="N9" s="29" t="n">
         <v>719548.3</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Rent and Overhead ($000's)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="25">
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="28">
         <f>E29</f>
         <v/>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="28">
         <f>F29</f>
         <v/>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="28">
         <f>G29</f>
         <v/>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="28">
         <f>H29</f>
         <v/>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="28">
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="26" t="n">
+      <c r="J10" s="29" t="n">
         <v>210948.6</v>
       </c>
-      <c r="K10" s="26" t="n">
+      <c r="K10" s="29" t="n">
         <v>227899.9</v>
       </c>
-      <c r="L10" s="26" t="n">
+      <c r="L10" s="29" t="n">
         <v>243914.8</v>
       </c>
-      <c r="M10" s="26" t="n">
+      <c r="M10" s="29" t="n">
         <v>256244</v>
       </c>
-      <c r="N10" s="26" t="n">
+      <c r="N10" s="29" t="n">
         <v>264166.4</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (% of PP&amp;E Open Bal)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="23">
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="25">
         <f>E30/E92</f>
         <v/>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="25">
         <f>F30/F92</f>
         <v/>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="25">
         <f>G30/G92</f>
         <v/>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="25">
         <f>H30/H92</f>
         <v/>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="25">
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="24" t="n">
+      <c r="J11" s="27" t="n">
         <v>0.35</v>
       </c>
-      <c r="K11" s="24" t="n">
+      <c r="K11" s="27" t="n">
         <v>0.35</v>
       </c>
-      <c r="L11" s="24" t="n">
+      <c r="L11" s="27" t="n">
         <v>0.35</v>
       </c>
-      <c r="M11" s="24" t="n">
+      <c r="M11" s="27" t="n">
         <v>0.35</v>
       </c>
-      <c r="N11" s="24" t="n">
+      <c r="N11" s="27" t="n">
         <v>0.35</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Interest (% of Debt Open Bal)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="23">
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="25">
         <f>E101/E98</f>
         <v/>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="25">
         <f>F101/F98</f>
         <v/>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="25">
         <f>G101/G98</f>
         <v/>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="25">
         <f>H101/H98</f>
         <v/>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="25">
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="24" t="n">
+      <c r="J12" s="27" t="n">
         <v>0.0437</v>
       </c>
-      <c r="K12" s="24" t="n">
+      <c r="K12" s="27" t="n">
         <v>0.0437</v>
       </c>
-      <c r="L12" s="24" t="n">
+      <c r="L12" s="27" t="n">
         <v>0.0437</v>
       </c>
-      <c r="M12" s="24" t="n">
+      <c r="M12" s="27" t="n">
         <v>0.0437</v>
       </c>
-      <c r="N12" s="24" t="n">
+      <c r="N12" s="27" t="n">
         <v>0.0437</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Tax Rate (% of Earnings Before Tax)</t>
         </is>
       </c>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="23">
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="25">
         <f>E35/E33</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="25">
         <f>F35/F33</f>
         <v/>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="25">
         <f>G35/G33</f>
         <v/>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="25">
         <f>H35/H33</f>
         <v/>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="25">
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="24" t="n">
+      <c r="J13" s="27" t="n">
         <v>0.1877</v>
       </c>
-      <c r="K13" s="24" t="n">
+      <c r="K13" s="27" t="n">
         <v>0.1877</v>
       </c>
-      <c r="L13" s="24" t="n">
+      <c r="L13" s="27" t="n">
         <v>0.1877</v>
       </c>
-      <c r="M13" s="24" t="n">
+      <c r="M13" s="27" t="n">
         <v>0.1877</v>
       </c>
-      <c r="N13" s="24" t="n">
+      <c r="N13" s="27" t="n">
         <v>0.1877</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>Balance Sheet</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="16" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="18" t="n"/>
+      <c r="M14" s="18" t="n"/>
+      <c r="N14" s="18" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Accounts Receivable (Days)</t>
         </is>
       </c>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="25">
+      <c r="D15" s="32" t="n"/>
+      <c r="E15" s="28">
         <f>E42/E24*365</f>
         <v/>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="28">
         <f>F42/F24*365</f>
         <v/>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="28">
         <f>G42/G24*365</f>
         <v/>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="28">
         <f>H42/H24*365</f>
         <v/>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="28">
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="26" t="n">
+      <c r="J15" s="29" t="n">
         <v>97</v>
       </c>
-      <c r="K15" s="26" t="n">
+      <c r="K15" s="29" t="n">
         <v>97</v>
       </c>
-      <c r="L15" s="26" t="n">
+      <c r="L15" s="29" t="n">
         <v>97</v>
       </c>
-      <c r="M15" s="26" t="n">
+      <c r="M15" s="29" t="n">
         <v>97</v>
       </c>
-      <c r="N15" s="26" t="n">
+      <c r="N15" s="29" t="n">
         <v>97</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Inventory (Days)</t>
         </is>
       </c>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="25">
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="28">
         <f>E43/E25*365</f>
         <v/>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="28">
         <f>F43/F25*365</f>
         <v/>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="28">
         <f>G43/G25*365</f>
         <v/>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="28">
         <f>H43/H25*365</f>
         <v/>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="28">
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="26" t="n">
+      <c r="J16" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="26" t="n">
+      <c r="K16" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="26" t="n">
+      <c r="L16" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="26" t="n">
+      <c r="M16" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="26" t="n">
+      <c r="N16" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Accounts Payable (Days)</t>
         </is>
       </c>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="25">
+      <c r="D17" s="32" t="n"/>
+      <c r="E17" s="28">
         <f>E48/E25*365</f>
         <v/>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="28">
         <f>F48/F25*365</f>
         <v/>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="28">
         <f>G48/G25*365</f>
         <v/>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="28">
         <f>H48/H25*365</f>
         <v/>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="28">
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="26" t="n">
+      <c r="J17" s="29" t="n">
         <v>33.3</v>
       </c>
-      <c r="K17" s="26" t="n">
+      <c r="K17" s="29" t="n">
         <v>33.3</v>
       </c>
-      <c r="L17" s="26" t="n">
+      <c r="L17" s="29" t="n">
         <v>33.3</v>
       </c>
-      <c r="M17" s="26" t="n">
+      <c r="M17" s="29" t="n">
         <v>33.3</v>
       </c>
-      <c r="N17" s="26" t="n">
+      <c r="N17" s="29" t="n">
         <v>33.3</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Capital Expenditures ($000's)</t>
         </is>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="28">
         <f>E68</f>
         <v/>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="28">
         <f>F68</f>
         <v/>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="28">
         <f>G68</f>
         <v/>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="28">
         <f>H68</f>
         <v/>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="28">
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="26" t="n">
+      <c r="J18" s="29" t="n">
         <v>42559.6</v>
       </c>
-      <c r="K18" s="26" t="n">
+      <c r="K18" s="29" t="n">
         <v>45964.3</v>
       </c>
-      <c r="L18" s="26" t="n">
+      <c r="L18" s="29" t="n">
         <v>49641.5</v>
       </c>
-      <c r="M18" s="26" t="n">
+      <c r="M18" s="29" t="n">
         <v>53612.8</v>
       </c>
-      <c r="N18" s="26" t="n">
+      <c r="N18" s="29" t="n">
         <v>57901.8</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Debt Issuance (Repayment) ($000's)</t>
         </is>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="28">
         <f>E99</f>
         <v/>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="28">
         <f>F99</f>
         <v/>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="28">
         <f>G99</f>
         <v/>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="28">
         <f>H99</f>
         <v/>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="28">
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="26" t="n">
+      <c r="J19" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="26" t="n">
+      <c r="K19" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="26" t="n">
+      <c r="L19" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="26" t="n">
+      <c r="M19" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="26" t="n">
+      <c r="N19" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Equity Issued (Repaid) ($000's)</t>
         </is>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="28">
         <f>E73</f>
         <v/>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="28">
         <f>F73</f>
         <v/>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="28">
         <f>G73</f>
         <v/>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="28">
         <f>H73</f>
         <v/>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="28">
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="26" t="n">
+      <c r="J20" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="26" t="n">
+      <c r="K20" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="26" t="n">
+      <c r="L20" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="26" t="n">
+      <c r="M20" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="26" t="n">
+      <c r="N20" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
-      <c r="G21" s="25" t="n"/>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="25" t="n"/>
-      <c r="J21" s="30" t="n"/>
-      <c r="K21" s="30" t="n"/>
-      <c r="L21" s="30" t="n"/>
-      <c r="M21" s="30" t="n"/>
-      <c r="N21" s="30" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+      <c r="H21" s="28" t="n"/>
+      <c r="I21" s="28" t="n"/>
+      <c r="J21" s="33" t="n"/>
+      <c r="K21" s="33" t="n"/>
+      <c r="L21" s="33" t="n"/>
+      <c r="M21" s="33" t="n"/>
+      <c r="N21" s="33" t="n"/>
     </row>
     <row r="22">
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="25" t="n"/>
-      <c r="G22" s="25" t="n"/>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="25" t="n"/>
-      <c r="J22" s="30" t="n"/>
-      <c r="K22" s="30" t="n"/>
-      <c r="L22" s="30" t="n"/>
-      <c r="M22" s="30" t="n"/>
-      <c r="N22" s="30" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="28" t="n"/>
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="33" t="n"/>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="33" t="n"/>
+      <c r="N22" s="33" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Income Statement</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="18" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="20" t="n"/>
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="20" t="n"/>
+      <c r="I23" s="20" t="n"/>
+      <c r="J23" s="20" t="n"/>
+      <c r="K23" s="20" t="n"/>
+      <c r="L23" s="20" t="n"/>
+      <c r="M23" s="20" t="n"/>
+      <c r="N23" s="20" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>Revenue (FICO: Revenues)</t>
         </is>
       </c>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="26" t="n">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="29" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="29" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="26" t="n">
+      <c r="G24" s="29" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="26" t="n">
+      <c r="H24" s="29" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I24" s="29" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="21">
         <f>I24*(1+J7)</f>
         <v/>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="21">
         <f>J24*(1+K7)</f>
         <v/>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="21">
         <f>K24*(1+L7)</f>
         <v/>
       </c>
-      <c r="M24" s="19">
+      <c r="M24" s="21">
         <f>L24*(1+M7)</f>
         <v/>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="21">
         <f>M24*(1+N7)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>COGS (FICO: Cost of revenues)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="26" t="n">
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="29" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="29" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="26" t="n">
+      <c r="G25" s="29" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="26" t="n">
+      <c r="H25" s="29" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="26" t="n">
+      <c r="I25" s="29" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="34">
         <f>J24*J8</f>
         <v/>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="34">
         <f>K24*K8</f>
         <v/>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="34">
         <f>L24*L8</f>
         <v/>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="34">
         <f>M24*M8</f>
         <v/>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="34">
         <f>N24*N8</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="33" t="n"/>
-      <c r="E26" s="34">
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="37">
         <f>E24-E25</f>
         <v/>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="37">
         <f>F24-F25</f>
         <v/>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="37">
         <f>G24-G25</f>
         <v/>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="37">
         <f>H24-H25</f>
         <v/>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="37">
         <f>I24-I25</f>
         <v/>
       </c>
-      <c r="J26" s="34">
+      <c r="J26" s="37">
         <f>J24-J25</f>
         <v/>
       </c>
-      <c r="K26" s="34">
+      <c r="K26" s="37">
         <f>K24-K25</f>
         <v/>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="37">
         <f>L24-L25</f>
         <v/>
       </c>
-      <c r="M26" s="34">
+      <c r="M26" s="37">
         <f>M24-M25</f>
         <v/>
       </c>
-      <c r="N26" s="34">
+      <c r="N26" s="37">
         <f>N24-N25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="35" t="n"/>
-      <c r="F27" s="35" t="n"/>
-      <c r="G27" s="35" t="n"/>
-      <c r="H27" s="35" t="n"/>
-      <c r="I27" s="35" t="n"/>
-      <c r="J27" s="22" t="n"/>
-      <c r="K27" s="22" t="n"/>
-      <c r="L27" s="22" t="n"/>
-      <c r="M27" s="22" t="n"/>
-      <c r="N27" s="22" t="n"/>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="38" t="n"/>
+      <c r="G27" s="38" t="n"/>
+      <c r="H27" s="38" t="n"/>
+      <c r="I27" s="38" t="n"/>
+      <c r="J27" s="24" t="n"/>
+      <c r="K27" s="24" t="n"/>
+      <c r="L27" s="24" t="n"/>
+      <c r="M27" s="24" t="n"/>
+      <c r="N27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>SG&amp;A (CFI Salaries ← FICO SG&amp;A)</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="n">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>SG&amp;A ← Salaries (depends on row 9)</t>
+        </is>
+      </c>
+      <c r="E28" s="29" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="29" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="26" t="n">
+      <c r="G28" s="29" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="26" t="n">
+      <c r="H28" s="29" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="26" t="n">
+      <c r="I28" s="29" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="18">
         <f>J9</f>
         <v/>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="18">
         <f>K9</f>
         <v/>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="18">
         <f>L9</f>
         <v/>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="18">
         <f>M9</f>
         <v/>
       </c>
-      <c r="N28" s="16">
+      <c r="N28" s="18">
         <f>N9</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>R&amp;D (CFI Rent/Overhead ← FICO R&amp;D)</t>
-        </is>
-      </c>
-      <c r="E29" s="26" t="n">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>R&amp;D ← Rent/Overhead (depends on row 10)</t>
+        </is>
+      </c>
+      <c r="E29" s="29" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="29" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="26" t="n">
+      <c r="G29" s="29" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="26" t="n">
+      <c r="H29" s="29" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="26" t="n">
+      <c r="I29" s="29" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="18">
         <f>J10</f>
         <v/>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="18">
         <f>K10</f>
         <v/>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="18">
         <f>L10</f>
         <v/>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="18">
         <f>M10</f>
         <v/>
       </c>
-      <c r="N29" s="16">
+      <c r="N29" s="18">
         <f>N10</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="29" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="29" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="26" t="n">
+      <c r="G30" s="29" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="26" t="n">
+      <c r="H30" s="29" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="26" t="n">
+      <c r="I30" s="29" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="18">
         <f>J94</f>
         <v/>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="18">
         <f>K94</f>
         <v/>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="18">
         <f>L94</f>
         <v/>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="18">
         <f>M94</f>
         <v/>
       </c>
-      <c r="N30" s="16">
+      <c r="N30" s="18">
         <f>N94</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="36" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="37" t="n"/>
-      <c r="E31" s="38" t="n">
+      <c r="C31" s="39" t="n"/>
+      <c r="D31" s="40" t="n"/>
+      <c r="E31" s="41" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="38" t="n">
+      <c r="F31" s="41" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="38" t="n">
+      <c r="G31" s="41" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="38" t="n">
+      <c r="H31" s="41" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="38" t="n">
+      <c r="I31" s="41" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="39">
+      <c r="J31" s="42">
         <f>J101</f>
         <v/>
       </c>
-      <c r="K31" s="39">
+      <c r="K31" s="42">
         <f>K101</f>
         <v/>
       </c>
-      <c r="L31" s="39">
+      <c r="L31" s="42">
         <f>L101</f>
         <v/>
       </c>
-      <c r="M31" s="39">
+      <c r="M31" s="42">
         <f>M101</f>
         <v/>
       </c>
-      <c r="N31" s="39">
+      <c r="N31" s="42">
         <f>N101</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="20" t="n"/>
-      <c r="E32" s="22">
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="24">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="24">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="24">
         <f>SUM(G28:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="24">
         <f>SUM(H28:H31)</f>
         <v/>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="24">
         <f>SUM(I28:I31)</f>
         <v/>
       </c>
-      <c r="J32" s="22">
+      <c r="J32" s="24">
         <f>SUM(J28:J31)</f>
         <v/>
       </c>
-      <c r="K32" s="22">
+      <c r="K32" s="24">
         <f>SUM(K28:K31)</f>
         <v/>
       </c>
-      <c r="L32" s="22">
+      <c r="L32" s="24">
         <f>SUM(L28:L31)</f>
         <v/>
       </c>
-      <c r="M32" s="22">
+      <c r="M32" s="24">
         <f>SUM(M28:M31)</f>
         <v/>
       </c>
-      <c r="N32" s="22">
+      <c r="N32" s="24">
         <f>SUM(N28:N31)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Earnings Before Tax</t>
         </is>
       </c>
-      <c r="C33" s="32" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="34">
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="37">
         <f>E26-E32</f>
         <v/>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="37">
         <f>F26-F32</f>
         <v/>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="37">
         <f>G26-G32</f>
         <v/>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="37">
         <f>H26-H32</f>
         <v/>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="37">
         <f>I26-I32</f>
         <v/>
       </c>
-      <c r="J33" s="34">
+      <c r="J33" s="37">
         <f>J26-J32</f>
         <v/>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="37">
         <f>K26-K32</f>
         <v/>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="37">
         <f>L26-L32</f>
         <v/>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="37">
         <f>M26-M32</f>
         <v/>
       </c>
-      <c r="N33" s="34">
+      <c r="N33" s="37">
         <f>N26-N32</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="35" t="n"/>
-      <c r="F34" s="35" t="n"/>
-      <c r="G34" s="35" t="n"/>
-      <c r="H34" s="35" t="n"/>
-      <c r="I34" s="35" t="n"/>
-      <c r="J34" s="22" t="n"/>
-      <c r="K34" s="22" t="n"/>
-      <c r="L34" s="22" t="n"/>
-      <c r="M34" s="22" t="n"/>
-      <c r="N34" s="22" t="n"/>
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="38" t="n"/>
+      <c r="F34" s="38" t="n"/>
+      <c r="G34" s="38" t="n"/>
+      <c r="H34" s="38" t="n"/>
+      <c r="I34" s="38" t="n"/>
+      <c r="J34" s="24" t="n"/>
+      <c r="K34" s="24" t="n"/>
+      <c r="L34" s="24" t="n"/>
+      <c r="M34" s="24" t="n"/>
+      <c r="N34" s="24" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>Taxes</t>
         </is>
       </c>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="20" t="n"/>
-      <c r="E35" s="26" t="n">
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="29" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="29" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="26" t="n">
+      <c r="G35" s="29" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="26" t="n">
+      <c r="H35" s="29" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="26" t="n">
+      <c r="I35" s="29" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="31">
+      <c r="J35" s="34">
         <f>J33*J13</f>
         <v/>
       </c>
-      <c r="K35" s="31">
+      <c r="K35" s="34">
         <f>K33*K13</f>
         <v/>
       </c>
-      <c r="L35" s="31">
+      <c r="L35" s="34">
         <f>L33*L13</f>
         <v/>
       </c>
-      <c r="M35" s="31">
+      <c r="M35" s="34">
         <f>M33*M13</f>
         <v/>
       </c>
-      <c r="N35" s="31">
+      <c r="N35" s="34">
         <f>N33*N13</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="C36" s="40" t="n"/>
-      <c r="D36" s="41" t="n"/>
-      <c r="E36" s="42">
+      <c r="C36" s="43" t="n"/>
+      <c r="D36" s="44" t="n"/>
+      <c r="E36" s="45">
         <f>E33-E35</f>
         <v/>
       </c>
-      <c r="F36" s="42">
+      <c r="F36" s="45">
         <f>F33-F35</f>
         <v/>
       </c>
-      <c r="G36" s="42">
+      <c r="G36" s="45">
         <f>G33-G35</f>
         <v/>
       </c>
-      <c r="H36" s="42">
+      <c r="H36" s="45">
         <f>H33-H35</f>
         <v/>
       </c>
-      <c r="I36" s="42">
+      <c r="I36" s="45">
         <f>I33-I35</f>
         <v/>
       </c>
-      <c r="J36" s="42">
+      <c r="J36" s="45">
         <f>J33-J35</f>
         <v/>
       </c>
-      <c r="K36" s="42">
+      <c r="K36" s="45">
         <f>K33-K35</f>
         <v/>
       </c>
-      <c r="L36" s="42">
+      <c r="L36" s="45">
         <f>L33-L35</f>
         <v/>
       </c>
-      <c r="M36" s="42">
+      <c r="M36" s="45">
         <f>M33-M35</f>
         <v/>
       </c>
-      <c r="N36" s="42">
+      <c r="N36" s="45">
         <f>N33-N35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="E37" s="30" t="n"/>
-      <c r="F37" s="30" t="n"/>
-      <c r="G37" s="30" t="n"/>
-      <c r="H37" s="30" t="n"/>
-      <c r="I37" s="30" t="n"/>
+      <c r="E37" s="33" t="n"/>
+      <c r="F37" s="33" t="n"/>
+      <c r="G37" s="33" t="n"/>
+      <c r="H37" s="33" t="n"/>
+      <c r="I37" s="33" t="n"/>
     </row>
     <row r="38">
-      <c r="E38" s="30" t="n"/>
-      <c r="F38" s="30" t="n"/>
-      <c r="G38" s="30" t="n"/>
-      <c r="H38" s="30" t="n"/>
-      <c r="I38" s="30" t="n"/>
-      <c r="J38" s="30" t="n"/>
-      <c r="K38" s="30" t="n"/>
-      <c r="L38" s="30" t="n"/>
-      <c r="M38" s="30" t="n"/>
-      <c r="N38" s="30" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="33" t="n"/>
+      <c r="I38" s="33" t="n"/>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="33" t="n"/>
+      <c r="L38" s="33" t="n"/>
+      <c r="M38" s="33" t="n"/>
+      <c r="N38" s="33" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>Balance Sheet</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
-      <c r="D39" s="18" t="n"/>
-      <c r="E39" s="18" t="n"/>
-      <c r="F39" s="18" t="n"/>
-      <c r="G39" s="18" t="n"/>
-      <c r="H39" s="18" t="n"/>
-      <c r="I39" s="18" t="n"/>
-      <c r="J39" s="18" t="n"/>
-      <c r="K39" s="18" t="n"/>
-      <c r="L39" s="18" t="n"/>
-      <c r="M39" s="18" t="n"/>
-      <c r="N39" s="18" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="20" t="n"/>
+      <c r="H39" s="20" t="n"/>
+      <c r="I39" s="20" t="n"/>
+      <c r="J39" s="20" t="n"/>
+      <c r="K39" s="20" t="n"/>
+      <c r="L39" s="20" t="n"/>
+      <c r="M39" s="20" t="n"/>
+      <c r="N39" s="20" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="E40" s="30" t="n"/>
-      <c r="F40" s="30" t="n"/>
-      <c r="G40" s="30" t="n"/>
-      <c r="H40" s="30" t="n"/>
-      <c r="I40" s="30" t="n"/>
+      <c r="E40" s="33" t="n"/>
+      <c r="F40" s="33" t="n"/>
+      <c r="G40" s="33" t="n"/>
+      <c r="H40" s="33" t="n"/>
+      <c r="I40" s="33" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="26" t="n">
+      <c r="E41" s="29" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="26" t="n">
+      <c r="F41" s="29" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="26" t="n">
+      <c r="G41" s="29" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="26" t="n">
+      <c r="H41" s="29" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="26" t="n">
+      <c r="I41" s="29" t="n">
         <v>134136</v>
       </c>
-      <c r="J41" s="16">
+      <c r="J41" s="18">
         <f>J78</f>
         <v/>
       </c>
-      <c r="K41" s="16">
+      <c r="K41" s="18">
         <f>K78</f>
         <v/>
       </c>
-      <c r="L41" s="16">
+      <c r="L41" s="18">
         <f>L78</f>
         <v/>
       </c>
-      <c r="M41" s="16">
+      <c r="M41" s="18">
         <f>M78</f>
         <v/>
       </c>
-      <c r="N41" s="16">
+      <c r="N41" s="18">
         <f>N78</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E42" s="26" t="n">
+      <c r="E42" s="29" t="n">
         <v>312107</v>
       </c>
-      <c r="F42" s="26" t="n">
+      <c r="F42" s="29" t="n">
         <v>322410</v>
       </c>
-      <c r="G42" s="26" t="n">
+      <c r="G42" s="29" t="n">
         <v>387947</v>
       </c>
-      <c r="H42" s="26" t="n">
+      <c r="H42" s="29" t="n">
         <v>426642</v>
       </c>
-      <c r="I42" s="26" t="n">
+      <c r="I42" s="29" t="n">
         <v>529148</v>
       </c>
-      <c r="J42" s="43">
+      <c r="J42" s="46">
         <f>J24*J15/365</f>
         <v/>
       </c>
-      <c r="K42" s="43">
+      <c r="K42" s="46">
         <f>K24*K15/365</f>
         <v/>
       </c>
-      <c r="L42" s="43">
+      <c r="L42" s="46">
         <f>L24*L15/365</f>
         <v/>
       </c>
-      <c r="M42" s="43">
+      <c r="M42" s="46">
         <f>M24*M15/365</f>
         <v/>
       </c>
-      <c r="N42" s="43">
+      <c r="N42" s="46">
         <f>N24*N15/365</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="18" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="26" t="n">
+      <c r="E43" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="26" t="n">
+      <c r="F43" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="26" t="n">
+      <c r="G43" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="26" t="n">
+      <c r="H43" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="26" t="n">
+      <c r="I43" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="16">
+      <c r="J43" s="18">
         <f>J25*J16/365</f>
         <v/>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="18">
         <f>K25*K16/365</f>
         <v/>
       </c>
-      <c r="L43" s="16">
+      <c r="L43" s="18">
         <f>L25*L16/365</f>
         <v/>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="18">
         <f>M25*M16/365</f>
         <v/>
       </c>
-      <c r="N43" s="16">
+      <c r="N43" s="18">
         <f>N25*N16/365</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="26" t="n">
+      <c r="E44" s="29" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="26" t="n">
+      <c r="F44" s="29" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="26" t="n">
+      <c r="G44" s="29" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="26" t="n">
+      <c r="H44" s="29" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="26" t="n">
+      <c r="I44" s="29" t="n">
         <v>67713</v>
       </c>
-      <c r="J44" s="16">
+      <c r="J44" s="18">
         <f>J95</f>
         <v/>
       </c>
-      <c r="K44" s="16">
+      <c r="K44" s="18">
         <f>K95</f>
         <v/>
       </c>
-      <c r="L44" s="16">
+      <c r="L44" s="18">
         <f>L95</f>
         <v/>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="18">
         <f>M95</f>
         <v/>
       </c>
-      <c r="N44" s="16">
+      <c r="N44" s="18">
         <f>N95</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="40" t="inlineStr">
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="C45" s="40" t="n"/>
-      <c r="D45" s="41" t="n"/>
-      <c r="E45" s="42">
+      <c r="C45" s="43" t="n"/>
+      <c r="D45" s="44" t="n"/>
+      <c r="E45" s="45">
         <f>SUM(E41:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="42">
+      <c r="F45" s="45">
         <f>SUM(F41:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="42">
+      <c r="G45" s="45">
         <f>SUM(G41:G44)</f>
         <v/>
       </c>
-      <c r="H45" s="42">
+      <c r="H45" s="45">
         <f>SUM(H41:H44)</f>
         <v/>
       </c>
-      <c r="I45" s="42">
+      <c r="I45" s="45">
         <f>SUM(I41:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="42">
+      <c r="J45" s="45">
         <f>SUM(J41:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="42">
+      <c r="K45" s="45">
         <f>SUM(K41:K44)</f>
         <v/>
       </c>
-      <c r="L45" s="42">
+      <c r="L45" s="45">
         <f>SUM(L41:L44)</f>
         <v/>
       </c>
-      <c r="M45" s="42">
+      <c r="M45" s="45">
         <f>SUM(M41:M44)</f>
         <v/>
       </c>
-      <c r="N45" s="42">
+      <c r="N45" s="45">
         <f>SUM(N41:N44)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="19" t="n"/>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="35" t="n"/>
-      <c r="F46" s="35" t="n"/>
-      <c r="G46" s="35" t="n"/>
-      <c r="H46" s="35" t="n"/>
-      <c r="I46" s="35" t="n"/>
-      <c r="J46" s="19" t="n"/>
-      <c r="K46" s="19" t="n"/>
-      <c r="L46" s="19" t="n"/>
-      <c r="M46" s="19" t="n"/>
-      <c r="N46" s="19" t="n"/>
+      <c r="B46" s="21" t="n"/>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="23" t="n"/>
+      <c r="E46" s="38" t="n"/>
+      <c r="F46" s="38" t="n"/>
+      <c r="G46" s="38" t="n"/>
+      <c r="H46" s="38" t="n"/>
+      <c r="I46" s="38" t="n"/>
+      <c r="J46" s="21" t="n"/>
+      <c r="K46" s="21" t="n"/>
+      <c r="L46" s="21" t="n"/>
+      <c r="M46" s="21" t="n"/>
+      <c r="N46" s="21" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
       </c>
-      <c r="E47" s="30" t="n"/>
-      <c r="F47" s="30" t="n"/>
-      <c r="G47" s="30" t="n"/>
-      <c r="H47" s="30" t="n"/>
-      <c r="I47" s="30" t="n"/>
+      <c r="E47" s="33" t="n"/>
+      <c r="F47" s="33" t="n"/>
+      <c r="G47" s="33" t="n"/>
+      <c r="H47" s="33" t="n"/>
+      <c r="I47" s="33" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E48" s="26" t="n">
+      <c r="E48" s="29" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="26" t="n">
+      <c r="F48" s="29" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="26" t="n">
+      <c r="G48" s="29" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="26" t="n">
+      <c r="H48" s="29" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="26" t="n">
+      <c r="I48" s="29" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="16">
+      <c r="J48" s="18">
         <f>J25*J17/365</f>
         <v/>
       </c>
-      <c r="K48" s="16">
+      <c r="K48" s="18">
         <f>K25*K17/365</f>
         <v/>
       </c>
-      <c r="L48" s="16">
+      <c r="L48" s="18">
         <f>L25*L17/365</f>
         <v/>
       </c>
-      <c r="M48" s="16">
+      <c r="M48" s="18">
         <f>M25*M17/365</f>
         <v/>
       </c>
-      <c r="N48" s="16">
+      <c r="N48" s="18">
         <f>N25*N17/365</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="18" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="26" t="n">
+      <c r="E49" s="29" t="n">
         <v>1009018</v>
       </c>
-      <c r="F49" s="26" t="n">
+      <c r="F49" s="29" t="n">
         <v>1823669</v>
       </c>
-      <c r="G49" s="26" t="n">
+      <c r="G49" s="29" t="n">
         <v>1811658</v>
       </c>
-      <c r="H49" s="26" t="n">
+      <c r="H49" s="29" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="26" t="n">
+      <c r="I49" s="29" t="n">
         <v>3055691</v>
       </c>
-      <c r="J49" s="16">
+      <c r="J49" s="18">
         <f>J100</f>
         <v/>
       </c>
-      <c r="K49" s="16">
+      <c r="K49" s="18">
         <f>K100</f>
         <v/>
       </c>
-      <c r="L49" s="16">
+      <c r="L49" s="18">
         <f>L100</f>
         <v/>
       </c>
-      <c r="M49" s="16">
+      <c r="M49" s="18">
         <f>M100</f>
         <v/>
       </c>
-      <c r="N49" s="16">
+      <c r="N49" s="18">
         <f>N100</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="32" t="inlineStr">
+      <c r="B50" s="35" t="inlineStr">
         <is>
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="C50" s="32" t="n"/>
-      <c r="D50" s="33" t="n"/>
-      <c r="E50" s="34">
+      <c r="C50" s="35" t="n"/>
+      <c r="D50" s="36" t="n"/>
+      <c r="E50" s="37">
         <f>SUM(E48:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="34">
+      <c r="F50" s="37">
         <f>SUM(F48:F49)</f>
         <v/>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="37">
         <f>SUM(G48:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="34">
+      <c r="H50" s="37">
         <f>SUM(H48:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="34">
+      <c r="I50" s="37">
         <f>SUM(I48:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="34">
+      <c r="J50" s="37">
         <f>SUM(J48:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="34">
+      <c r="K50" s="37">
         <f>SUM(K48:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="34">
+      <c r="L50" s="37">
         <f>SUM(L48:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="34">
+      <c r="M50" s="37">
         <f>SUM(M48:M49)</f>
         <v/>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="37">
         <f>SUM(N48:N49)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B51" s="21" t="inlineStr">
         <is>
           <t>Shareholder's Equity</t>
         </is>
       </c>
-      <c r="E51" s="30" t="n"/>
-      <c r="F51" s="30" t="n"/>
-      <c r="G51" s="30" t="n"/>
-      <c r="H51" s="30" t="n"/>
-      <c r="I51" s="30" t="n"/>
+      <c r="E51" s="33" t="n"/>
+      <c r="F51" s="33" t="n"/>
+      <c r="G51" s="33" t="n"/>
+      <c r="H51" s="33" t="n"/>
+      <c r="I51" s="33" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="26" t="n">
+      <c r="E52" s="29" t="n">
         <v>-3079536</v>
       </c>
-      <c r="F52" s="26" t="n">
+      <c r="F52" s="29" t="n">
         <v>-4326434</v>
       </c>
-      <c r="G52" s="26" t="n">
+      <c r="G52" s="29" t="n">
         <v>-4683035</v>
       </c>
-      <c r="H52" s="26" t="n">
+      <c r="H52" s="29" t="n">
         <v>-5516590</v>
       </c>
-      <c r="I52" s="26" t="n">
+      <c r="I52" s="29" t="n">
         <v>-6909825</v>
       </c>
-      <c r="J52" s="16">
+      <c r="J52" s="18">
         <f>I52+J20</f>
         <v/>
       </c>
-      <c r="K52" s="16">
+      <c r="K52" s="18">
         <f>J52+K20</f>
         <v/>
       </c>
-      <c r="L52" s="16">
+      <c r="L52" s="18">
         <f>K52+L20</f>
         <v/>
       </c>
-      <c r="M52" s="16">
+      <c r="M52" s="18">
         <f>L52+M20</f>
         <v/>
       </c>
-      <c r="N52" s="16">
+      <c r="N52" s="18">
         <f>M52+N20</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="18" t="inlineStr">
         <is>
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="E53" s="26" t="n">
+      <c r="E53" s="29" t="n">
         <v>2585143</v>
       </c>
-      <c r="F53" s="26" t="n">
+      <c r="F53" s="29" t="n">
         <v>2958684</v>
       </c>
-      <c r="G53" s="26" t="n">
+      <c r="G53" s="29" t="n">
         <v>3388059</v>
       </c>
-      <c r="H53" s="26" t="n">
+      <c r="H53" s="29" t="n">
         <v>3900870</v>
       </c>
-      <c r="I53" s="26" t="n">
+      <c r="I53" s="29" t="n">
         <v>4552816</v>
       </c>
-      <c r="J53" s="16">
+      <c r="J53" s="18">
         <f>I53+J36</f>
         <v/>
       </c>
-      <c r="K53" s="16">
+      <c r="K53" s="18">
         <f>J53+K36</f>
         <v/>
       </c>
-      <c r="L53" s="16">
+      <c r="L53" s="18">
         <f>K53+L36</f>
         <v/>
       </c>
-      <c r="M53" s="16">
+      <c r="M53" s="18">
         <f>L53+M36</f>
         <v/>
       </c>
-      <c r="N53" s="16">
+      <c r="N53" s="18">
         <f>M53+N36</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="44" t="inlineStr">
+      <c r="B54" s="47" t="inlineStr">
         <is>
           <t>Shareholder's Equity</t>
         </is>
       </c>
-      <c r="C54" s="44" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="46">
+      <c r="C54" s="47" t="n"/>
+      <c r="D54" s="48" t="n"/>
+      <c r="E54" s="49">
         <f>SUM(E52:E53)</f>
         <v/>
       </c>
-      <c r="F54" s="46">
+      <c r="F54" s="49">
         <f>SUM(F52:F53)</f>
         <v/>
       </c>
-      <c r="G54" s="46">
+      <c r="G54" s="49">
         <f>SUM(G52:G53)</f>
         <v/>
       </c>
-      <c r="H54" s="46">
+      <c r="H54" s="49">
         <f>SUM(H52:H53)</f>
         <v/>
       </c>
-      <c r="I54" s="46">
+      <c r="I54" s="49">
         <f>SUM(I52:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="46">
+      <c r="J54" s="49">
         <f>SUM(J52:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="46">
+      <c r="K54" s="49">
         <f>SUM(K52:K53)</f>
         <v/>
       </c>
-      <c r="L54" s="46">
+      <c r="L54" s="49">
         <f>SUM(L52:L53)</f>
         <v/>
       </c>
-      <c r="M54" s="46">
+      <c r="M54" s="49">
         <f>SUM(M52:M53)</f>
         <v/>
       </c>
-      <c r="N54" s="46">
+      <c r="N54" s="49">
         <f>SUM(N52:N53)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="40" t="inlineStr">
+      <c r="B55" s="43" t="inlineStr">
         <is>
           <t>Total Liabilities &amp; Shareholder's Equity</t>
         </is>
       </c>
-      <c r="C55" s="40" t="n"/>
-      <c r="D55" s="41" t="n"/>
-      <c r="E55" s="42">
+      <c r="C55" s="43" t="n"/>
+      <c r="D55" s="44" t="n"/>
+      <c r="E55" s="45">
         <f>E50+E54</f>
         <v/>
       </c>
-      <c r="F55" s="42">
+      <c r="F55" s="45">
         <f>F50+F54</f>
         <v/>
       </c>
-      <c r="G55" s="42">
+      <c r="G55" s="45">
         <f>G50+G54</f>
         <v/>
       </c>
-      <c r="H55" s="42">
+      <c r="H55" s="45">
         <f>H50+H54</f>
         <v/>
       </c>
-      <c r="I55" s="42">
+      <c r="I55" s="45">
         <f>I50+I54</f>
         <v/>
       </c>
-      <c r="J55" s="42">
+      <c r="J55" s="45">
         <f>J50+J54</f>
         <v/>
       </c>
-      <c r="K55" s="42">
+      <c r="K55" s="45">
         <f>K50+K54</f>
         <v/>
       </c>
-      <c r="L55" s="42">
+      <c r="L55" s="45">
         <f>L50+L54</f>
         <v/>
       </c>
-      <c r="M55" s="42">
+      <c r="M55" s="45">
         <f>M50+M54</f>
         <v/>
       </c>
-      <c r="N55" s="42">
+      <c r="N55" s="45">
         <f>N50+N54</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="E56" s="30" t="n"/>
-      <c r="F56" s="30" t="n"/>
-      <c r="G56" s="30" t="n"/>
-      <c r="H56" s="30" t="n"/>
-      <c r="I56" s="30" t="n"/>
-      <c r="J56" s="30" t="n"/>
-      <c r="K56" s="30" t="n"/>
-      <c r="L56" s="30" t="n"/>
-      <c r="M56" s="30" t="n"/>
-      <c r="N56" s="30" t="n"/>
+      <c r="E56" s="33" t="n"/>
+      <c r="F56" s="33" t="n"/>
+      <c r="G56" s="33" t="n"/>
+      <c r="H56" s="33" t="n"/>
+      <c r="I56" s="33" t="n"/>
+      <c r="J56" s="33" t="n"/>
+      <c r="K56" s="33" t="n"/>
+      <c r="L56" s="33" t="n"/>
+      <c r="M56" s="33" t="n"/>
+      <c r="N56" s="33" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="27" t="inlineStr">
+      <c r="B57" s="30" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C57" s="47" t="n"/>
-      <c r="D57" s="48" t="n"/>
-      <c r="E57" s="49">
+      <c r="C57" s="50" t="n"/>
+      <c r="D57" s="51" t="n"/>
+      <c r="E57" s="52">
         <f>E55-E45</f>
         <v/>
       </c>
-      <c r="F57" s="49">
+      <c r="F57" s="52">
         <f>F55-F45</f>
         <v/>
       </c>
-      <c r="G57" s="49">
+      <c r="G57" s="52">
         <f>G55-G45</f>
         <v/>
       </c>
-      <c r="H57" s="49">
+      <c r="H57" s="52">
         <f>H55-H45</f>
         <v/>
       </c>
-      <c r="I57" s="49">
+      <c r="I57" s="52">
         <f>I55-I45</f>
         <v/>
       </c>
-      <c r="J57" s="49">
+      <c r="J57" s="52">
         <f>J55-J45</f>
         <v/>
       </c>
-      <c r="K57" s="49">
+      <c r="K57" s="52">
         <f>K55-K45</f>
         <v/>
       </c>
-      <c r="L57" s="49">
+      <c r="L57" s="52">
         <f>L55-L45</f>
         <v/>
       </c>
-      <c r="M57" s="49">
+      <c r="M57" s="52">
         <f>M55-M45</f>
         <v/>
       </c>
-      <c r="N57" s="49">
+      <c r="N57" s="52">
         <f>N55-N45</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="47" t="n"/>
-      <c r="C58" s="47" t="n"/>
-      <c r="D58" s="48" t="n"/>
-      <c r="E58" s="47" t="n"/>
-      <c r="F58" s="47" t="n"/>
-      <c r="G58" s="47" t="n"/>
-      <c r="H58" s="47" t="n"/>
-      <c r="I58" s="47" t="n"/>
-      <c r="J58" s="47" t="n"/>
-      <c r="K58" s="47" t="n"/>
-      <c r="L58" s="47" t="n"/>
-      <c r="M58" s="47" t="n"/>
-      <c r="N58" s="47" t="n"/>
+      <c r="B58" s="50" t="n"/>
+      <c r="C58" s="50" t="n"/>
+      <c r="D58" s="51" t="n"/>
+      <c r="E58" s="50" t="n"/>
+      <c r="F58" s="50" t="n"/>
+      <c r="G58" s="50" t="n"/>
+      <c r="H58" s="50" t="n"/>
+      <c r="I58" s="50" t="n"/>
+      <c r="J58" s="50" t="n"/>
+      <c r="K58" s="50" t="n"/>
+      <c r="L58" s="50" t="n"/>
+      <c r="M58" s="50" t="n"/>
+      <c r="N58" s="50" t="n"/>
     </row>
     <row r="59">
-      <c r="E59" s="30" t="n"/>
-      <c r="F59" s="30" t="n"/>
-      <c r="G59" s="30" t="n"/>
-      <c r="H59" s="30" t="n"/>
-      <c r="I59" s="30" t="n"/>
+      <c r="E59" s="33" t="n"/>
+      <c r="F59" s="33" t="n"/>
+      <c r="G59" s="33" t="n"/>
+      <c r="H59" s="33" t="n"/>
+      <c r="I59" s="33" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="18" t="inlineStr">
+      <c r="B60" s="20" t="inlineStr">
         <is>
           <t>Cash Flow Statement</t>
         </is>
       </c>
-      <c r="C60" s="18" t="n"/>
-      <c r="D60" s="18" t="n"/>
-      <c r="E60" s="18" t="n"/>
-      <c r="F60" s="18" t="n"/>
-      <c r="G60" s="18" t="n"/>
-      <c r="H60" s="18" t="n"/>
-      <c r="I60" s="18" t="n"/>
-      <c r="J60" s="18" t="n"/>
-      <c r="K60" s="18" t="n"/>
-      <c r="L60" s="18" t="n"/>
-      <c r="M60" s="18" t="n"/>
-      <c r="N60" s="18" t="n"/>
+      <c r="C60" s="20" t="n"/>
+      <c r="D60" s="20" t="n"/>
+      <c r="E60" s="20" t="n"/>
+      <c r="F60" s="20" t="n"/>
+      <c r="G60" s="20" t="n"/>
+      <c r="H60" s="20" t="n"/>
+      <c r="I60" s="20" t="n"/>
+      <c r="J60" s="20" t="n"/>
+      <c r="K60" s="20" t="n"/>
+      <c r="L60" s="20" t="n"/>
+      <c r="M60" s="20" t="n"/>
+      <c r="N60" s="20" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="19" t="inlineStr">
+      <c r="B61" s="21" t="inlineStr">
         <is>
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="E61" s="30" t="n"/>
-      <c r="F61" s="30" t="n"/>
-      <c r="G61" s="30" t="n"/>
-      <c r="H61" s="30" t="n"/>
-      <c r="I61" s="30" t="n"/>
+      <c r="E61" s="33" t="n"/>
+      <c r="F61" s="33" t="n"/>
+      <c r="G61" s="33" t="n"/>
+      <c r="H61" s="33" t="n"/>
+      <c r="I61" s="33" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B62" s="18" t="inlineStr">
         <is>
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="E62" s="16">
+      <c r="E62" s="18">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F62" s="16">
+      <c r="F62" s="18">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G62" s="16">
+      <c r="G62" s="18">
         <f>G36</f>
         <v/>
       </c>
-      <c r="H62" s="16">
+      <c r="H62" s="18">
         <f>H36</f>
         <v/>
       </c>
-      <c r="I62" s="16">
+      <c r="I62" s="18">
         <f>I36</f>
         <v/>
       </c>
-      <c r="J62" s="16">
+      <c r="J62" s="18">
         <f>J36</f>
         <v/>
       </c>
-      <c r="K62" s="16">
+      <c r="K62" s="18">
         <f>K36</f>
         <v/>
       </c>
-      <c r="L62" s="16">
+      <c r="L62" s="18">
         <f>L36</f>
         <v/>
       </c>
-      <c r="M62" s="16">
+      <c r="M62" s="18">
         <f>M36</f>
         <v/>
       </c>
-      <c r="N62" s="16">
+      <c r="N62" s="18">
         <f>N36</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="16" t="inlineStr">
+      <c r="B63" s="18" t="inlineStr">
         <is>
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="18">
         <f>+E30</f>
         <v/>
       </c>
-      <c r="F63" s="16">
+      <c r="F63" s="18">
         <f>+F30</f>
         <v/>
       </c>
-      <c r="G63" s="16">
+      <c r="G63" s="18">
         <f>+G30</f>
         <v/>
       </c>
-      <c r="H63" s="16">
+      <c r="H63" s="18">
         <f>+H30</f>
         <v/>
       </c>
-      <c r="I63" s="16">
+      <c r="I63" s="18">
         <f>+I30</f>
         <v/>
       </c>
-      <c r="J63" s="16">
+      <c r="J63" s="18">
         <f>+J30</f>
         <v/>
       </c>
-      <c r="K63" s="16">
+      <c r="K63" s="18">
         <f>+K30</f>
         <v/>
       </c>
-      <c r="L63" s="16">
+      <c r="L63" s="18">
         <f>+L30</f>
         <v/>
       </c>
-      <c r="M63" s="16">
+      <c r="M63" s="18">
         <f>+M30</f>
         <v/>
       </c>
-      <c r="N63" s="16">
+      <c r="N63" s="18">
         <f>+N30</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="16" t="inlineStr">
+      <c r="B64" s="18" t="inlineStr">
         <is>
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="E64" s="26" t="n">
+      <c r="E64" s="29" t="n">
         <v>-19789</v>
       </c>
-      <c r="F64" s="26" t="n">
+      <c r="F64" s="29" t="n">
         <v>13779</v>
       </c>
-      <c r="G64" s="26" t="n">
+      <c r="G64" s="29" t="n">
         <v>63801</v>
       </c>
-      <c r="H64" s="26" t="n">
+      <c r="H64" s="29" t="n">
         <v>35231</v>
       </c>
-      <c r="I64" s="26" t="n">
+      <c r="I64" s="29" t="n">
         <v>92664</v>
       </c>
-      <c r="J64" s="16">
+      <c r="J64" s="18">
         <f>J89</f>
         <v/>
       </c>
-      <c r="K64" s="16">
+      <c r="K64" s="18">
         <f>K89</f>
         <v/>
       </c>
-      <c r="L64" s="16">
+      <c r="L64" s="18">
         <f>L89</f>
         <v/>
       </c>
-      <c r="M64" s="16">
+      <c r="M64" s="18">
         <f>M89</f>
         <v/>
       </c>
-      <c r="N64" s="16">
+      <c r="N64" s="18">
         <f>N89</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="32" t="inlineStr">
+      <c r="B65" s="35" t="inlineStr">
         <is>
           <t>Cash from Operations</t>
         </is>
       </c>
-      <c r="C65" s="50" t="n"/>
-      <c r="D65" s="51" t="n"/>
-      <c r="E65" s="34">
+      <c r="C65" s="53" t="n"/>
+      <c r="D65" s="54" t="n"/>
+      <c r="E65" s="37">
         <f>E62+E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="34">
+      <c r="F65" s="37">
         <f>F62+F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="34">
+      <c r="G65" s="37">
         <f>G62+G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="34">
+      <c r="H65" s="37">
         <f>H62+H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="34">
+      <c r="I65" s="37">
         <f>I62+I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="34">
+      <c r="J65" s="37">
         <f>J62+J63-J64</f>
         <v/>
       </c>
-      <c r="K65" s="34">
+      <c r="K65" s="37">
         <f>K62+K63-K64</f>
         <v/>
       </c>
-      <c r="L65" s="34">
+      <c r="L65" s="37">
         <f>L62+L63-L64</f>
         <v/>
       </c>
-      <c r="M65" s="34">
+      <c r="M65" s="37">
         <f>M62+M63-M64</f>
         <v/>
       </c>
-      <c r="N65" s="34">
+      <c r="N65" s="37">
         <f>N62+N63-N64</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="19" t="n"/>
-      <c r="C66" s="16" t="n"/>
-      <c r="D66" s="20" t="n"/>
-      <c r="E66" s="35" t="n"/>
-      <c r="F66" s="35" t="n"/>
-      <c r="G66" s="35" t="n"/>
-      <c r="H66" s="35" t="n"/>
-      <c r="I66" s="35" t="n"/>
-      <c r="J66" s="19" t="n"/>
-      <c r="K66" s="19" t="n"/>
-      <c r="L66" s="19" t="n"/>
-      <c r="M66" s="19" t="n"/>
-      <c r="N66" s="19" t="n"/>
+      <c r="B66" s="21" t="n"/>
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="22" t="n"/>
+      <c r="E66" s="38" t="n"/>
+      <c r="F66" s="38" t="n"/>
+      <c r="G66" s="38" t="n"/>
+      <c r="H66" s="38" t="n"/>
+      <c r="I66" s="38" t="n"/>
+      <c r="J66" s="21" t="n"/>
+      <c r="K66" s="21" t="n"/>
+      <c r="L66" s="21" t="n"/>
+      <c r="M66" s="21" t="n"/>
+      <c r="N66" s="21" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="19" t="inlineStr">
+      <c r="B67" s="21" t="inlineStr">
         <is>
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="E67" s="30" t="n"/>
-      <c r="F67" s="30" t="n"/>
-      <c r="G67" s="30" t="n"/>
-      <c r="H67" s="30" t="n"/>
-      <c r="I67" s="30" t="n"/>
-      <c r="J67" s="16" t="n"/>
-      <c r="K67" s="16" t="n"/>
-      <c r="L67" s="16" t="n"/>
-      <c r="M67" s="16" t="n"/>
-      <c r="N67" s="16" t="n"/>
+      <c r="E67" s="33" t="n"/>
+      <c r="F67" s="33" t="n"/>
+      <c r="G67" s="33" t="n"/>
+      <c r="H67" s="33" t="n"/>
+      <c r="I67" s="33" t="n"/>
+      <c r="J67" s="18" t="n"/>
+      <c r="K67" s="18" t="n"/>
+      <c r="L67" s="18" t="n"/>
+      <c r="M67" s="18" t="n"/>
+      <c r="N67" s="18" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="16" t="inlineStr">
+      <c r="B68" s="18" t="inlineStr">
         <is>
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E68" s="26" t="n">
+      <c r="E68" s="29" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="26" t="n">
+      <c r="F68" s="29" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="26" t="n">
+      <c r="G68" s="29" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="26" t="n">
+      <c r="H68" s="29" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="26" t="n">
+      <c r="I68" s="29" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="16">
+      <c r="J68" s="18">
         <f>J18</f>
         <v/>
       </c>
-      <c r="K68" s="16">
+      <c r="K68" s="18">
         <f>K18</f>
         <v/>
       </c>
-      <c r="L68" s="16">
+      <c r="L68" s="18">
         <f>L18</f>
         <v/>
       </c>
-      <c r="M68" s="16">
+      <c r="M68" s="18">
         <f>M18</f>
         <v/>
       </c>
-      <c r="N68" s="16">
+      <c r="N68" s="18">
         <f>N18</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="32" t="inlineStr">
+      <c r="B69" s="35" t="inlineStr">
         <is>
           <t>Cash from Investing</t>
         </is>
       </c>
-      <c r="C69" s="50" t="n"/>
-      <c r="D69" s="51" t="n"/>
-      <c r="E69" s="34">
+      <c r="C69" s="53" t="n"/>
+      <c r="D69" s="54" t="n"/>
+      <c r="E69" s="37">
         <f>SUM(E68)</f>
         <v/>
       </c>
-      <c r="F69" s="34">
+      <c r="F69" s="37">
         <f>SUM(F68)</f>
         <v/>
       </c>
-      <c r="G69" s="34">
+      <c r="G69" s="37">
         <f>SUM(G68)</f>
         <v/>
       </c>
-      <c r="H69" s="34">
+      <c r="H69" s="37">
         <f>SUM(H68)</f>
         <v/>
       </c>
-      <c r="I69" s="34">
+      <c r="I69" s="37">
         <f>SUM(I68)</f>
         <v/>
       </c>
-      <c r="J69" s="34">
+      <c r="J69" s="37">
         <f>SUM(J68)</f>
         <v/>
       </c>
-      <c r="K69" s="34">
+      <c r="K69" s="37">
         <f>SUM(K68)</f>
         <v/>
       </c>
-      <c r="L69" s="34">
+      <c r="L69" s="37">
         <f>SUM(L68)</f>
         <v/>
       </c>
-      <c r="M69" s="34">
+      <c r="M69" s="37">
         <f>SUM(M68)</f>
         <v/>
       </c>
-      <c r="N69" s="34">
+      <c r="N69" s="37">
         <f>SUM(N68)</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="19" t="n"/>
-      <c r="C70" s="16" t="n"/>
-      <c r="D70" s="20" t="n"/>
-      <c r="E70" s="35" t="n"/>
-      <c r="F70" s="35" t="n"/>
-      <c r="G70" s="35" t="n"/>
-      <c r="H70" s="35" t="n"/>
-      <c r="I70" s="35" t="n"/>
-      <c r="J70" s="19" t="n"/>
-      <c r="K70" s="19" t="n"/>
-      <c r="L70" s="19" t="n"/>
-      <c r="M70" s="19" t="n"/>
-      <c r="N70" s="19" t="n"/>
+      <c r="B70" s="21" t="n"/>
+      <c r="C70" s="18" t="n"/>
+      <c r="D70" s="22" t="n"/>
+      <c r="E70" s="38" t="n"/>
+      <c r="F70" s="38" t="n"/>
+      <c r="G70" s="38" t="n"/>
+      <c r="H70" s="38" t="n"/>
+      <c r="I70" s="38" t="n"/>
+      <c r="J70" s="21" t="n"/>
+      <c r="K70" s="21" t="n"/>
+      <c r="L70" s="21" t="n"/>
+      <c r="M70" s="21" t="n"/>
+      <c r="N70" s="21" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="19" t="inlineStr">
+      <c r="B71" s="21" t="inlineStr">
         <is>
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="E71" s="30" t="n"/>
-      <c r="F71" s="30" t="n"/>
-      <c r="G71" s="30" t="n"/>
-      <c r="H71" s="30" t="n"/>
-      <c r="I71" s="30" t="n"/>
-      <c r="J71" s="16" t="n"/>
-      <c r="K71" s="16" t="n"/>
-      <c r="L71" s="16" t="n"/>
-      <c r="M71" s="16" t="n"/>
-      <c r="N71" s="16" t="n"/>
+      <c r="E71" s="33" t="n"/>
+      <c r="F71" s="33" t="n"/>
+      <c r="G71" s="33" t="n"/>
+      <c r="H71" s="33" t="n"/>
+      <c r="I71" s="33" t="n"/>
+      <c r="J71" s="18" t="n"/>
+      <c r="K71" s="18" t="n"/>
+      <c r="L71" s="18" t="n"/>
+      <c r="M71" s="18" t="n"/>
+      <c r="N71" s="18" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="16" t="inlineStr">
+      <c r="B72" s="18" t="inlineStr">
         <is>
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="26" t="n">
+      <c r="E72" s="29" t="n">
         <v>269583</v>
       </c>
-      <c r="F72" s="26" t="n">
+      <c r="F72" s="29" t="n">
         <v>814651</v>
       </c>
-      <c r="G72" s="26" t="n">
+      <c r="G72" s="29" t="n">
         <v>-12011</v>
       </c>
-      <c r="H72" s="26" t="n">
+      <c r="H72" s="29" t="n">
         <v>397363</v>
       </c>
-      <c r="I72" s="26" t="n">
+      <c r="I72" s="29" t="n">
         <v>846670</v>
       </c>
-      <c r="J72" s="16">
+      <c r="J72" s="18">
         <f>J19</f>
         <v/>
       </c>
-      <c r="K72" s="16">
+      <c r="K72" s="18">
         <f>K19</f>
         <v/>
       </c>
-      <c r="L72" s="16">
+      <c r="L72" s="18">
         <f>L19</f>
         <v/>
       </c>
-      <c r="M72" s="16">
+      <c r="M72" s="18">
         <f>M19</f>
         <v/>
       </c>
-      <c r="N72" s="16">
+      <c r="N72" s="18">
         <f>N19</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="16" t="inlineStr">
+      <c r="B73" s="18" t="inlineStr">
         <is>
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="26" t="n">
+      <c r="E73" s="29" t="n">
         <v>-661519</v>
       </c>
-      <c r="F73" s="26" t="n">
+      <c r="F73" s="29" t="n">
         <v>-1251001</v>
       </c>
-      <c r="G73" s="26" t="n">
+      <c r="G73" s="29" t="n">
         <v>-360388</v>
       </c>
-      <c r="H73" s="26" t="n">
+      <c r="H73" s="29" t="n">
         <v>-849330</v>
       </c>
-      <c r="I73" s="26" t="n">
+      <c r="I73" s="29" t="n">
         <v>-1398028</v>
       </c>
-      <c r="J73" s="16">
+      <c r="J73" s="18">
         <f>J20</f>
         <v/>
       </c>
-      <c r="K73" s="16">
+      <c r="K73" s="18">
         <f>K20</f>
         <v/>
       </c>
-      <c r="L73" s="16">
+      <c r="L73" s="18">
         <f>L20</f>
         <v/>
       </c>
-      <c r="M73" s="16">
+      <c r="M73" s="18">
         <f>M20</f>
         <v/>
       </c>
-      <c r="N73" s="16">
+      <c r="N73" s="18">
         <f>N20</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="32" t="inlineStr">
+      <c r="B74" s="35" t="inlineStr">
         <is>
           <t>Cash from Financing</t>
         </is>
       </c>
-      <c r="C74" s="50" t="n"/>
-      <c r="D74" s="51" t="n"/>
-      <c r="E74" s="34">
+      <c r="C74" s="53" t="n"/>
+      <c r="D74" s="54" t="n"/>
+      <c r="E74" s="37">
         <f>SUM(E72:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="34">
+      <c r="F74" s="37">
         <f>SUM(F72:F73)</f>
         <v/>
       </c>
-      <c r="G74" s="34">
+      <c r="G74" s="37">
         <f>SUM(G72:G73)</f>
         <v/>
       </c>
-      <c r="H74" s="34">
+      <c r="H74" s="37">
         <f>SUM(H72:H73)</f>
         <v/>
       </c>
-      <c r="I74" s="34">
+      <c r="I74" s="37">
         <f>SUM(I72:I73)</f>
         <v/>
       </c>
-      <c r="J74" s="34">
+      <c r="J74" s="37">
         <f>SUM(J72:J73)</f>
         <v/>
       </c>
-      <c r="K74" s="34">
+      <c r="K74" s="37">
         <f>SUM(K72:K73)</f>
         <v/>
       </c>
-      <c r="L74" s="34">
+      <c r="L74" s="37">
         <f>SUM(L72:L73)</f>
         <v/>
       </c>
-      <c r="M74" s="34">
+      <c r="M74" s="37">
         <f>SUM(M72:M73)</f>
         <v/>
       </c>
-      <c r="N74" s="34">
+      <c r="N74" s="37">
         <f>SUM(N72:N73)</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="19" t="n"/>
-      <c r="C75" s="16" t="n"/>
-      <c r="D75" s="20" t="n"/>
-      <c r="E75" s="35" t="n"/>
-      <c r="F75" s="35" t="n"/>
-      <c r="G75" s="35" t="n"/>
-      <c r="H75" s="35" t="n"/>
-      <c r="I75" s="35" t="n"/>
-      <c r="J75" s="19" t="n"/>
-      <c r="K75" s="19" t="n"/>
-      <c r="L75" s="19" t="n"/>
-      <c r="M75" s="19" t="n"/>
-      <c r="N75" s="19" t="n"/>
+      <c r="B75" s="21" t="n"/>
+      <c r="C75" s="18" t="n"/>
+      <c r="D75" s="22" t="n"/>
+      <c r="E75" s="38" t="n"/>
+      <c r="F75" s="38" t="n"/>
+      <c r="G75" s="38" t="n"/>
+      <c r="H75" s="38" t="n"/>
+      <c r="I75" s="38" t="n"/>
+      <c r="J75" s="21" t="n"/>
+      <c r="K75" s="21" t="n"/>
+      <c r="L75" s="21" t="n"/>
+      <c r="M75" s="21" t="n"/>
+      <c r="N75" s="21" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="16" t="inlineStr">
+      <c r="B76" s="18" t="inlineStr">
         <is>
           <t>Net Increase (decrease) in Cash</t>
         </is>
       </c>
-      <c r="E76" s="25">
+      <c r="E76" s="28">
         <f>E65-E69+E74</f>
         <v/>
       </c>
-      <c r="F76" s="25">
+      <c r="F76" s="28">
         <f>F65-F69+F74</f>
         <v/>
       </c>
-      <c r="G76" s="25">
+      <c r="G76" s="28">
         <f>G65-G69+G74</f>
         <v/>
       </c>
-      <c r="H76" s="25">
+      <c r="H76" s="28">
         <f>H65-H69+H74</f>
         <v/>
       </c>
-      <c r="I76" s="25">
+      <c r="I76" s="28">
         <f>I65-I69+I74</f>
         <v/>
       </c>
-      <c r="J76" s="25">
+      <c r="J76" s="28">
         <f>J65-J69+J74</f>
         <v/>
       </c>
-      <c r="K76" s="25">
+      <c r="K76" s="28">
         <f>K65-K69+K74</f>
         <v/>
       </c>
-      <c r="L76" s="25">
+      <c r="L76" s="28">
         <f>L65-L69+L74</f>
         <v/>
       </c>
-      <c r="M76" s="25">
+      <c r="M76" s="28">
         <f>M65-M69+M74</f>
         <v/>
       </c>
-      <c r="N76" s="25">
+      <c r="N76" s="28">
         <f>N65-N69+N74</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="16" t="inlineStr">
+      <c r="B77" s="18" t="inlineStr">
         <is>
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="16">
+      <c r="E77" s="18">
         <f>D78</f>
         <v/>
       </c>
-      <c r="F77" s="26" t="n">
+      <c r="F77" s="29" t="n">
         <v>195354</v>
       </c>
-      <c r="G77" s="26" t="n">
+      <c r="G77" s="29" t="n">
         <v>133202</v>
       </c>
-      <c r="H77" s="26" t="n">
+      <c r="H77" s="29" t="n">
         <v>136778</v>
       </c>
-      <c r="I77" s="26" t="n">
+      <c r="I77" s="29" t="n">
         <v>150667</v>
       </c>
-      <c r="J77" s="16">
+      <c r="J77" s="18">
         <f>+I78</f>
         <v/>
       </c>
-      <c r="K77" s="16">
+      <c r="K77" s="18">
         <f>+J78</f>
         <v/>
       </c>
-      <c r="L77" s="16">
+      <c r="L77" s="18">
         <f>+K78</f>
         <v/>
       </c>
-      <c r="M77" s="16">
+      <c r="M77" s="18">
         <f>+L78</f>
         <v/>
       </c>
-      <c r="N77" s="16">
+      <c r="N77" s="18">
         <f>+M78</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="32" t="inlineStr">
+      <c r="B78" s="35" t="inlineStr">
         <is>
           <t>Closing Cash Balance</t>
         </is>
       </c>
-      <c r="C78" s="50" t="n"/>
-      <c r="D78" s="52" t="n">
+      <c r="C78" s="53" t="n"/>
+      <c r="D78" s="55" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="34">
+      <c r="E78" s="37">
         <f>SUM(E76:E77)</f>
         <v/>
       </c>
-      <c r="F78" s="34">
+      <c r="F78" s="37">
         <f>SUM(F76:F77)</f>
         <v/>
       </c>
-      <c r="G78" s="34">
+      <c r="G78" s="37">
         <f>SUM(G76:G77)</f>
         <v/>
       </c>
-      <c r="H78" s="34">
+      <c r="H78" s="37">
         <f>SUM(H76:H77)</f>
         <v/>
       </c>
-      <c r="I78" s="34">
+      <c r="I78" s="37">
         <f>SUM(I76:I77)</f>
         <v/>
       </c>
-      <c r="J78" s="34">
+      <c r="J78" s="37">
         <f>SUM(J76:J77)</f>
         <v/>
       </c>
-      <c r="K78" s="34">
+      <c r="K78" s="37">
         <f>SUM(K76:K77)</f>
         <v/>
       </c>
-      <c r="L78" s="34">
+      <c r="L78" s="37">
         <f>SUM(L76:L77)</f>
         <v/>
       </c>
-      <c r="M78" s="34">
+      <c r="M78" s="37">
         <f>SUM(M76:M77)</f>
         <v/>
       </c>
-      <c r="N78" s="34">
+      <c r="N78" s="37">
         <f>SUM(N76:N77)</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="19" t="n"/>
-      <c r="E79" s="35" t="n"/>
-      <c r="F79" s="30" t="n"/>
-      <c r="G79" s="30" t="n"/>
-      <c r="H79" s="30" t="n"/>
-      <c r="I79" s="30" t="n"/>
+      <c r="B79" s="21" t="n"/>
+      <c r="E79" s="38" t="n"/>
+      <c r="F79" s="33" t="n"/>
+      <c r="G79" s="33" t="n"/>
+      <c r="H79" s="33" t="n"/>
+      <c r="I79" s="33" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="27" t="inlineStr">
+      <c r="B80" s="30" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C80" s="47" t="n"/>
-      <c r="D80" s="48" t="n"/>
-      <c r="E80" s="49">
+      <c r="C80" s="50" t="n"/>
+      <c r="D80" s="51" t="n"/>
+      <c r="E80" s="52">
         <f>E78-E41</f>
         <v/>
       </c>
-      <c r="F80" s="49">
+      <c r="F80" s="52">
         <f>F78-F41</f>
         <v/>
       </c>
-      <c r="G80" s="49">
+      <c r="G80" s="52">
         <f>G78-G41</f>
         <v/>
       </c>
-      <c r="H80" s="49">
+      <c r="H80" s="52">
         <f>H78-H41</f>
         <v/>
       </c>
-      <c r="I80" s="49">
+      <c r="I80" s="52">
         <f>I78-I41</f>
         <v/>
       </c>
-      <c r="J80" s="49">
+      <c r="J80" s="52">
         <f>J78-J41</f>
         <v/>
       </c>
-      <c r="K80" s="49">
+      <c r="K80" s="52">
         <f>K78-K41</f>
         <v/>
       </c>
-      <c r="L80" s="49">
+      <c r="L80" s="52">
         <f>L78-L41</f>
         <v/>
       </c>
-      <c r="M80" s="49">
+      <c r="M80" s="52">
         <f>M78-M41</f>
         <v/>
       </c>
-      <c r="N80" s="49">
+      <c r="N80" s="52">
         <f>N78-N41</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="19" t="n"/>
-      <c r="E81" s="35" t="n"/>
-      <c r="F81" s="30" t="n"/>
-      <c r="G81" s="30" t="n"/>
-      <c r="H81" s="30" t="n"/>
-      <c r="I81" s="30" t="n"/>
+      <c r="B81" s="21" t="n"/>
+      <c r="E81" s="38" t="n"/>
+      <c r="F81" s="33" t="n"/>
+      <c r="G81" s="33" t="n"/>
+      <c r="H81" s="33" t="n"/>
+      <c r="I81" s="33" t="n"/>
     </row>
     <row r="82">
-      <c r="E82" s="30" t="n"/>
-      <c r="F82" s="30" t="n"/>
-      <c r="G82" s="30" t="n"/>
-      <c r="H82" s="30" t="n"/>
-      <c r="I82" s="30" t="n"/>
+      <c r="E82" s="33" t="n"/>
+      <c r="F82" s="33" t="n"/>
+      <c r="G82" s="33" t="n"/>
+      <c r="H82" s="33" t="n"/>
+      <c r="I82" s="33" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="18" t="inlineStr">
+      <c r="B83" s="20" t="inlineStr">
         <is>
           <t>Supporting Schedules</t>
         </is>
       </c>
-      <c r="C83" s="18" t="n"/>
-      <c r="D83" s="18" t="n"/>
-      <c r="E83" s="18" t="n"/>
-      <c r="F83" s="18" t="n"/>
-      <c r="G83" s="18" t="n"/>
-      <c r="H83" s="18" t="n"/>
-      <c r="I83" s="18" t="n"/>
-      <c r="J83" s="18" t="n"/>
-      <c r="K83" s="18" t="n"/>
-      <c r="L83" s="18" t="n"/>
-      <c r="M83" s="18" t="n"/>
-      <c r="N83" s="18" t="n"/>
+      <c r="C83" s="20" t="n"/>
+      <c r="D83" s="20" t="n"/>
+      <c r="E83" s="20" t="n"/>
+      <c r="F83" s="20" t="n"/>
+      <c r="G83" s="20" t="n"/>
+      <c r="H83" s="20" t="n"/>
+      <c r="I83" s="20" t="n"/>
+      <c r="J83" s="20" t="n"/>
+      <c r="K83" s="20" t="n"/>
+      <c r="L83" s="20" t="n"/>
+      <c r="M83" s="20" t="n"/>
+      <c r="N83" s="20" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="19" t="inlineStr">
+      <c r="B84" s="21" t="inlineStr">
         <is>
           <t>Working Capital Schedule</t>
         </is>
       </c>
-      <c r="F84" s="30" t="n"/>
-      <c r="G84" s="30" t="n"/>
-      <c r="H84" s="30" t="n"/>
-      <c r="I84" s="30" t="n"/>
+      <c r="F84" s="33" t="n"/>
+      <c r="G84" s="33" t="n"/>
+      <c r="H84" s="33" t="n"/>
+      <c r="I84" s="33" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="16" t="inlineStr">
+      <c r="B85" s="18" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="26" t="n">
+      <c r="E85" s="29" t="n">
         <v>312107</v>
       </c>
-      <c r="F85" s="26" t="n">
+      <c r="F85" s="29" t="n">
         <v>322410</v>
       </c>
-      <c r="G85" s="26" t="n">
+      <c r="G85" s="29" t="n">
         <v>387947</v>
       </c>
-      <c r="H85" s="26" t="n">
+      <c r="H85" s="29" t="n">
         <v>426642</v>
       </c>
-      <c r="I85" s="26" t="n">
+      <c r="I85" s="29" t="n">
         <v>529148</v>
       </c>
-      <c r="J85" s="16">
+      <c r="J85" s="18">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K85" s="16">
+      <c r="K85" s="18">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L85" s="16">
+      <c r="L85" s="18">
         <f>L42</f>
         <v/>
       </c>
-      <c r="M85" s="16">
+      <c r="M85" s="18">
         <f>M42</f>
         <v/>
       </c>
-      <c r="N85" s="16">
+      <c r="N85" s="18">
         <f>N42</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="16" t="inlineStr">
+      <c r="B86" s="18" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="26" t="n">
+      <c r="E86" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="26" t="n">
+      <c r="F86" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="26" t="n">
+      <c r="G86" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="26" t="n">
+      <c r="H86" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="26" t="n">
+      <c r="I86" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="16">
+      <c r="J86" s="18">
         <f>J43</f>
         <v/>
       </c>
-      <c r="K86" s="16">
+      <c r="K86" s="18">
         <f>K43</f>
         <v/>
       </c>
-      <c r="L86" s="16">
+      <c r="L86" s="18">
         <f>L43</f>
         <v/>
       </c>
-      <c r="M86" s="16">
+      <c r="M86" s="18">
         <f>M43</f>
         <v/>
       </c>
-      <c r="N86" s="16">
+      <c r="N86" s="18">
         <f>N43</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="16" t="inlineStr">
+      <c r="B87" s="18" t="inlineStr">
         <is>
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="26" t="n">
+      <c r="E87" s="29" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="26" t="n">
+      <c r="F87" s="29" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="26" t="n">
+      <c r="G87" s="29" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="26" t="n">
+      <c r="H87" s="29" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="26" t="n">
+      <c r="I87" s="29" t="n">
         <v>32315</v>
       </c>
-      <c r="J87" s="16">
+      <c r="J87" s="18">
         <f>J48</f>
         <v/>
       </c>
-      <c r="K87" s="16">
+      <c r="K87" s="18">
         <f>K48</f>
         <v/>
       </c>
-      <c r="L87" s="16">
+      <c r="L87" s="18">
         <f>L48</f>
         <v/>
       </c>
-      <c r="M87" s="16">
+      <c r="M87" s="18">
         <f>M48</f>
         <v/>
       </c>
-      <c r="N87" s="16">
+      <c r="N87" s="18">
         <f>N48</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="50" t="inlineStr">
+      <c r="B88" s="53" t="inlineStr">
         <is>
           <t>Net Working Capital (NWC)</t>
         </is>
       </c>
-      <c r="C88" s="50" t="n"/>
-      <c r="D88" s="51" t="n"/>
-      <c r="E88" s="53">
+      <c r="C88" s="53" t="n"/>
+      <c r="D88" s="54" t="n"/>
+      <c r="E88" s="56">
         <f>E85+E86-E87</f>
         <v/>
       </c>
-      <c r="F88" s="53">
+      <c r="F88" s="56">
         <f>F85+F86-F87</f>
         <v/>
       </c>
-      <c r="G88" s="53">
+      <c r="G88" s="56">
         <f>G85+G86-G87</f>
         <v/>
       </c>
-      <c r="H88" s="53">
+      <c r="H88" s="56">
         <f>H85+H86-H87</f>
         <v/>
       </c>
-      <c r="I88" s="53">
+      <c r="I88" s="56">
         <f>I85+I86-I87</f>
         <v/>
       </c>
-      <c r="J88" s="53">
+      <c r="J88" s="56">
         <f>J85+J86-J87</f>
         <v/>
       </c>
-      <c r="K88" s="53">
+      <c r="K88" s="56">
         <f>K85+K86-K87</f>
         <v/>
       </c>
-      <c r="L88" s="53">
+      <c r="L88" s="56">
         <f>L85+L86-L87</f>
         <v/>
       </c>
-      <c r="M88" s="53">
+      <c r="M88" s="56">
         <f>M85+M86-M87</f>
         <v/>
       </c>
-      <c r="N88" s="53">
+      <c r="N88" s="56">
         <f>N85+N86-N87</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="16" t="inlineStr">
+      <c r="B89" s="18" t="inlineStr">
         <is>
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E89" s="25">
+      <c r="E89" s="28">
         <f>E88-D88</f>
         <v/>
       </c>
-      <c r="F89" s="25">
+      <c r="F89" s="28">
         <f>F88-E88</f>
         <v/>
       </c>
-      <c r="G89" s="25">
+      <c r="G89" s="28">
         <f>G88-F88</f>
         <v/>
       </c>
-      <c r="H89" s="25">
+      <c r="H89" s="28">
         <f>H88-G88</f>
         <v/>
       </c>
-      <c r="I89" s="25">
+      <c r="I89" s="28">
         <f>I88-H88</f>
         <v/>
       </c>
-      <c r="J89" s="25">
+      <c r="J89" s="28">
         <f>J88-I88</f>
         <v/>
       </c>
-      <c r="K89" s="25">
+      <c r="K89" s="28">
         <f>K88-J88</f>
         <v/>
       </c>
-      <c r="L89" s="25">
+      <c r="L89" s="28">
         <f>L88-K88</f>
         <v/>
       </c>
-      <c r="M89" s="25">
+      <c r="M89" s="28">
         <f>M88-L88</f>
         <v/>
       </c>
-      <c r="N89" s="25">
+      <c r="N89" s="28">
         <f>N88-M88</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="E90" s="30" t="n"/>
-      <c r="F90" s="30" t="n"/>
-      <c r="G90" s="30" t="n"/>
-      <c r="H90" s="30" t="n"/>
-      <c r="I90" s="30" t="n"/>
+      <c r="E90" s="33" t="n"/>
+      <c r="F90" s="33" t="n"/>
+      <c r="G90" s="33" t="n"/>
+      <c r="H90" s="33" t="n"/>
+      <c r="I90" s="33" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="19" t="inlineStr">
+      <c r="B91" s="21" t="inlineStr">
         <is>
           <t>Depreciation Schedule</t>
         </is>
       </c>
-      <c r="E91" s="30" t="n"/>
-      <c r="F91" s="30" t="n"/>
-      <c r="G91" s="30" t="n"/>
-      <c r="H91" s="30" t="n"/>
-      <c r="I91" s="30" t="n"/>
+      <c r="E91" s="33" t="n"/>
+      <c r="F91" s="33" t="n"/>
+      <c r="G91" s="33" t="n"/>
+      <c r="H91" s="33" t="n"/>
+      <c r="I91" s="33" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="16" t="inlineStr">
+      <c r="B92" s="18" t="inlineStr">
         <is>
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="26" t="n">
+      <c r="E92" s="29" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="26" t="n">
+      <c r="F92" s="29" t="n">
         <v>27913</v>
       </c>
-      <c r="G92" s="26" t="n">
+      <c r="G92" s="29" t="n">
         <v>17580</v>
       </c>
-      <c r="H92" s="26" t="n">
+      <c r="H92" s="29" t="n">
         <v>10966</v>
       </c>
-      <c r="I92" s="26" t="n">
+      <c r="I92" s="29" t="n">
         <v>38465</v>
       </c>
-      <c r="J92" s="16">
+      <c r="J92" s="18">
         <f>I95</f>
         <v/>
       </c>
-      <c r="K92" s="16">
+      <c r="K92" s="18">
         <f>J95</f>
         <v/>
       </c>
-      <c r="L92" s="16">
+      <c r="L92" s="18">
         <f>K95</f>
         <v/>
       </c>
-      <c r="M92" s="16">
+      <c r="M92" s="18">
         <f>L95</f>
         <v/>
       </c>
-      <c r="N92" s="16">
+      <c r="N92" s="18">
         <f>M95</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="16" t="inlineStr">
+      <c r="B93" s="18" t="inlineStr">
         <is>
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="26" t="n">
+      <c r="E93" s="29" t="n">
         <v>7086</v>
       </c>
-      <c r="F93" s="26" t="n">
+      <c r="F93" s="29" t="n">
         <v>10132</v>
       </c>
-      <c r="G93" s="26" t="n">
+      <c r="G93" s="29" t="n">
         <v>8024</v>
       </c>
-      <c r="H93" s="26" t="n">
+      <c r="H93" s="29" t="n">
         <v>41326</v>
       </c>
-      <c r="I93" s="26" t="n">
+      <c r="I93" s="29" t="n">
         <v>44200</v>
       </c>
-      <c r="J93" s="16">
+      <c r="J93" s="18">
         <f>+J18</f>
         <v/>
       </c>
-      <c r="K93" s="16">
+      <c r="K93" s="18">
         <f>+K18</f>
         <v/>
       </c>
-      <c r="L93" s="16">
+      <c r="L93" s="18">
         <f>+L18</f>
         <v/>
       </c>
-      <c r="M93" s="16">
+      <c r="M93" s="18">
         <f>+M18</f>
         <v/>
       </c>
-      <c r="N93" s="16">
+      <c r="N93" s="18">
         <f>+N18</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="16" t="inlineStr">
+      <c r="B94" s="18" t="inlineStr">
         <is>
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="26" t="n">
+      <c r="E94" s="29" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="26" t="n">
+      <c r="F94" s="29" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="26" t="n">
+      <c r="G94" s="29" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="26" t="n">
+      <c r="H94" s="29" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="26" t="n">
+      <c r="I94" s="29" t="n">
         <v>14952</v>
       </c>
-      <c r="J94" s="31">
+      <c r="J94" s="34">
         <f>J92*J11</f>
         <v/>
       </c>
-      <c r="K94" s="31">
+      <c r="K94" s="34">
         <f>K92*K11</f>
         <v/>
       </c>
-      <c r="L94" s="31">
+      <c r="L94" s="34">
         <f>L92*L11</f>
         <v/>
       </c>
-      <c r="M94" s="31">
+      <c r="M94" s="34">
         <f>M92*M11</f>
         <v/>
       </c>
-      <c r="N94" s="31">
+      <c r="N94" s="34">
         <f>N92*N11</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="50" t="inlineStr">
+      <c r="B95" s="53" t="inlineStr">
         <is>
           <t>PPE Closing</t>
         </is>
       </c>
-      <c r="C95" s="50" t="n"/>
-      <c r="D95" s="51" t="n"/>
-      <c r="E95" s="53">
+      <c r="C95" s="53" t="n"/>
+      <c r="D95" s="54" t="n"/>
+      <c r="E95" s="56">
         <f>E92+E93-E94</f>
         <v/>
       </c>
-      <c r="F95" s="53">
+      <c r="F95" s="56">
         <f>F92+F93-F94</f>
         <v/>
       </c>
-      <c r="G95" s="53">
+      <c r="G95" s="56">
         <f>G92+G93-G94</f>
         <v/>
       </c>
-      <c r="H95" s="53">
+      <c r="H95" s="56">
         <f>H92+H93-H94</f>
         <v/>
       </c>
-      <c r="I95" s="53">
+      <c r="I95" s="56">
         <f>I92+I93-I94</f>
         <v/>
       </c>
-      <c r="J95" s="53">
+      <c r="J95" s="56">
         <f>J92+J93-J94</f>
         <v/>
       </c>
-      <c r="K95" s="53">
+      <c r="K95" s="56">
         <f>K92+K93-K94</f>
         <v/>
       </c>
-      <c r="L95" s="53">
+      <c r="L95" s="56">
         <f>L92+L93-L94</f>
         <v/>
       </c>
-      <c r="M95" s="53">
+      <c r="M95" s="56">
         <f>M92+M93-M94</f>
         <v/>
       </c>
-      <c r="N95" s="53">
+      <c r="N95" s="56">
         <f>N92+N93-N94</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="E96" s="30" t="n"/>
-      <c r="F96" s="30" t="n"/>
-      <c r="G96" s="30" t="n"/>
-      <c r="H96" s="30" t="n"/>
-      <c r="I96" s="30" t="n"/>
-      <c r="J96" s="30" t="n"/>
-      <c r="K96" s="30" t="n"/>
-      <c r="L96" s="30" t="n"/>
-      <c r="M96" s="30" t="n"/>
-      <c r="N96" s="30" t="n"/>
+      <c r="E96" s="33" t="n"/>
+      <c r="F96" s="33" t="n"/>
+      <c r="G96" s="33" t="n"/>
+      <c r="H96" s="33" t="n"/>
+      <c r="I96" s="33" t="n"/>
+      <c r="J96" s="33" t="n"/>
+      <c r="K96" s="33" t="n"/>
+      <c r="L96" s="33" t="n"/>
+      <c r="M96" s="33" t="n"/>
+      <c r="N96" s="33" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="19" t="inlineStr">
+      <c r="B97" s="21" t="inlineStr">
         <is>
           <t>Debt &amp; Interest Schedule</t>
         </is>
       </c>
-      <c r="E97" s="30" t="n"/>
-      <c r="F97" s="30" t="n"/>
-      <c r="G97" s="30" t="n"/>
-      <c r="H97" s="30" t="n"/>
-      <c r="I97" s="30" t="n"/>
+      <c r="E97" s="33" t="n"/>
+      <c r="F97" s="33" t="n"/>
+      <c r="G97" s="33" t="n"/>
+      <c r="H97" s="33" t="n"/>
+      <c r="I97" s="33" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="16" t="inlineStr">
+      <c r="B98" s="18" t="inlineStr">
         <is>
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="26" t="n">
+      <c r="E98" s="29" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="26" t="n">
+      <c r="F98" s="29" t="n">
         <v>1009018</v>
       </c>
-      <c r="G98" s="26" t="n">
+      <c r="G98" s="29" t="n">
         <v>1823669</v>
       </c>
-      <c r="H98" s="26" t="n">
+      <c r="H98" s="29" t="n">
         <v>1811658</v>
       </c>
-      <c r="I98" s="26" t="n">
+      <c r="I98" s="29" t="n">
         <v>2209021</v>
       </c>
-      <c r="J98" s="16">
+      <c r="J98" s="18">
         <f>I100</f>
         <v/>
       </c>
-      <c r="K98" s="16">
+      <c r="K98" s="18">
         <f>J100</f>
         <v/>
       </c>
-      <c r="L98" s="16">
+      <c r="L98" s="18">
         <f>K100</f>
         <v/>
       </c>
-      <c r="M98" s="16">
+      <c r="M98" s="18">
         <f>L100</f>
         <v/>
       </c>
-      <c r="N98" s="16">
+      <c r="N98" s="18">
         <f>M100</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="16" t="inlineStr">
+      <c r="B99" s="18" t="inlineStr">
         <is>
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="26" t="n">
+      <c r="E99" s="29" t="n">
         <v>269583</v>
       </c>
-      <c r="F99" s="26" t="n">
+      <c r="F99" s="29" t="n">
         <v>814651</v>
       </c>
-      <c r="G99" s="26" t="n">
+      <c r="G99" s="29" t="n">
         <v>-12011</v>
       </c>
-      <c r="H99" s="26" t="n">
+      <c r="H99" s="29" t="n">
         <v>397363</v>
       </c>
-      <c r="I99" s="26" t="n">
+      <c r="I99" s="29" t="n">
         <v>846670</v>
       </c>
-      <c r="J99" s="25">
+      <c r="J99" s="28">
         <f>+J19</f>
         <v/>
       </c>
-      <c r="K99" s="25">
+      <c r="K99" s="28">
         <f>+K19</f>
         <v/>
       </c>
-      <c r="L99" s="25">
+      <c r="L99" s="28">
         <f>+L19</f>
         <v/>
       </c>
-      <c r="M99" s="25">
+      <c r="M99" s="28">
         <f>+M19</f>
         <v/>
       </c>
-      <c r="N99" s="25">
+      <c r="N99" s="28">
         <f>+N19</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="50" t="inlineStr">
+      <c r="B100" s="53" t="inlineStr">
         <is>
           <t>Debt Closing</t>
         </is>
       </c>
-      <c r="C100" s="50" t="n"/>
-      <c r="D100" s="51" t="n"/>
-      <c r="E100" s="53">
+      <c r="C100" s="53" t="n"/>
+      <c r="D100" s="54" t="n"/>
+      <c r="E100" s="56">
         <f>SUM(E98:E99)</f>
         <v/>
       </c>
-      <c r="F100" s="53">
+      <c r="F100" s="56">
         <f>SUM(F98:F99)</f>
         <v/>
       </c>
-      <c r="G100" s="53">
+      <c r="G100" s="56">
         <f>SUM(G98:G99)</f>
         <v/>
       </c>
-      <c r="H100" s="53">
+      <c r="H100" s="56">
         <f>SUM(H98:H99)</f>
         <v/>
       </c>
-      <c r="I100" s="53">
+      <c r="I100" s="56">
         <f>SUM(I98:I99)</f>
         <v/>
       </c>
-      <c r="J100" s="53">
+      <c r="J100" s="56">
         <f>SUM(J98:J99)</f>
         <v/>
       </c>
-      <c r="K100" s="53">
+      <c r="K100" s="56">
         <f>SUM(K98:K99)</f>
         <v/>
       </c>
-      <c r="L100" s="53">
+      <c r="L100" s="56">
         <f>SUM(L98:L99)</f>
         <v/>
       </c>
-      <c r="M100" s="53">
+      <c r="M100" s="56">
         <f>SUM(M98:M99)</f>
         <v/>
       </c>
-      <c r="N100" s="53">
+      <c r="N100" s="56">
         <f>SUM(N98:N99)</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="16" t="inlineStr">
+      <c r="B101" s="18" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="26" t="n">
+      <c r="E101" s="29" t="n">
         <v>40092</v>
       </c>
-      <c r="F101" s="26" t="n">
+      <c r="F101" s="29" t="n">
         <v>68967</v>
       </c>
-      <c r="G101" s="26" t="n">
+      <c r="G101" s="29" t="n">
         <v>95546</v>
       </c>
-      <c r="H101" s="26" t="n">
+      <c r="H101" s="29" t="n">
         <v>105638</v>
       </c>
-      <c r="I101" s="26" t="n">
+      <c r="I101" s="29" t="n">
         <v>133647</v>
       </c>
-      <c r="J101" s="16">
+      <c r="J101" s="18">
         <f>J98*J12</f>
         <v/>
       </c>
-      <c r="K101" s="16">
+      <c r="K101" s="18">
         <f>K98*K12</f>
         <v/>
       </c>
-      <c r="L101" s="16">
+      <c r="L101" s="18">
         <f>L98*L12</f>
         <v/>
       </c>
-      <c r="M101" s="16">
+      <c r="M101" s="18">
         <f>M98*M12</f>
         <v/>
       </c>
-      <c r="N101" s="16">
+      <c r="N101" s="18">
         <f>N98*N12</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="E102" s="30" t="n"/>
-      <c r="F102" s="30" t="n"/>
-      <c r="G102" s="54" t="n"/>
-      <c r="H102" s="30" t="n"/>
-      <c r="I102" s="30" t="n"/>
+      <c r="E102" s="33" t="n"/>
+      <c r="F102" s="33" t="n"/>
+      <c r="G102" s="57" t="n"/>
+      <c r="H102" s="33" t="n"/>
+      <c r="I102" s="33" t="n"/>
     </row>
     <row r="103">
-      <c r="E103" s="30" t="n"/>
-      <c r="F103" s="30" t="n"/>
-      <c r="G103" s="30" t="n"/>
-      <c r="H103" s="30" t="n"/>
-      <c r="I103" s="30" t="n"/>
+      <c r="E103" s="33" t="n"/>
+      <c r="F103" s="33" t="n"/>
+      <c r="G103" s="33" t="n"/>
+      <c r="H103" s="33" t="n"/>
+      <c r="I103" s="33" t="n"/>
     </row>
     <row r="104">
-      <c r="E104" s="30" t="n"/>
-      <c r="F104" s="30" t="n"/>
-      <c r="G104" s="30" t="n"/>
-      <c r="H104" s="30" t="n"/>
-      <c r="I104" s="30" t="n"/>
+      <c r="E104" s="33" t="n"/>
+      <c r="F104" s="33" t="n"/>
+      <c r="G104" s="33" t="n"/>
+      <c r="H104" s="33" t="n"/>
+      <c r="I104" s="33" t="n"/>
     </row>
     <row r="105">
-      <c r="B105" s="18" t="inlineStr">
+      <c r="B105" s="20" t="inlineStr">
         <is>
           <t>Charts and Graphs</t>
         </is>
       </c>
-      <c r="C105" s="18" t="n"/>
-      <c r="D105" s="18" t="n"/>
-      <c r="E105" s="18" t="n"/>
-      <c r="F105" s="18" t="n"/>
-      <c r="G105" s="18" t="n"/>
-      <c r="H105" s="18" t="n"/>
-      <c r="I105" s="18" t="n"/>
-      <c r="J105" s="18" t="n"/>
-      <c r="K105" s="18" t="n"/>
-      <c r="L105" s="18" t="n"/>
-      <c r="M105" s="18" t="n"/>
-      <c r="N105" s="18" t="n"/>
+      <c r="C105" s="20" t="n"/>
+      <c r="D105" s="20" t="n"/>
+      <c r="E105" s="20" t="n"/>
+      <c r="F105" s="20" t="n"/>
+      <c r="G105" s="20" t="n"/>
+      <c r="H105" s="20" t="n"/>
+      <c r="I105" s="20" t="n"/>
+      <c r="J105" s="20" t="n"/>
+      <c r="K105" s="20" t="n"/>
+      <c r="L105" s="20" t="n"/>
+      <c r="M105" s="20" t="n"/>
+      <c r="N105" s="20" t="n"/>
     </row>
     <row r="106"/>
     <row r="107"/>
@@ -4882,174 +5206,174 @@
     <row r="116"/>
     <row r="117"/>
     <row r="118">
-      <c r="C118" s="55" t="n"/>
-      <c r="D118" s="55" t="n"/>
+      <c r="C118" s="58" t="n"/>
+      <c r="D118" s="58" t="n"/>
     </row>
     <row r="119">
-      <c r="B119" s="55" t="n"/>
-      <c r="C119" s="55" t="n"/>
-      <c r="D119" s="55" t="n"/>
+      <c r="B119" s="58" t="n"/>
+      <c r="C119" s="58" t="n"/>
+      <c r="D119" s="58" t="n"/>
     </row>
     <row r="120"/>
     <row r="121">
-      <c r="B121" s="16" t="inlineStr">
+      <c r="B121" s="18" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="E121" s="16">
+      <c r="E121" s="18">
         <f>E24</f>
         <v/>
       </c>
-      <c r="F121" s="16">
+      <c r="F121" s="18">
         <f>F24</f>
         <v/>
       </c>
-      <c r="G121" s="16">
+      <c r="G121" s="18">
         <f>G24</f>
         <v/>
       </c>
-      <c r="H121" s="16">
+      <c r="H121" s="18">
         <f>H24</f>
         <v/>
       </c>
-      <c r="I121" s="16">
+      <c r="I121" s="18">
         <f>I24</f>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="B122" s="16" t="inlineStr">
+      <c r="B122" s="18" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="E122" s="16">
+      <c r="E122" s="18">
         <f>E26</f>
         <v/>
       </c>
-      <c r="F122" s="16">
+      <c r="F122" s="18">
         <f>F26</f>
         <v/>
       </c>
-      <c r="G122" s="16">
+      <c r="G122" s="18">
         <f>G26</f>
         <v/>
       </c>
-      <c r="H122" s="16">
+      <c r="H122" s="18">
         <f>H26</f>
         <v/>
       </c>
-      <c r="I122" s="16">
+      <c r="I122" s="18">
         <f>I26</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="B123" s="16" t="inlineStr">
+      <c r="B123" s="18" t="inlineStr">
         <is>
           <t>Earning Before Tax</t>
         </is>
       </c>
-      <c r="E123" s="16">
+      <c r="E123" s="18">
         <f>E33</f>
         <v/>
       </c>
-      <c r="F123" s="16">
+      <c r="F123" s="18">
         <f>F33</f>
         <v/>
       </c>
-      <c r="G123" s="16">
+      <c r="G123" s="18">
         <f>G33</f>
         <v/>
       </c>
-      <c r="H123" s="16">
+      <c r="H123" s="18">
         <f>H33</f>
         <v/>
       </c>
-      <c r="I123" s="16">
+      <c r="I123" s="18">
         <f>I33</f>
         <v/>
       </c>
     </row>
     <row r="124"/>
     <row r="125">
-      <c r="B125" s="16" t="inlineStr">
+      <c r="B125" s="18" t="inlineStr">
         <is>
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="E125" s="16">
+      <c r="E125" s="18">
         <f>E65</f>
         <v/>
       </c>
-      <c r="F125" s="16">
+      <c r="F125" s="18">
         <f>F65</f>
         <v/>
       </c>
-      <c r="G125" s="16">
+      <c r="G125" s="18">
         <f>G65</f>
         <v/>
       </c>
-      <c r="H125" s="16">
+      <c r="H125" s="18">
         <f>H65</f>
         <v/>
       </c>
-      <c r="I125" s="16">
+      <c r="I125" s="18">
         <f>I65</f>
         <v/>
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="16" t="inlineStr">
+      <c r="B126" s="18" t="inlineStr">
         <is>
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="E126" s="16">
+      <c r="E126" s="18">
         <f>-E69</f>
         <v/>
       </c>
-      <c r="F126" s="16">
+      <c r="F126" s="18">
         <f>-F69</f>
         <v/>
       </c>
-      <c r="G126" s="16">
+      <c r="G126" s="18">
         <f>-G69</f>
         <v/>
       </c>
-      <c r="H126" s="16">
+      <c r="H126" s="18">
         <f>-H69</f>
         <v/>
       </c>
-      <c r="I126" s="16">
+      <c r="I126" s="18">
         <f>-I69</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="16" t="inlineStr">
+      <c r="B127" s="18" t="inlineStr">
         <is>
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="E127" s="16">
+      <c r="E127" s="18">
         <f>E74</f>
         <v/>
       </c>
-      <c r="F127" s="16">
+      <c r="F127" s="18">
         <f>F74</f>
         <v/>
       </c>
-      <c r="G127" s="16">
+      <c r="G127" s="18">
         <f>G74</f>
         <v/>
       </c>
-      <c r="H127" s="16">
+      <c r="H127" s="18">
         <f>H74</f>
         <v/>
       </c>
-      <c r="I127" s="16">
+      <c r="I127" s="18">
         <f>I74</f>
         <v/>
       </c>
@@ -5058,54 +5382,54 @@
     <row r="129"/>
     <row r="130"/>
     <row r="131">
-      <c r="B131" s="56" t="inlineStr">
-        <is>
-          <t>FIXED: forecast drivers now FICO-scale (COGS%~17.8%, SG&amp;A/R&amp;D from FY25, tax~18.8%, AR days~97, Inv days=0, Capex from 10-K). Years 2021–2030 hardcoded.</t>
+      <c r="B131" s="59" t="inlineStr">
+        <is>
+          <t>Yellow = inputs. All Gross Profit / totals / forecast Revenue(=prior*(1+g)) / COGS(=Rev*COGS%) / Capex(=row18) / ΔNWC(=schedule) are Excel formulas.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="B132" s="55" t="n"/>
-      <c r="C132" s="55" t="n"/>
-      <c r="D132" s="55" t="n"/>
+      <c r="B132" s="58" t="n"/>
+      <c r="C132" s="58" t="n"/>
+      <c r="D132" s="58" t="n"/>
     </row>
     <row r="133">
-      <c r="B133" s="55" t="n"/>
-      <c r="C133" s="55" t="n"/>
-      <c r="D133" s="55" t="n"/>
+      <c r="B133" s="58" t="n"/>
+      <c r="C133" s="58" t="n"/>
+      <c r="D133" s="58" t="n"/>
     </row>
     <row r="134">
-      <c r="B134" s="55" t="n"/>
-      <c r="C134" s="55" t="n"/>
-      <c r="D134" s="55" t="n"/>
+      <c r="B134" s="58" t="n"/>
+      <c r="C134" s="58" t="n"/>
+      <c r="D134" s="58" t="n"/>
     </row>
     <row r="135">
-      <c r="B135" s="55" t="n"/>
-      <c r="C135" s="55" t="n"/>
-      <c r="D135" s="55" t="n"/>
+      <c r="B135" s="58" t="n"/>
+      <c r="C135" s="58" t="n"/>
+      <c r="D135" s="58" t="n"/>
     </row>
     <row r="136">
-      <c r="B136" s="55" t="n"/>
-      <c r="C136" s="55" t="n"/>
-      <c r="D136" s="55" t="n"/>
+      <c r="B136" s="58" t="n"/>
+      <c r="C136" s="58" t="n"/>
+      <c r="D136" s="58" t="n"/>
     </row>
     <row r="137">
-      <c r="B137" s="55" t="inlineStr">
+      <c r="B137" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Corporate Finance Institute® </t>
         </is>
       </c>
-      <c r="C137" s="57" t="n"/>
-      <c r="D137" s="57" t="n"/>
+      <c r="C137" s="60" t="n"/>
+      <c r="D137" s="60" t="n"/>
     </row>
     <row r="138">
-      <c r="B138" s="58" t="inlineStr">
+      <c r="B138" s="61" t="inlineStr">
         <is>
           <t>https://corporatefinanceinstitute.com/</t>
         </is>
       </c>
-      <c r="C138" s="59" t="n"/>
-      <c r="D138" s="59" t="n"/>
+      <c r="C138" s="62" t="n"/>
+      <c r="D138" s="62" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5123,7 +5447,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.54296875" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="12.453125" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -5140,390 +5464,369 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="63" t="inlineStr">
         <is>
           <t>© Corporate Finance Institute®. All rights reserved.</t>
         </is>
       </c>
-      <c r="B1" s="61" t="n"/>
-      <c r="C1" s="61" t="n"/>
-      <c r="D1" s="62" t="n"/>
-      <c r="E1" s="62" t="n"/>
-      <c r="F1" s="62" t="n"/>
-      <c r="G1" s="62" t="n"/>
-      <c r="H1" s="60" t="n"/>
-      <c r="I1" s="61" t="n"/>
-      <c r="J1" s="61" t="n"/>
-      <c r="K1" s="62" t="n"/>
-      <c r="L1" s="62" t="n"/>
-      <c r="M1" s="62" t="n"/>
-      <c r="N1" s="62" t="n"/>
+      <c r="B1" s="64" t="n"/>
+      <c r="C1" s="64" t="n"/>
+      <c r="D1" s="65" t="n"/>
+      <c r="E1" s="65" t="n"/>
+      <c r="F1" s="65" t="n"/>
+      <c r="G1" s="65" t="n"/>
+      <c r="H1" s="63" t="n"/>
+      <c r="I1" s="64" t="n"/>
+      <c r="J1" s="64" t="n"/>
+      <c r="K1" s="65" t="n"/>
+      <c r="L1" s="65" t="n"/>
+      <c r="M1" s="65" t="n"/>
+      <c r="N1" s="65" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="n"/>
-      <c r="B2" s="63" t="inlineStr">
-        <is>
-          <t>FICO DCF (joined, corrected)</t>
-        </is>
-      </c>
-      <c r="C2" s="64" t="n"/>
-      <c r="D2" s="65" t="inlineStr">
-        <is>
-          <t>FIXED: EBIT anchored to FY25 OpInc; years 2026–2030; FY25 base in row 16</t>
-        </is>
-      </c>
-      <c r="E2" s="64" t="n"/>
-      <c r="F2" s="62" t="n"/>
-      <c r="G2" s="62" t="n"/>
-      <c r="H2" s="61" t="n"/>
-      <c r="I2" s="63" t="n"/>
-      <c r="J2" s="64" t="n"/>
-      <c r="K2" s="64" t="n"/>
-      <c r="L2" s="64" t="n"/>
-      <c r="M2" s="62" t="n"/>
-      <c r="N2" s="62" t="n"/>
+      <c r="A2" s="64" t="n"/>
+      <c r="B2" s="66" t="inlineStr">
+        <is>
+          <t>FICO DCF (linked formulas → 03_Three_Statement)</t>
+        </is>
+      </c>
+      <c r="C2" s="67" t="n"/>
+      <c r="D2" s="67" t="n"/>
+      <c r="E2" s="67" t="n"/>
+      <c r="F2" s="65" t="n"/>
+      <c r="G2" s="65" t="n"/>
+      <c r="H2" s="64" t="n"/>
+      <c r="I2" s="66" t="n"/>
+      <c r="J2" s="67" t="n"/>
+      <c r="K2" s="67" t="n"/>
+      <c r="L2" s="67" t="n"/>
+      <c r="M2" s="65" t="n"/>
+      <c r="N2" s="65" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="66" t="n"/>
-      <c r="B3" s="67" t="n"/>
-      <c r="C3" s="66" t="n"/>
-      <c r="D3" s="68" t="n"/>
-      <c r="E3" s="69" t="n"/>
-      <c r="F3" s="69" t="n"/>
-      <c r="G3" s="69" t="n"/>
-      <c r="H3" s="69" t="n"/>
-      <c r="I3" s="69" t="n"/>
-      <c r="J3" s="66" t="n"/>
-      <c r="K3" s="66" t="n"/>
-      <c r="L3" s="66" t="n"/>
-      <c r="M3" s="66" t="n"/>
-      <c r="N3" s="66" t="n"/>
-      <c r="O3" s="66" t="n"/>
+      <c r="A3" s="68" t="n"/>
+      <c r="B3" s="69" t="inlineStr">
+        <is>
+          <t>FY25 OpInc (base)</t>
+        </is>
+      </c>
+      <c r="C3" s="68" t="inlineStr">
+        <is>
+          <t>FY25 D&amp;A</t>
+        </is>
+      </c>
+      <c r="D3" s="70" t="n">
+        <v>924850</v>
+      </c>
+      <c r="E3" s="71" t="n">
+        <v>14952</v>
+      </c>
+      <c r="F3" s="72" t="n"/>
+      <c r="G3" s="72" t="n"/>
+      <c r="H3" s="72" t="n"/>
+      <c r="I3" s="72" t="n"/>
+      <c r="J3" s="68" t="n"/>
+      <c r="K3" s="68" t="n"/>
+      <c r="L3" s="68" t="n"/>
+      <c r="M3" s="68" t="n"/>
+      <c r="N3" s="68" t="n"/>
+      <c r="O3" s="68" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="66" t="n"/>
-      <c r="B4" s="70" t="inlineStr">
+      <c r="A4" s="68" t="n"/>
+      <c r="B4" s="73" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="C4" s="71" t="n"/>
-      <c r="D4" s="71" t="n"/>
-      <c r="E4" s="69" t="n"/>
-      <c r="F4" s="66" t="n"/>
-      <c r="G4" s="66" t="n"/>
-      <c r="H4" s="66" t="n"/>
-      <c r="I4" s="66" t="n"/>
-      <c r="J4" s="66" t="n"/>
-      <c r="K4" s="66" t="n"/>
-      <c r="L4" s="66" t="n"/>
-      <c r="M4" s="66" t="n"/>
-      <c r="N4" s="66" t="n"/>
-      <c r="O4" s="66" t="n"/>
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="74" t="n"/>
+      <c r="E4" s="72" t="n"/>
+      <c r="F4" s="68" t="n"/>
+      <c r="G4" s="68" t="n"/>
+      <c r="H4" s="68" t="n"/>
+      <c r="I4" s="68" t="n"/>
+      <c r="J4" s="68" t="n"/>
+      <c r="K4" s="68" t="n"/>
+      <c r="L4" s="68" t="n"/>
+      <c r="M4" s="68" t="n"/>
+      <c r="N4" s="68" t="n"/>
+      <c r="O4" s="68" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="66" t="n"/>
-      <c r="B5" s="72" t="inlineStr">
+      <c r="A5" s="68" t="n"/>
+      <c r="B5" s="75" t="inlineStr">
         <is>
           <t>Tax Rate</t>
         </is>
       </c>
-      <c r="C5" s="69" t="n"/>
-      <c r="D5" s="73" t="n">
-        <v>0.1877</v>
-      </c>
-      <c r="E5" s="69" t="n"/>
-      <c r="F5" s="66" t="n"/>
-      <c r="G5" s="66" t="n"/>
-      <c r="H5" s="66" t="n"/>
-      <c r="I5" s="66" t="n"/>
-      <c r="J5" s="66" t="n"/>
-      <c r="K5" s="66" t="n"/>
-      <c r="L5" s="66" t="n"/>
-      <c r="M5" s="66" t="n"/>
-      <c r="N5" s="66" t="n"/>
-      <c r="O5" s="66" t="n"/>
+      <c r="C5" s="72" t="n"/>
+      <c r="D5" s="76">
+        <f>'03_Three_Statement'!J13</f>
+        <v/>
+      </c>
+      <c r="E5" s="72" t="n"/>
+      <c r="F5" s="68" t="n"/>
+      <c r="G5" s="68" t="n"/>
+      <c r="H5" s="68" t="n"/>
+      <c r="I5" s="68" t="n"/>
+      <c r="J5" s="68" t="n"/>
+      <c r="K5" s="68" t="n"/>
+      <c r="L5" s="68" t="n"/>
+      <c r="M5" s="68" t="n"/>
+      <c r="N5" s="68" t="n"/>
+      <c r="O5" s="68" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="66" t="n"/>
-      <c r="B6" s="72" t="inlineStr">
+      <c r="A6" s="68" t="n"/>
+      <c r="B6" s="75" t="inlineStr">
         <is>
           <t>Discount Rate</t>
         </is>
       </c>
-      <c r="C6" s="66" t="n"/>
-      <c r="D6" s="74" t="n">
+      <c r="C6" s="68" t="n"/>
+      <c r="D6" s="77" t="n">
         <v>0.096</v>
       </c>
-      <c r="E6" s="66" t="n"/>
-      <c r="F6" s="66" t="n"/>
-      <c r="G6" s="66" t="n"/>
-      <c r="H6" s="66" t="n"/>
-      <c r="I6" s="66" t="n"/>
-      <c r="J6" s="66" t="n"/>
-      <c r="K6" s="66" t="n"/>
-      <c r="L6" s="66" t="n"/>
-      <c r="M6" s="66" t="n"/>
-      <c r="N6" s="66" t="n"/>
-      <c r="O6" s="66" t="n"/>
+      <c r="E6" s="68" t="n"/>
+      <c r="F6" s="68" t="n"/>
+      <c r="G6" s="68" t="n"/>
+      <c r="H6" s="68" t="n"/>
+      <c r="I6" s="68" t="n"/>
+      <c r="J6" s="68" t="n"/>
+      <c r="K6" s="68" t="n"/>
+      <c r="L6" s="68" t="n"/>
+      <c r="M6" s="68" t="n"/>
+      <c r="N6" s="68" t="n"/>
+      <c r="O6" s="68" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="66" t="n"/>
-      <c r="B7" s="66" t="inlineStr">
+      <c r="A7" s="68" t="n"/>
+      <c r="B7" s="68" t="inlineStr">
         <is>
           <t>Perpetural Growth Rate</t>
         </is>
       </c>
-      <c r="C7" s="66" t="n"/>
-      <c r="D7" s="74" t="n">
+      <c r="C7" s="68" t="n"/>
+      <c r="D7" s="77" t="n">
         <v>0.03</v>
       </c>
-      <c r="E7" s="66" t="n"/>
-      <c r="F7" s="66" t="n"/>
-      <c r="G7" s="66" t="n"/>
-      <c r="H7" s="66" t="n"/>
-      <c r="I7" s="66" t="n"/>
-      <c r="J7" s="66" t="n"/>
-      <c r="K7" s="66" t="n"/>
-      <c r="L7" s="66" t="n"/>
-      <c r="M7" s="66" t="n"/>
-      <c r="N7" s="66" t="n"/>
-      <c r="O7" s="66" t="n"/>
+      <c r="E7" s="68" t="n"/>
+      <c r="F7" s="68" t="n"/>
+      <c r="G7" s="68" t="n"/>
+      <c r="H7" s="68" t="n"/>
+      <c r="I7" s="68" t="n"/>
+      <c r="J7" s="68" t="n"/>
+      <c r="K7" s="68" t="n"/>
+      <c r="L7" s="68" t="n"/>
+      <c r="M7" s="68" t="n"/>
+      <c r="N7" s="68" t="n"/>
+      <c r="O7" s="68" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="66" t="n"/>
-      <c r="B8" s="66" t="inlineStr">
+      <c r="A8" s="68" t="n"/>
+      <c r="B8" s="68" t="inlineStr">
         <is>
           <t>EV/EBITDA Mulltiple</t>
         </is>
       </c>
-      <c r="C8" s="66" t="n"/>
-      <c r="D8" s="75" t="n">
+      <c r="C8" s="68" t="n"/>
+      <c r="D8" s="78" t="n">
         <v>22</v>
       </c>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="66" t="n"/>
-      <c r="G8" s="66" t="n"/>
-      <c r="H8" s="66" t="n"/>
-      <c r="I8" s="66" t="n"/>
-      <c r="J8" s="66" t="n"/>
-      <c r="K8" s="66" t="n"/>
-      <c r="L8" s="66" t="n"/>
-      <c r="M8" s="66" t="n"/>
-      <c r="N8" s="66" t="n"/>
-      <c r="O8" s="66" t="n"/>
+      <c r="E8" s="68" t="n"/>
+      <c r="F8" s="68" t="n"/>
+      <c r="G8" s="68" t="n"/>
+      <c r="H8" s="68" t="n"/>
+      <c r="I8" s="68" t="n"/>
+      <c r="J8" s="68" t="n"/>
+      <c r="K8" s="68" t="n"/>
+      <c r="L8" s="68" t="n"/>
+      <c r="M8" s="68" t="n"/>
+      <c r="N8" s="68" t="n"/>
+      <c r="O8" s="68" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="66" t="n"/>
-      <c r="B9" s="66" t="inlineStr">
+      <c r="A9" s="68" t="n"/>
+      <c r="B9" s="68" t="inlineStr">
         <is>
           <t>Transaction Date</t>
         </is>
       </c>
-      <c r="C9" s="66" t="n"/>
-      <c r="D9" s="76" t="n">
+      <c r="C9" s="68" t="n"/>
+      <c r="D9" s="79" t="n">
         <v>45930</v>
       </c>
-      <c r="E9" s="66" t="n"/>
-      <c r="F9" s="66" t="n"/>
-      <c r="G9" s="66" t="n"/>
-      <c r="H9" s="66" t="n"/>
-      <c r="I9" s="66" t="n"/>
-      <c r="J9" s="66" t="n"/>
-      <c r="K9" s="66" t="n"/>
-      <c r="L9" s="66" t="n"/>
-      <c r="M9" s="66" t="n"/>
-      <c r="N9" s="66" t="n"/>
-      <c r="O9" s="66" t="n"/>
+      <c r="E9" s="68" t="n"/>
+      <c r="F9" s="68" t="n"/>
+      <c r="G9" s="68" t="n"/>
+      <c r="H9" s="68" t="n"/>
+      <c r="I9" s="68" t="n"/>
+      <c r="J9" s="68" t="n"/>
+      <c r="K9" s="68" t="n"/>
+      <c r="L9" s="68" t="n"/>
+      <c r="M9" s="68" t="n"/>
+      <c r="N9" s="68" t="n"/>
+      <c r="O9" s="68" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="66" t="n"/>
-      <c r="B10" s="66" t="inlineStr">
+      <c r="A10" s="68" t="n"/>
+      <c r="B10" s="68" t="inlineStr">
         <is>
           <t>Fiscal Year End</t>
         </is>
       </c>
-      <c r="C10" s="66" t="n"/>
-      <c r="D10" s="76" t="n">
+      <c r="C10" s="68" t="n"/>
+      <c r="D10" s="79" t="n">
         <v>45930</v>
       </c>
-      <c r="E10" s="66" t="n"/>
-      <c r="F10" s="66" t="n"/>
-      <c r="G10" s="66" t="n"/>
-      <c r="H10" s="66" t="n"/>
-      <c r="I10" s="66" t="n"/>
-      <c r="J10" s="66" t="n"/>
-      <c r="K10" s="66" t="n"/>
-      <c r="L10" s="66" t="n"/>
-      <c r="M10" s="66" t="n"/>
-      <c r="N10" s="66" t="n"/>
-      <c r="O10" s="66" t="n"/>
+      <c r="E10" s="68" t="n"/>
+      <c r="F10" s="68" t="n"/>
+      <c r="G10" s="68" t="n"/>
+      <c r="H10" s="68" t="n"/>
+      <c r="I10" s="68" t="n"/>
+      <c r="J10" s="68" t="n"/>
+      <c r="K10" s="68" t="n"/>
+      <c r="L10" s="68" t="n"/>
+      <c r="M10" s="68" t="n"/>
+      <c r="N10" s="68" t="n"/>
+      <c r="O10" s="68" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="66" t="n"/>
-      <c r="B11" s="66" t="inlineStr">
+      <c r="A11" s="68" t="n"/>
+      <c r="B11" s="68" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="C11" s="66" t="n"/>
-      <c r="D11" s="77" t="n">
+      <c r="C11" s="68" t="n"/>
+      <c r="D11" s="80" t="n">
         <v>1046.23</v>
       </c>
-      <c r="E11" s="66" t="n"/>
-      <c r="F11" s="66" t="n"/>
-      <c r="G11" s="66" t="n"/>
-      <c r="H11" s="66" t="n"/>
-      <c r="I11" s="66" t="n"/>
-      <c r="J11" s="66" t="n"/>
-      <c r="K11" s="66" t="n"/>
-      <c r="L11" s="66" t="n"/>
-      <c r="M11" s="66" t="n"/>
-      <c r="N11" s="66" t="n"/>
-      <c r="O11" s="66" t="n"/>
+      <c r="E11" s="68" t="n"/>
+      <c r="F11" s="68" t="n"/>
+      <c r="G11" s="68" t="n"/>
+      <c r="H11" s="68" t="n"/>
+      <c r="I11" s="68" t="n"/>
+      <c r="J11" s="68" t="n"/>
+      <c r="K11" s="68" t="n"/>
+      <c r="L11" s="68" t="n"/>
+      <c r="M11" s="68" t="n"/>
+      <c r="N11" s="68" t="n"/>
+      <c r="O11" s="68" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="66" t="n"/>
-      <c r="B12" s="66" t="inlineStr">
+      <c r="A12" s="68" t="n"/>
+      <c r="B12" s="68" t="inlineStr">
         <is>
           <t>Shares Outstanding</t>
         </is>
       </c>
-      <c r="C12" s="66" t="n"/>
-      <c r="D12" s="78" t="n">
+      <c r="C12" s="68" t="n"/>
+      <c r="D12" s="81" t="n">
         <v>21597.635</v>
       </c>
-      <c r="E12" s="66" t="n"/>
-      <c r="F12" s="66" t="n"/>
-      <c r="G12" s="66" t="n"/>
-      <c r="H12" s="66" t="n"/>
-      <c r="I12" s="66" t="n"/>
-      <c r="J12" s="66" t="n"/>
-      <c r="K12" s="66" t="n"/>
-      <c r="L12" s="66" t="n"/>
-      <c r="M12" s="66" t="n"/>
-      <c r="N12" s="66" t="n"/>
-      <c r="O12" s="66" t="n"/>
+      <c r="E12" s="68" t="n"/>
+      <c r="F12" s="68" t="n"/>
+      <c r="G12" s="68" t="n"/>
+      <c r="H12" s="68" t="n"/>
+      <c r="I12" s="68" t="n"/>
+      <c r="J12" s="68" t="n"/>
+      <c r="K12" s="68" t="n"/>
+      <c r="L12" s="68" t="n"/>
+      <c r="M12" s="68" t="n"/>
+      <c r="N12" s="68" t="n"/>
+      <c r="O12" s="68" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="66" t="n"/>
-      <c r="B13" s="66" t="inlineStr">
+      <c r="A13" s="68" t="n"/>
+      <c r="B13" s="68" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="C13" s="66" t="n"/>
-      <c r="D13" s="79" t="n">
+      <c r="C13" s="68" t="n"/>
+      <c r="D13" s="82" t="n">
         <v>5582389</v>
       </c>
-      <c r="E13" s="66" t="n"/>
-      <c r="F13" s="66" t="n"/>
-      <c r="G13" s="66" t="n"/>
-      <c r="H13" s="66" t="n"/>
-      <c r="I13" s="66" t="n"/>
-      <c r="J13" s="66" t="n"/>
-      <c r="K13" s="66" t="n"/>
-      <c r="L13" s="66" t="n"/>
-      <c r="M13" s="66" t="n"/>
-      <c r="N13" s="66" t="n"/>
-      <c r="O13" s="66" t="n"/>
+      <c r="E13" s="68" t="n"/>
+      <c r="F13" s="68" t="n"/>
+      <c r="G13" s="68" t="n"/>
+      <c r="H13" s="68" t="n"/>
+      <c r="I13" s="68" t="n"/>
+      <c r="J13" s="68" t="n"/>
+      <c r="K13" s="68" t="n"/>
+      <c r="L13" s="68" t="n"/>
+      <c r="M13" s="68" t="n"/>
+      <c r="N13" s="68" t="n"/>
+      <c r="O13" s="68" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="66" t="n"/>
-      <c r="B14" s="66" t="inlineStr">
+      <c r="A14" s="68" t="n"/>
+      <c r="B14" s="68" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="79" t="n">
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="82" t="n">
         <v>304537</v>
       </c>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="66" t="n"/>
-      <c r="G14" s="66" t="n"/>
-      <c r="H14" s="66" t="n"/>
-      <c r="I14" s="66" t="n"/>
-      <c r="J14" s="66" t="n"/>
-      <c r="K14" s="66" t="n"/>
-      <c r="L14" s="66" t="n"/>
-      <c r="M14" s="66" t="n"/>
-      <c r="N14" s="66" t="n"/>
-      <c r="O14" s="66" t="n"/>
+      <c r="E14" s="68" t="n"/>
+      <c r="F14" s="68" t="n"/>
+      <c r="G14" s="68" t="n"/>
+      <c r="H14" s="68" t="n"/>
+      <c r="I14" s="68" t="n"/>
+      <c r="J14" s="68" t="n"/>
+      <c r="K14" s="68" t="n"/>
+      <c r="L14" s="68" t="n"/>
+      <c r="M14" s="68" t="n"/>
+      <c r="N14" s="68" t="n"/>
+      <c r="O14" s="68" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="66" t="n"/>
-      <c r="B15" s="66" t="inlineStr">
+      <c r="A15" s="68" t="n"/>
+      <c r="B15" s="68" t="inlineStr">
         <is>
           <t>Capex</t>
         </is>
       </c>
-      <c r="C15" s="66" t="n"/>
-      <c r="D15" s="80" t="n">
+      <c r="C15" s="68" t="n"/>
+      <c r="D15" s="71" t="n">
         <v>39407</v>
       </c>
-      <c r="E15" s="66" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="F15" s="66" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="G15" s="66" t="inlineStr">
-        <is>
-          <t>Capex</t>
-        </is>
-      </c>
-      <c r="H15" s="66" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="I15" s="66" t="n"/>
-      <c r="J15" s="66" t="n"/>
-      <c r="K15" s="66" t="n"/>
-      <c r="L15" s="66" t="n"/>
-      <c r="M15" s="66" t="n"/>
-      <c r="N15" s="66" t="n"/>
-      <c r="O15" s="66" t="n"/>
+      <c r="E15" s="68" t="n"/>
+      <c r="F15" s="68" t="n"/>
+      <c r="G15" s="68" t="n"/>
+      <c r="H15" s="68" t="n"/>
+      <c r="I15" s="68" t="n"/>
+      <c r="J15" s="68" t="n"/>
+      <c r="K15" s="68" t="n"/>
+      <c r="L15" s="68" t="n"/>
+      <c r="M15" s="68" t="n"/>
+      <c r="N15" s="68" t="n"/>
+      <c r="O15" s="68" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="66" t="n"/>
-      <c r="B16" s="66" t="inlineStr">
-        <is>
-          <t>FY2025 actuals (10-K base)</t>
-        </is>
-      </c>
-      <c r="C16" s="66" t="n"/>
-      <c r="D16" s="81" t="inlineStr">
-        <is>
-          <t>EBIT/DA/Capex/Tax</t>
-        </is>
-      </c>
-      <c r="E16" s="82" t="n">
-        <v>924850</v>
-      </c>
-      <c r="F16" s="82" t="n">
-        <v>14952</v>
-      </c>
-      <c r="G16" s="82" t="n">
-        <v>39407</v>
-      </c>
-      <c r="H16" s="82" t="n">
-        <v>150649</v>
-      </c>
-      <c r="J16" s="66" t="n"/>
-      <c r="K16" s="66" t="n"/>
-      <c r="L16" s="66" t="n"/>
-      <c r="M16" s="66" t="n"/>
-      <c r="N16" s="66" t="n"/>
-      <c r="O16" s="66" t="n"/>
+      <c r="A16" s="68" t="n"/>
+      <c r="B16" s="68" t="inlineStr">
+        <is>
+          <t>Capex growth</t>
+        </is>
+      </c>
+      <c r="C16" s="68" t="n"/>
+      <c r="D16" s="26" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J16" s="68" t="n"/>
+      <c r="K16" s="68" t="n"/>
+      <c r="L16" s="68" t="n"/>
+      <c r="M16" s="68" t="n"/>
+      <c r="N16" s="68" t="n"/>
+      <c r="O16" s="68" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="66" t="n"/>
+      <c r="A17" s="68" t="n"/>
       <c r="B17" s="83" t="inlineStr">
         <is>
           <t>Discounted Cash Flow</t>
@@ -5535,27 +5838,32 @@
           <t>Entry</t>
         </is>
       </c>
-      <c r="E17" s="86" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F17" s="86" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G17" s="86" t="n">
-        <v>2028</v>
-      </c>
-      <c r="H17" s="86" t="n">
-        <v>2029</v>
-      </c>
-      <c r="I17" s="86" t="n">
-        <v>2030</v>
+      <c r="E17" s="86">
+        <f>YEAR(E18)</f>
+        <v/>
+      </c>
+      <c r="F17" s="86">
+        <f>YEAR(F18)</f>
+        <v/>
+      </c>
+      <c r="G17" s="86">
+        <f>YEAR(G18)</f>
+        <v/>
+      </c>
+      <c r="H17" s="86">
+        <f>YEAR(H18)</f>
+        <v/>
+      </c>
+      <c r="I17" s="86">
+        <f>YEAR(I18)</f>
+        <v/>
       </c>
       <c r="J17" s="85" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
       </c>
-      <c r="K17" s="66" t="n"/>
+      <c r="K17" s="68" t="n"/>
       <c r="L17" s="83" t="inlineStr">
         <is>
           <t>Terminal Value</t>
@@ -5563,421 +5871,485 @@
       </c>
       <c r="M17" s="84" t="n"/>
       <c r="N17" s="84" t="n"/>
-      <c r="O17" s="66" t="n"/>
+      <c r="O17" s="68" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="66" t="n"/>
-      <c r="B18" s="66" t="inlineStr">
+      <c r="A18" s="68" t="n"/>
+      <c r="B18" s="68" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C18" s="66" t="n"/>
-      <c r="D18" s="87" t="n">
-        <v>45930</v>
-      </c>
-      <c r="E18" s="87" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F18" s="87" t="n">
-        <v>46660</v>
-      </c>
-      <c r="G18" s="87" t="n">
-        <v>47026</v>
-      </c>
-      <c r="H18" s="87" t="n">
-        <v>47391</v>
-      </c>
-      <c r="I18" s="87" t="n">
-        <v>47756</v>
-      </c>
-      <c r="J18" s="88" t="n">
-        <v>47756</v>
-      </c>
-      <c r="K18" s="66" t="n"/>
-      <c r="L18" s="66" t="inlineStr">
+      <c r="C18" s="68" t="n"/>
+      <c r="D18" s="87">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="E18" s="87">
+        <f>DATE(YEAR($D$10)+E19,9,30)</f>
+        <v/>
+      </c>
+      <c r="F18" s="87">
+        <f>DATE(YEAR($D$10)+F19,9,30)</f>
+        <v/>
+      </c>
+      <c r="G18" s="87">
+        <f>DATE(YEAR($D$10)+G19,9,30)</f>
+        <v/>
+      </c>
+      <c r="H18" s="87">
+        <f>DATE(YEAR($D$10)+H19,9,30)</f>
+        <v/>
+      </c>
+      <c r="I18" s="87">
+        <f>DATE(YEAR($D$10)+I19,9,30)</f>
+        <v/>
+      </c>
+      <c r="J18" s="87">
+        <f>I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="68" t="n"/>
+      <c r="L18" s="68" t="inlineStr">
         <is>
           <t>Perpetual Growth</t>
         </is>
       </c>
-      <c r="M18" s="66" t="n"/>
-      <c r="N18" s="89" t="n">
-        <v>18113172.1</v>
-      </c>
-      <c r="O18" s="66" t="n"/>
+      <c r="M18" s="68" t="n"/>
+      <c r="N18" s="88">
+        <f>(I26*(1+D7))/(D6-D7)</f>
+        <v/>
+      </c>
+      <c r="O18" s="68" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="66" t="n"/>
-      <c r="B19" s="90" t="inlineStr">
+      <c r="A19" s="68" t="n"/>
+      <c r="B19" s="89" t="inlineStr">
         <is>
           <t>Time Periods</t>
         </is>
       </c>
-      <c r="C19" s="90" t="n"/>
-      <c r="D19" s="91" t="n"/>
-      <c r="E19" s="92" t="n">
+      <c r="C19" s="89" t="n"/>
+      <c r="D19" s="90" t="n"/>
+      <c r="E19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="93" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="93" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="93" t="n">
-        <v>5</v>
-      </c>
-      <c r="J19" s="91" t="n"/>
-      <c r="K19" s="66" t="n"/>
-      <c r="L19" s="66" t="inlineStr">
+      <c r="F19" s="86">
+        <f>E19+1</f>
+        <v/>
+      </c>
+      <c r="G19" s="86">
+        <f>F19+1</f>
+        <v/>
+      </c>
+      <c r="H19" s="86">
+        <f>G19+1</f>
+        <v/>
+      </c>
+      <c r="I19" s="86">
+        <f>H19+1</f>
+        <v/>
+      </c>
+      <c r="J19" s="90" t="n"/>
+      <c r="K19" s="68" t="n"/>
+      <c r="L19" s="68" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="M19" s="66" t="n"/>
-      <c r="N19" s="89" t="n">
-        <v>34250977</v>
-      </c>
-      <c r="O19" s="66" t="n"/>
+      <c r="M19" s="68" t="n"/>
+      <c r="N19" s="88">
+        <f>D8*(I21+I23)</f>
+        <v/>
+      </c>
+      <c r="O19" s="68" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="66" t="n"/>
-      <c r="B20" s="90" t="inlineStr">
+      <c r="A20" s="68" t="n"/>
+      <c r="B20" s="89" t="inlineStr">
         <is>
           <t>Year Fraction</t>
         </is>
       </c>
-      <c r="C20" s="66" t="n"/>
-      <c r="D20" s="66" t="n"/>
-      <c r="E20" s="94" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="94" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="94" t="n">
-        <v>1.0027</v>
-      </c>
-      <c r="H20" s="94" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="94" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="66" t="n"/>
-      <c r="K20" s="66" t="n"/>
-      <c r="L20" s="66" t="inlineStr">
+      <c r="C20" s="68" t="n"/>
+      <c r="D20" s="68" t="n"/>
+      <c r="E20" s="91">
+        <f>YEARFRAC(D18,E18)</f>
+        <v/>
+      </c>
+      <c r="F20" s="91">
+        <f>YEARFRAC(E18,F18)</f>
+        <v/>
+      </c>
+      <c r="G20" s="91">
+        <f>YEARFRAC(F18,G18)</f>
+        <v/>
+      </c>
+      <c r="H20" s="91">
+        <f>YEARFRAC(G18,H18)</f>
+        <v/>
+      </c>
+      <c r="I20" s="91">
+        <f>YEARFRAC(H18,I18)</f>
+        <v/>
+      </c>
+      <c r="J20" s="68" t="n"/>
+      <c r="K20" s="68" t="n"/>
+      <c r="L20" s="68" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="M20" s="66" t="n"/>
-      <c r="N20" s="95" t="n">
-        <v>26182074.6</v>
-      </c>
-      <c r="O20" s="66" t="n"/>
+      <c r="M20" s="68" t="n"/>
+      <c r="N20" s="92">
+        <f>AVERAGE(N18:N19)</f>
+        <v/>
+      </c>
+      <c r="O20" s="68" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="66" t="n"/>
-      <c r="B21" s="66" t="inlineStr">
-        <is>
-          <t>EBIT (= Operating income path)</t>
-        </is>
-      </c>
-      <c r="C21" s="66" t="n"/>
-      <c r="D21" s="66" t="n"/>
-      <c r="E21" s="80" t="n">
-        <v>1031318.4</v>
-      </c>
-      <c r="F21" s="80" t="n">
-        <v>1149880.5</v>
-      </c>
-      <c r="G21" s="80" t="n">
-        <v>1270112.3</v>
-      </c>
-      <c r="H21" s="80" t="n">
-        <v>1398473.3</v>
-      </c>
-      <c r="I21" s="80" t="n">
-        <v>1533659.6</v>
-      </c>
-      <c r="J21" s="66" t="n"/>
-      <c r="K21" s="66" t="n"/>
-      <c r="L21" s="66" t="n"/>
-      <c r="M21" s="66" t="n"/>
-      <c r="N21" s="66" t="n"/>
-      <c r="O21" s="66" t="n"/>
+      <c r="A21" s="68" t="n"/>
+      <c r="B21" s="68" t="inlineStr">
+        <is>
+          <t>EBIT (linked 3-stmt GP−SG&amp;A−R&amp;D−D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C21" s="68" t="n"/>
+      <c r="D21" s="68" t="n"/>
+      <c r="E21" s="93">
+        <f>'03_Three_Statement'!J26-'03_Three_Statement'!J28-'03_Three_Statement'!J29-'03_Three_Statement'!J30</f>
+        <v/>
+      </c>
+      <c r="F21" s="93">
+        <f>'03_Three_Statement'!K26-'03_Three_Statement'!K28-'03_Three_Statement'!K29-'03_Three_Statement'!K30</f>
+        <v/>
+      </c>
+      <c r="G21" s="93">
+        <f>'03_Three_Statement'!L26-'03_Three_Statement'!L28-'03_Three_Statement'!L29-'03_Three_Statement'!L30</f>
+        <v/>
+      </c>
+      <c r="H21" s="93">
+        <f>'03_Three_Statement'!M26-'03_Three_Statement'!M28-'03_Three_Statement'!M29-'03_Three_Statement'!M30</f>
+        <v/>
+      </c>
+      <c r="I21" s="93">
+        <f>'03_Three_Statement'!N26-'03_Three_Statement'!N28-'03_Three_Statement'!N29-'03_Three_Statement'!N30</f>
+        <v/>
+      </c>
+      <c r="J21" s="68" t="n"/>
+      <c r="K21" s="68" t="n"/>
+      <c r="L21" s="68" t="n"/>
+      <c r="M21" s="68" t="n"/>
+      <c r="N21" s="68" t="n"/>
+      <c r="O21" s="68" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="66" t="n"/>
-      <c r="B22" s="66" t="inlineStr">
-        <is>
-          <t>Less: Cash Taxes</t>
-        </is>
-      </c>
-      <c r="C22" s="66" t="n"/>
-      <c r="D22" s="66" t="n"/>
-      <c r="E22" s="89" t="n">
-        <v>193580.9</v>
-      </c>
-      <c r="F22" s="89" t="n">
-        <v>215835.3</v>
-      </c>
-      <c r="G22" s="89" t="n">
-        <v>238403.1</v>
-      </c>
-      <c r="H22" s="89" t="n">
-        <v>262496.8</v>
-      </c>
-      <c r="I22" s="89" t="n">
-        <v>287871.6</v>
-      </c>
-      <c r="J22" s="66" t="n"/>
-      <c r="K22" s="66" t="n"/>
-      <c r="L22" s="66" t="n"/>
-      <c r="M22" s="66" t="n"/>
-      <c r="N22" s="66" t="n"/>
-      <c r="O22" s="66" t="n"/>
+      <c r="A22" s="68" t="n"/>
+      <c r="B22" s="68" t="inlineStr">
+        <is>
+          <t>Less: Cash Taxes (=EBIT×D5)</t>
+        </is>
+      </c>
+      <c r="C22" s="68" t="n"/>
+      <c r="D22" s="68" t="n"/>
+      <c r="E22" s="88">
+        <f>E21*$D$5</f>
+        <v/>
+      </c>
+      <c r="F22" s="88">
+        <f>F21*$D$5</f>
+        <v/>
+      </c>
+      <c r="G22" s="88">
+        <f>G21*$D$5</f>
+        <v/>
+      </c>
+      <c r="H22" s="88">
+        <f>H21*$D$5</f>
+        <v/>
+      </c>
+      <c r="I22" s="88">
+        <f>I21*$D$5</f>
+        <v/>
+      </c>
+      <c r="J22" s="68" t="n"/>
+      <c r="K22" s="68" t="n"/>
+      <c r="L22" s="68" t="n"/>
+      <c r="M22" s="68" t="n"/>
+      <c r="N22" s="68" t="n"/>
+      <c r="O22" s="68" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="66" t="n"/>
-      <c r="B23" s="66" t="inlineStr">
-        <is>
-          <t>Plus: D&amp;A</t>
-        </is>
-      </c>
-      <c r="C23" s="66" t="n"/>
-      <c r="D23" s="66" t="n"/>
-      <c r="E23" s="80" t="n">
-        <v>16746.2</v>
-      </c>
-      <c r="F23" s="80" t="n">
-        <v>18420.9</v>
-      </c>
-      <c r="G23" s="80" t="n">
-        <v>20078.7</v>
-      </c>
-      <c r="H23" s="80" t="n">
-        <v>21685</v>
-      </c>
-      <c r="I23" s="80" t="n">
-        <v>23203</v>
-      </c>
-      <c r="J23" s="66" t="n"/>
-      <c r="K23" s="66" t="n"/>
-      <c r="L23" s="66" t="n"/>
-      <c r="M23" s="66" t="n"/>
-      <c r="N23" s="66" t="n"/>
-      <c r="O23" s="66" t="n"/>
+      <c r="A23" s="68" t="n"/>
+      <c r="B23" s="68" t="inlineStr">
+        <is>
+          <t>Plus: D&amp;A (linked 3-stmt)</t>
+        </is>
+      </c>
+      <c r="C23" s="68" t="n"/>
+      <c r="D23" s="68" t="n"/>
+      <c r="E23" s="93">
+        <f>'03_Three_Statement'!J30</f>
+        <v/>
+      </c>
+      <c r="F23" s="93">
+        <f>'03_Three_Statement'!K30</f>
+        <v/>
+      </c>
+      <c r="G23" s="93">
+        <f>'03_Three_Statement'!L30</f>
+        <v/>
+      </c>
+      <c r="H23" s="93">
+        <f>'03_Three_Statement'!M30</f>
+        <v/>
+      </c>
+      <c r="I23" s="93">
+        <f>'03_Three_Statement'!N30</f>
+        <v/>
+      </c>
+      <c r="J23" s="68" t="n"/>
+      <c r="K23" s="68" t="n"/>
+      <c r="L23" s="68" t="n"/>
+      <c r="M23" s="68" t="n"/>
+      <c r="N23" s="68" t="n"/>
+      <c r="O23" s="68" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="66" t="n"/>
-      <c r="B24" s="66" t="inlineStr">
-        <is>
-          <t>Less: Capex (grows w/ rev)</t>
-        </is>
-      </c>
-      <c r="C24" s="66" t="n"/>
-      <c r="D24" s="66" t="n"/>
-      <c r="E24" s="96" t="n">
-        <v>42559.6</v>
-      </c>
-      <c r="F24" s="96" t="n">
-        <v>45964.3</v>
-      </c>
-      <c r="G24" s="96" t="n">
-        <v>49641.5</v>
-      </c>
-      <c r="H24" s="96" t="n">
-        <v>53612.8</v>
-      </c>
-      <c r="I24" s="96" t="n">
-        <v>57901.8</v>
-      </c>
-      <c r="J24" s="66" t="n"/>
-      <c r="K24" s="66" t="n"/>
-      <c r="L24" s="66" t="n"/>
-      <c r="M24" s="66" t="n"/>
-      <c r="N24" s="66" t="n"/>
-      <c r="O24" s="66" t="n"/>
+      <c r="A24" s="68" t="n"/>
+      <c r="B24" s="68" t="inlineStr">
+        <is>
+          <t>Less: Capex (linked 3-stmt row 68)</t>
+        </is>
+      </c>
+      <c r="C24" s="68" t="n"/>
+      <c r="D24" s="68" t="n"/>
+      <c r="E24" s="93">
+        <f>'03_Three_Statement'!J68</f>
+        <v/>
+      </c>
+      <c r="F24" s="93">
+        <f>'03_Three_Statement'!K68</f>
+        <v/>
+      </c>
+      <c r="G24" s="93">
+        <f>'03_Three_Statement'!L68</f>
+        <v/>
+      </c>
+      <c r="H24" s="93">
+        <f>'03_Three_Statement'!M68</f>
+        <v/>
+      </c>
+      <c r="I24" s="93">
+        <f>'03_Three_Statement'!N68</f>
+        <v/>
+      </c>
+      <c r="J24" s="68" t="n"/>
+      <c r="K24" s="68" t="n"/>
+      <c r="L24" s="68" t="n"/>
+      <c r="M24" s="68" t="n"/>
+      <c r="N24" s="68" t="n"/>
+      <c r="O24" s="68" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="66" t="n"/>
-      <c r="B25" s="66" t="inlineStr">
-        <is>
-          <t>Less: Changes in NWC</t>
-        </is>
-      </c>
-      <c r="C25" s="66" t="n"/>
-      <c r="D25" s="66" t="n"/>
-      <c r="E25" s="80" t="n">
-        <v>59620</v>
-      </c>
-      <c r="F25" s="80" t="n">
-        <v>55645.3</v>
-      </c>
-      <c r="G25" s="80" t="n">
-        <v>55088.8</v>
-      </c>
-      <c r="H25" s="80" t="n">
-        <v>53375</v>
-      </c>
-      <c r="I25" s="80" t="n">
-        <v>50439.3</v>
-      </c>
-      <c r="J25" s="66" t="n"/>
-      <c r="K25" s="66" t="n"/>
-      <c r="L25" s="66" t="n"/>
-      <c r="M25" s="66" t="n"/>
-      <c r="N25" s="66" t="n"/>
-      <c r="O25" s="66" t="n"/>
+      <c r="A25" s="68" t="n"/>
+      <c r="B25" s="68" t="inlineStr">
+        <is>
+          <t>Less: ΔNWC (linked 3-stmt row 89)</t>
+        </is>
+      </c>
+      <c r="C25" s="68" t="n"/>
+      <c r="D25" s="68" t="n"/>
+      <c r="E25" s="93">
+        <f>'03_Three_Statement'!J89</f>
+        <v/>
+      </c>
+      <c r="F25" s="93">
+        <f>'03_Three_Statement'!K89</f>
+        <v/>
+      </c>
+      <c r="G25" s="93">
+        <f>'03_Three_Statement'!L89</f>
+        <v/>
+      </c>
+      <c r="H25" s="93">
+        <f>'03_Three_Statement'!M89</f>
+        <v/>
+      </c>
+      <c r="I25" s="93">
+        <f>'03_Three_Statement'!N89</f>
+        <v/>
+      </c>
+      <c r="J25" s="68" t="n"/>
+      <c r="K25" s="68" t="n"/>
+      <c r="L25" s="68" t="n"/>
+      <c r="M25" s="68" t="n"/>
+      <c r="N25" s="68" t="n"/>
+      <c r="O25" s="68" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="66" t="n"/>
-      <c r="B26" s="66" t="inlineStr">
-        <is>
-          <t>Unlevered FCF</t>
-        </is>
-      </c>
-      <c r="C26" s="66" t="n"/>
-      <c r="D26" s="66" t="n"/>
-      <c r="E26" s="95" t="n">
-        <v>752304.2</v>
-      </c>
-      <c r="F26" s="95" t="n">
-        <v>850856.4</v>
-      </c>
-      <c r="G26" s="95" t="n">
-        <v>947057.6</v>
-      </c>
-      <c r="H26" s="95" t="n">
-        <v>1050673.8</v>
-      </c>
-      <c r="I26" s="95" t="n">
-        <v>1160649.9</v>
-      </c>
-      <c r="J26" s="66" t="n"/>
-      <c r="K26" s="66" t="n"/>
-      <c r="L26" s="66" t="n"/>
-      <c r="M26" s="66" t="n"/>
-      <c r="N26" s="66" t="n"/>
-      <c r="O26" s="66" t="n"/>
+      <c r="A26" s="68" t="n"/>
+      <c r="B26" s="68" t="inlineStr">
+        <is>
+          <t>Unlevered FCF (formula)</t>
+        </is>
+      </c>
+      <c r="C26" s="68" t="n"/>
+      <c r="D26" s="68" t="n"/>
+      <c r="E26" s="92">
+        <f>E21-E22+E23-E24-E25</f>
+        <v/>
+      </c>
+      <c r="F26" s="92">
+        <f>F21-F22+F23-F24-F25</f>
+        <v/>
+      </c>
+      <c r="G26" s="92">
+        <f>G21-G22+G23-G24-G25</f>
+        <v/>
+      </c>
+      <c r="H26" s="92">
+        <f>H21-H22+H23-H24-H25</f>
+        <v/>
+      </c>
+      <c r="I26" s="92">
+        <f>I21-I22+I23-I24-I25</f>
+        <v/>
+      </c>
+      <c r="J26" s="68" t="n"/>
+      <c r="K26" s="68" t="n"/>
+      <c r="L26" s="68" t="n"/>
+      <c r="M26" s="68" t="n"/>
+      <c r="N26" s="68" t="n"/>
+      <c r="O26" s="68" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="66" t="n"/>
-      <c r="B27" s="66" t="inlineStr">
+      <c r="A27" s="68" t="n"/>
+      <c r="B27" s="68" t="inlineStr">
         <is>
           <t>(Entry)/Exit</t>
         </is>
       </c>
-      <c r="C27" s="66" t="n"/>
-      <c r="D27" s="89" t="n">
-        <v>-27873945.7</v>
-      </c>
-      <c r="E27" s="66" t="n"/>
-      <c r="F27" s="66" t="n"/>
-      <c r="G27" s="66" t="n"/>
-      <c r="H27" s="66" t="n"/>
-      <c r="I27" s="66" t="n"/>
-      <c r="J27" s="89" t="n">
-        <v>26182074.6</v>
-      </c>
-      <c r="K27" s="66" t="n"/>
-      <c r="L27" s="66" t="n"/>
-      <c r="M27" s="66" t="n"/>
-      <c r="N27" s="66" t="n"/>
-      <c r="O27" s="66" t="n"/>
+      <c r="C27" s="68" t="n"/>
+      <c r="D27" s="88">
+        <f>-I35</f>
+        <v/>
+      </c>
+      <c r="E27" s="68" t="n"/>
+      <c r="F27" s="68" t="n"/>
+      <c r="G27" s="68" t="n"/>
+      <c r="H27" s="68" t="n"/>
+      <c r="I27" s="68" t="n"/>
+      <c r="J27" s="88">
+        <f>N20</f>
+        <v/>
+      </c>
+      <c r="K27" s="68" t="n"/>
+      <c r="L27" s="68" t="n"/>
+      <c r="M27" s="68" t="n"/>
+      <c r="N27" s="68" t="n"/>
+      <c r="O27" s="68" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="66" t="n"/>
-      <c r="B28" s="66" t="inlineStr">
+      <c r="A28" s="68" t="n"/>
+      <c r="B28" s="68" t="inlineStr">
         <is>
           <t>Transaction CF</t>
         </is>
       </c>
-      <c r="C28" s="66" t="n"/>
-      <c r="D28" s="95" t="n">
+      <c r="C28" s="68" t="n"/>
+      <c r="D28" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="95" t="n">
-        <v>752304.2</v>
-      </c>
-      <c r="F28" s="95" t="n">
-        <v>850856.4</v>
-      </c>
-      <c r="G28" s="95" t="n">
-        <v>949652.3</v>
-      </c>
-      <c r="H28" s="95" t="n">
-        <v>1050673.8</v>
-      </c>
-      <c r="I28" s="95" t="n">
-        <v>1160649.9</v>
-      </c>
-      <c r="J28" s="95" t="n">
-        <v>26182074.6</v>
-      </c>
-      <c r="K28" s="66" t="n"/>
-      <c r="L28" s="66" t="n"/>
-      <c r="M28" s="66" t="n"/>
-      <c r="N28" s="66" t="n"/>
-      <c r="O28" s="66" t="n"/>
+      <c r="E28" s="92">
+        <f>(E27+E26)*E20</f>
+        <v/>
+      </c>
+      <c r="F28" s="92">
+        <f>(F27+F26)*F20</f>
+        <v/>
+      </c>
+      <c r="G28" s="92">
+        <f>(G27+G26)*G20</f>
+        <v/>
+      </c>
+      <c r="H28" s="92">
+        <f>(H27+H26)*H20</f>
+        <v/>
+      </c>
+      <c r="I28" s="92">
+        <f>(I27+I26)*I20</f>
+        <v/>
+      </c>
+      <c r="J28" s="92">
+        <f>J27+J26</f>
+        <v/>
+      </c>
+      <c r="K28" s="68" t="n"/>
+      <c r="L28" s="68" t="n"/>
+      <c r="M28" s="68" t="n"/>
+      <c r="N28" s="68" t="n"/>
+      <c r="O28" s="68" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="66" t="n"/>
-      <c r="B29" s="66" t="inlineStr">
+      <c r="A29" s="68" t="n"/>
+      <c r="B29" s="68" t="inlineStr">
         <is>
           <t>Transaction CF</t>
         </is>
       </c>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="89" t="n">
-        <v>-27873945.7</v>
-      </c>
-      <c r="E29" s="89" t="n">
-        <v>752304.2</v>
-      </c>
-      <c r="F29" s="89" t="n">
-        <v>850856.4</v>
-      </c>
-      <c r="G29" s="89" t="n">
-        <v>949652.3</v>
-      </c>
-      <c r="H29" s="89" t="n">
-        <v>1050673.8</v>
-      </c>
-      <c r="I29" s="89" t="n">
-        <v>1160649.9</v>
-      </c>
-      <c r="J29" s="89" t="n">
-        <v>26182074.6</v>
-      </c>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="66" t="n"/>
-      <c r="O29" s="66" t="n"/>
+      <c r="C29" s="68" t="n"/>
+      <c r="D29" s="88">
+        <f>D27+D26</f>
+        <v/>
+      </c>
+      <c r="E29" s="88">
+        <f>(E27+E26)*E20</f>
+        <v/>
+      </c>
+      <c r="F29" s="88">
+        <f>(F27+F26)*F20</f>
+        <v/>
+      </c>
+      <c r="G29" s="88">
+        <f>(G27+G26)*G20</f>
+        <v/>
+      </c>
+      <c r="H29" s="88">
+        <f>(H27+H26)*H20</f>
+        <v/>
+      </c>
+      <c r="I29" s="88">
+        <f>(I27+I26)*I20</f>
+        <v/>
+      </c>
+      <c r="J29" s="88">
+        <f>J27</f>
+        <v/>
+      </c>
+      <c r="K29" s="68" t="n"/>
+      <c r="L29" s="68" t="n"/>
+      <c r="M29" s="68" t="n"/>
+      <c r="N29" s="68" t="n"/>
+      <c r="O29" s="68" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="66" t="n"/>
-      <c r="B30" s="66" t="n"/>
-      <c r="C30" s="66" t="n"/>
-      <c r="D30" s="68" t="n"/>
-      <c r="E30" s="66" t="n"/>
-      <c r="G30" s="66" t="n"/>
-      <c r="H30" s="66" t="n"/>
-      <c r="I30" s="66" t="n"/>
-      <c r="J30" s="66" t="n"/>
-      <c r="L30" s="66" t="n"/>
-      <c r="M30" s="66" t="n"/>
-      <c r="N30" s="66" t="n"/>
-      <c r="O30" s="66" t="n"/>
+      <c r="A30" s="68" t="n"/>
+      <c r="B30" s="68" t="n"/>
+      <c r="C30" s="68" t="n"/>
+      <c r="D30" s="95" t="n"/>
+      <c r="E30" s="68" t="n"/>
+      <c r="G30" s="68" t="n"/>
+      <c r="H30" s="68" t="n"/>
+      <c r="I30" s="68" t="n"/>
+      <c r="J30" s="68" t="n"/>
+      <c r="L30" s="68" t="n"/>
+      <c r="M30" s="68" t="n"/>
+      <c r="N30" s="68" t="n"/>
+      <c r="O30" s="68" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="66" t="n"/>
+      <c r="A31" s="68" t="n"/>
       <c r="B31" s="83" t="inlineStr">
         <is>
           <t>Intrinsic Value</t>
@@ -5985,7 +6357,7 @@
       </c>
       <c r="C31" s="84" t="n"/>
       <c r="D31" s="84" t="n"/>
-      <c r="E31" s="66" t="n"/>
+      <c r="E31" s="68" t="n"/>
       <c r="G31" s="83" t="inlineStr">
         <is>
           <t>Market Value</t>
@@ -5993,7 +6365,7 @@
       </c>
       <c r="H31" s="84" t="n"/>
       <c r="I31" s="84" t="n"/>
-      <c r="J31" s="66" t="n"/>
+      <c r="J31" s="68" t="n"/>
       <c r="L31" s="83" t="inlineStr">
         <is>
           <t>Rate of Return</t>
@@ -6001,123 +6373,133 @@
       </c>
       <c r="M31" s="84" t="n"/>
       <c r="N31" s="84" t="n"/>
-      <c r="O31" s="66" t="n"/>
+      <c r="O31" s="68" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="66" t="n"/>
-      <c r="B32" s="66" t="inlineStr">
+      <c r="A32" s="68" t="n"/>
+      <c r="B32" s="68" t="inlineStr">
         <is>
           <t>Enterprise Value</t>
         </is>
       </c>
-      <c r="C32" s="66" t="n"/>
-      <c r="D32" s="89" t="n">
-        <v>20127310.6</v>
-      </c>
-      <c r="E32" s="66" t="n"/>
-      <c r="G32" s="66" t="inlineStr">
+      <c r="C32" s="68" t="n"/>
+      <c r="D32" s="88">
+        <f>XNPV(D6,D28:J28,D18:J18)</f>
+        <v/>
+      </c>
+      <c r="E32" s="68" t="n"/>
+      <c r="G32" s="68" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="H32" s="66" t="n"/>
-      <c r="I32" s="89" t="n">
-        <v>22596093.7</v>
-      </c>
-      <c r="J32" s="66" t="n"/>
-      <c r="L32" s="66" t="inlineStr">
+      <c r="H32" s="68" t="n"/>
+      <c r="I32" s="88">
+        <f>D12*D11</f>
+        <v/>
+      </c>
+      <c r="J32" s="68" t="n"/>
+      <c r="L32" s="68" t="inlineStr">
         <is>
           <t>Target Price Upside</t>
         </is>
       </c>
-      <c r="M32" s="66" t="n"/>
-      <c r="N32" s="97" t="n">
-        <v>-0.3428</v>
-      </c>
-      <c r="O32" s="66" t="n"/>
+      <c r="M32" s="68" t="n"/>
+      <c r="N32" s="96">
+        <f>D37/I37-1</f>
+        <v/>
+      </c>
+      <c r="O32" s="68" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="66" t="n"/>
-      <c r="B33" s="66" t="inlineStr">
+      <c r="A33" s="68" t="n"/>
+      <c r="B33" s="68" t="inlineStr">
         <is>
           <t>Plus: Cash</t>
         </is>
       </c>
-      <c r="C33" s="66" t="n"/>
-      <c r="D33" s="89" t="n">
-        <v>304537</v>
-      </c>
-      <c r="E33" s="66" t="n"/>
-      <c r="G33" s="66" t="inlineStr">
+      <c r="C33" s="68" t="n"/>
+      <c r="D33" s="88">
+        <f>+D14</f>
+        <v/>
+      </c>
+      <c r="E33" s="68" t="n"/>
+      <c r="G33" s="68" t="inlineStr">
         <is>
           <t>Plus: Debt</t>
         </is>
       </c>
-      <c r="H33" s="66" t="n"/>
-      <c r="I33" s="89" t="n">
-        <v>5582389</v>
-      </c>
-      <c r="J33" s="66" t="n"/>
-      <c r="L33" s="66" t="inlineStr">
+      <c r="H33" s="68" t="n"/>
+      <c r="I33" s="88">
+        <f>D13</f>
+        <v/>
+      </c>
+      <c r="J33" s="68" t="n"/>
+      <c r="L33" s="68" t="inlineStr">
         <is>
           <t>Internal Rate of Return (IRR)</t>
         </is>
       </c>
-      <c r="M33" s="66" t="n"/>
-      <c r="N33" s="97" t="n">
-        <v>0.0224</v>
-      </c>
-      <c r="O33" s="66" t="n"/>
+      <c r="M33" s="68" t="n"/>
+      <c r="N33" s="96">
+        <f>XIRR(D29:J29,D18:J18)</f>
+        <v/>
+      </c>
+      <c r="O33" s="68" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="66" t="n"/>
-      <c r="B34" s="66" t="inlineStr">
+      <c r="A34" s="68" t="n"/>
+      <c r="B34" s="68" t="inlineStr">
         <is>
           <t>Less: Debt</t>
         </is>
       </c>
-      <c r="C34" s="66" t="n"/>
-      <c r="D34" s="89" t="n">
-        <v>5582389</v>
-      </c>
-      <c r="E34" s="66" t="n"/>
-      <c r="G34" s="66" t="inlineStr">
+      <c r="C34" s="68" t="n"/>
+      <c r="D34" s="88">
+        <f>+D13</f>
+        <v/>
+      </c>
+      <c r="E34" s="68" t="n"/>
+      <c r="G34" s="68" t="inlineStr">
         <is>
           <t>Less: Cash</t>
         </is>
       </c>
-      <c r="H34" s="66" t="n"/>
-      <c r="I34" s="89" t="n">
-        <v>304537</v>
-      </c>
-      <c r="J34" s="66" t="n"/>
-      <c r="L34" s="66" t="n"/>
-      <c r="M34" s="66" t="n"/>
-      <c r="N34" s="66" t="n"/>
-      <c r="O34" s="66" t="n"/>
+      <c r="H34" s="68" t="n"/>
+      <c r="I34" s="88">
+        <f>+D14</f>
+        <v/>
+      </c>
+      <c r="J34" s="68" t="n"/>
+      <c r="L34" s="68" t="n"/>
+      <c r="M34" s="68" t="n"/>
+      <c r="N34" s="68" t="n"/>
+      <c r="O34" s="68" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="66" t="n"/>
-      <c r="B35" s="66" t="inlineStr">
+      <c r="A35" s="68" t="n"/>
+      <c r="B35" s="68" t="inlineStr">
         <is>
           <t>Equity Value</t>
         </is>
       </c>
-      <c r="C35" s="66" t="n"/>
-      <c r="D35" s="95" t="n">
-        <v>14849458.6</v>
-      </c>
-      <c r="E35" s="66" t="n"/>
-      <c r="G35" s="66" t="inlineStr">
+      <c r="C35" s="68" t="n"/>
+      <c r="D35" s="92">
+        <f>D32+D33-D34</f>
+        <v/>
+      </c>
+      <c r="E35" s="68" t="n"/>
+      <c r="G35" s="68" t="inlineStr">
         <is>
           <t>Enterprise Value</t>
         </is>
       </c>
-      <c r="H35" s="66" t="n"/>
-      <c r="I35" s="95" t="n">
-        <v>27873945.7</v>
-      </c>
-      <c r="J35" s="66" t="n"/>
+      <c r="H35" s="68" t="n"/>
+      <c r="I35" s="92">
+        <f>I32+I33-I34</f>
+        <v/>
+      </c>
+      <c r="J35" s="68" t="n"/>
       <c r="L35" s="83" t="inlineStr">
         <is>
           <t>Market Value vs Intrinsic Value</t>
@@ -6125,121 +6507,126 @@
       </c>
       <c r="M35" s="84" t="n"/>
       <c r="N35" s="84" t="n"/>
-      <c r="O35" s="66" t="n"/>
+      <c r="O35" s="68" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="66" t="n"/>
-      <c r="B36" s="66" t="n"/>
-      <c r="C36" s="66" t="n"/>
-      <c r="D36" s="66" t="n"/>
-      <c r="E36" s="66" t="n"/>
-      <c r="G36" s="66" t="n"/>
-      <c r="H36" s="66" t="n"/>
-      <c r="I36" s="98" t="n"/>
-      <c r="J36" s="66" t="n"/>
-      <c r="L36" s="66" t="inlineStr">
+      <c r="A36" s="68" t="n"/>
+      <c r="B36" s="68" t="n"/>
+      <c r="C36" s="68" t="n"/>
+      <c r="D36" s="68" t="n"/>
+      <c r="E36" s="68" t="n"/>
+      <c r="G36" s="68" t="n"/>
+      <c r="H36" s="68" t="n"/>
+      <c r="I36" s="97" t="n"/>
+      <c r="J36" s="68" t="n"/>
+      <c r="L36" s="68" t="inlineStr">
         <is>
           <t>Market Value</t>
         </is>
       </c>
-      <c r="M36" s="66" t="n"/>
-      <c r="N36" s="99" t="n">
-        <v>1046.23</v>
-      </c>
-      <c r="O36" s="66" t="n"/>
+      <c r="M36" s="68" t="n"/>
+      <c r="N36" s="98">
+        <f>I37</f>
+        <v/>
+      </c>
+      <c r="O36" s="68" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="66" t="n"/>
-      <c r="B37" s="66" t="inlineStr">
+      <c r="A37" s="68" t="n"/>
+      <c r="B37" s="68" t="inlineStr">
         <is>
           <t>Equity Value/Share</t>
         </is>
       </c>
-      <c r="C37" s="66" t="n"/>
-      <c r="D37" s="99" t="n">
-        <v>687.55</v>
-      </c>
-      <c r="E37" s="66" t="n"/>
-      <c r="G37" s="66" t="inlineStr">
+      <c r="C37" s="68" t="n"/>
+      <c r="D37" s="98">
+        <f>D35/D12</f>
+        <v/>
+      </c>
+      <c r="E37" s="68" t="n"/>
+      <c r="G37" s="68" t="inlineStr">
         <is>
           <t>Equity Value/Share</t>
         </is>
       </c>
-      <c r="H37" s="66" t="n"/>
-      <c r="I37" s="99" t="n">
-        <v>1046.23</v>
-      </c>
-      <c r="J37" s="66" t="n"/>
-      <c r="L37" s="66" t="inlineStr">
+      <c r="H37" s="68" t="n"/>
+      <c r="I37" s="98">
+        <f>D11</f>
+        <v/>
+      </c>
+      <c r="J37" s="68" t="n"/>
+      <c r="L37" s="68" t="inlineStr">
         <is>
           <t>Upside</t>
         </is>
       </c>
-      <c r="M37" s="66" t="n"/>
-      <c r="N37" s="99" t="n">
-        <v>-358.68</v>
-      </c>
-      <c r="O37" s="66" t="n"/>
+      <c r="M37" s="68" t="n"/>
+      <c r="N37" s="98">
+        <f>D37-I37</f>
+        <v/>
+      </c>
+      <c r="O37" s="68" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="66" t="n"/>
-      <c r="B38" s="66" t="n"/>
-      <c r="C38" s="66" t="n"/>
-      <c r="D38" s="66" t="n"/>
-      <c r="E38" s="66" t="n"/>
-      <c r="G38" s="66" t="n"/>
-      <c r="H38" s="66" t="n"/>
-      <c r="I38" s="66" t="n"/>
-      <c r="J38" s="66" t="n"/>
-      <c r="L38" s="66" t="inlineStr">
+      <c r="A38" s="68" t="n"/>
+      <c r="B38" s="68" t="n"/>
+      <c r="C38" s="68" t="n"/>
+      <c r="D38" s="68" t="n"/>
+      <c r="E38" s="68" t="n"/>
+      <c r="G38" s="68" t="n"/>
+      <c r="H38" s="68" t="n"/>
+      <c r="I38" s="68" t="n"/>
+      <c r="J38" s="68" t="n"/>
+      <c r="L38" s="68" t="inlineStr">
         <is>
           <t>Intrinsic Value</t>
         </is>
       </c>
-      <c r="M38" s="66" t="n"/>
-      <c r="N38" s="99" t="n">
-        <v>687.55</v>
-      </c>
-      <c r="O38" s="66" t="n"/>
+      <c r="M38" s="68" t="n"/>
+      <c r="N38" s="98">
+        <f>SUM(N36:N37)</f>
+        <v/>
+      </c>
+      <c r="O38" s="68" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="66" t="n"/>
-      <c r="C39" s="66" t="n"/>
-      <c r="D39" s="68" t="n"/>
-      <c r="E39" s="66" t="n"/>
-      <c r="G39" s="66" t="n"/>
-      <c r="H39" s="66" t="n"/>
-      <c r="I39" s="67" t="n"/>
-      <c r="J39" s="66" t="n"/>
-      <c r="L39" s="66" t="n"/>
-      <c r="M39" s="66" t="n"/>
-      <c r="N39" s="66" t="n"/>
-      <c r="O39" s="66" t="n"/>
+      <c r="A39" s="68" t="n"/>
+      <c r="C39" s="68" t="n"/>
+      <c r="D39" s="95" t="n"/>
+      <c r="E39" s="68" t="n"/>
+      <c r="G39" s="68" t="n"/>
+      <c r="H39" s="68" t="n"/>
+      <c r="I39" s="69" t="n"/>
+      <c r="J39" s="68" t="n"/>
+      <c r="L39" s="68" t="n"/>
+      <c r="M39" s="68" t="n"/>
+      <c r="N39" s="68" t="n"/>
+      <c r="O39" s="68" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="66" t="n"/>
-      <c r="C40" s="66" t="n"/>
-      <c r="D40" s="68" t="n"/>
-      <c r="E40" s="66" t="n"/>
-      <c r="F40" s="66" t="n"/>
-      <c r="G40" s="66" t="n"/>
-      <c r="H40" s="67" t="n"/>
-      <c r="I40" s="66" t="n"/>
-      <c r="K40" s="66" t="n"/>
-      <c r="L40" s="66" t="n"/>
-      <c r="M40" s="66" t="n"/>
-      <c r="N40" s="66" t="n"/>
-      <c r="O40" s="66" t="n"/>
+      <c r="A40" s="68" t="n"/>
+      <c r="C40" s="68" t="n"/>
+      <c r="D40" s="95" t="n"/>
+      <c r="E40" s="68" t="n"/>
+      <c r="F40" s="68" t="n"/>
+      <c r="G40" s="68" t="n"/>
+      <c r="H40" s="69" t="n"/>
+      <c r="I40" s="68" t="n"/>
+      <c r="K40" s="68" t="n"/>
+      <c r="L40" s="68" t="n"/>
+      <c r="M40" s="68" t="n"/>
+      <c r="N40" s="68" t="n"/>
+      <c r="O40" s="68" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="66" t="n"/>
+      <c r="A41" s="68" t="n"/>
       <c r="B41" s="83" t="inlineStr">
         <is>
           <t>Instructions</t>
         </is>
       </c>
       <c r="C41" s="84" t="n"/>
-      <c r="D41" s="100" t="n"/>
+      <c r="D41" s="99" t="n"/>
       <c r="E41" s="84" t="n"/>
       <c r="F41" s="84" t="n"/>
       <c r="G41" s="84" t="n"/>
@@ -6250,330 +6637,327 @@
       <c r="L41" s="84" t="n"/>
       <c r="M41" s="84" t="n"/>
       <c r="N41" s="84" t="n"/>
-      <c r="O41" s="66" t="n"/>
+      <c r="O41" s="68" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="66" t="n"/>
-      <c r="B42" s="66" t="inlineStr">
+      <c r="A42" s="68" t="n"/>
+      <c r="B42" s="68" t="inlineStr">
         <is>
           <t>Step 1: Get EBIT and D&amp;A from the income statement</t>
         </is>
       </c>
-      <c r="C42" s="66" t="n"/>
-      <c r="D42" s="68" t="n"/>
-      <c r="E42" s="66" t="n"/>
-      <c r="F42" s="66" t="n"/>
-      <c r="G42" s="66" t="n"/>
-      <c r="H42" s="66" t="n"/>
-      <c r="N42" s="101" t="inlineStr">
+      <c r="C42" s="68" t="n"/>
+      <c r="D42" s="95" t="n"/>
+      <c r="E42" s="68" t="n"/>
+      <c r="F42" s="68" t="n"/>
+      <c r="G42" s="68" t="n"/>
+      <c r="H42" s="68" t="n"/>
+      <c r="N42" s="100" t="inlineStr">
         <is>
           <t>This file is for educational purposes only. E&amp;OE</t>
         </is>
       </c>
-      <c r="O42" s="66" t="n"/>
+      <c r="O42" s="68" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="66" t="n"/>
-      <c r="B43" s="66" t="inlineStr">
+      <c r="A43" s="68" t="n"/>
+      <c r="B43" s="68" t="inlineStr">
         <is>
           <t>Step 2: Calculate the net working capital</t>
         </is>
       </c>
-      <c r="C43" s="66" t="n"/>
-      <c r="D43" s="68" t="n"/>
-      <c r="E43" s="66" t="n"/>
-      <c r="F43" s="66" t="n"/>
-      <c r="G43" s="66" t="n"/>
-      <c r="H43" s="66" t="n"/>
-      <c r="N43" s="55" t="n"/>
-      <c r="O43" s="66" t="n"/>
+      <c r="C43" s="68" t="n"/>
+      <c r="D43" s="95" t="n"/>
+      <c r="E43" s="68" t="n"/>
+      <c r="F43" s="68" t="n"/>
+      <c r="G43" s="68" t="n"/>
+      <c r="H43" s="68" t="n"/>
+      <c r="N43" s="58" t="n"/>
+      <c r="O43" s="68" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="66" t="n"/>
-      <c r="B44" s="102" t="inlineStr">
+      <c r="A44" s="68" t="n"/>
+      <c r="B44" s="101" t="inlineStr">
         <is>
           <t>There are two ways to find NWC:</t>
         </is>
       </c>
-      <c r="C44" s="66" t="n"/>
-      <c r="D44" s="68" t="n"/>
-      <c r="E44" s="66" t="n"/>
-      <c r="F44" s="66" t="n"/>
-      <c r="G44" s="66" t="n"/>
-      <c r="H44" s="66" t="n"/>
-      <c r="N44" s="55" t="n"/>
-      <c r="O44" s="66" t="n"/>
+      <c r="C44" s="68" t="n"/>
+      <c r="D44" s="95" t="n"/>
+      <c r="E44" s="68" t="n"/>
+      <c r="F44" s="68" t="n"/>
+      <c r="G44" s="68" t="n"/>
+      <c r="H44" s="68" t="n"/>
+      <c r="N44" s="58" t="n"/>
+      <c r="O44" s="68" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="66" t="n"/>
-      <c r="B45" s="102" t="inlineStr">
+      <c r="A45" s="68" t="n"/>
+      <c r="B45" s="101" t="inlineStr">
         <is>
           <t>1. NWC = Current Assets (less cash) - Current Liabilities (less debt)</t>
         </is>
       </c>
-      <c r="C45" s="66" t="n"/>
-      <c r="D45" s="68" t="n"/>
-      <c r="E45" s="66" t="n"/>
-      <c r="F45" s="66" t="n"/>
-      <c r="G45" s="66" t="n"/>
-      <c r="H45" s="66" t="n"/>
-      <c r="N45" s="55" t="n"/>
-      <c r="O45" s="66" t="n"/>
+      <c r="C45" s="68" t="n"/>
+      <c r="D45" s="95" t="n"/>
+      <c r="E45" s="68" t="n"/>
+      <c r="F45" s="68" t="n"/>
+      <c r="G45" s="68" t="n"/>
+      <c r="H45" s="68" t="n"/>
+      <c r="N45" s="58" t="n"/>
+      <c r="O45" s="68" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="66" t="n"/>
-      <c r="B46" s="102" t="inlineStr">
+      <c r="A46" s="68" t="n"/>
+      <c r="B46" s="101" t="inlineStr">
         <is>
           <t>2. NWC = Accounts Receivable + Inventory - Accounts Payable</t>
         </is>
       </c>
-      <c r="C46" s="66" t="n"/>
-      <c r="D46" s="68" t="n"/>
-      <c r="E46" s="66" t="n"/>
-      <c r="F46" s="66" t="n"/>
-      <c r="G46" s="66" t="n"/>
-      <c r="H46" s="66" t="n"/>
-      <c r="N46" s="55" t="n"/>
-      <c r="O46" s="66" t="n"/>
+      <c r="C46" s="68" t="n"/>
+      <c r="D46" s="95" t="n"/>
+      <c r="E46" s="68" t="n"/>
+      <c r="F46" s="68" t="n"/>
+      <c r="G46" s="68" t="n"/>
+      <c r="H46" s="68" t="n"/>
+      <c r="N46" s="58" t="n"/>
+      <c r="O46" s="68" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="66" t="n"/>
-      <c r="B47" s="66" t="n"/>
-      <c r="C47" s="66" t="n"/>
-      <c r="D47" s="68" t="n"/>
-      <c r="E47" s="66" t="n"/>
-      <c r="F47" s="66" t="n"/>
-      <c r="G47" s="66" t="n"/>
-      <c r="H47" s="66" t="n"/>
-      <c r="N47" s="55" t="n"/>
-      <c r="O47" s="66" t="n"/>
+      <c r="A47" s="68" t="n"/>
+      <c r="B47" s="68" t="n"/>
+      <c r="C47" s="68" t="n"/>
+      <c r="D47" s="95" t="n"/>
+      <c r="E47" s="68" t="n"/>
+      <c r="F47" s="68" t="n"/>
+      <c r="G47" s="68" t="n"/>
+      <c r="H47" s="68" t="n"/>
+      <c r="N47" s="58" t="n"/>
+      <c r="O47" s="68" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="66" t="n"/>
-      <c r="B48" s="66" t="n"/>
-      <c r="C48" s="66" t="n"/>
-      <c r="D48" s="68" t="n"/>
-      <c r="E48" s="66" t="n"/>
-      <c r="F48" s="66" t="n"/>
-      <c r="G48" s="66" t="n"/>
-      <c r="H48" s="66" t="n"/>
-      <c r="N48" s="103" t="inlineStr">
+      <c r="A48" s="68" t="n"/>
+      <c r="B48" s="68" t="n"/>
+      <c r="C48" s="68" t="n"/>
+      <c r="D48" s="95" t="n"/>
+      <c r="E48" s="68" t="n"/>
+      <c r="F48" s="68" t="n"/>
+      <c r="G48" s="68" t="n"/>
+      <c r="H48" s="68" t="n"/>
+      <c r="N48" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">Corporate Finance Institute® </t>
         </is>
       </c>
-      <c r="O48" s="66" t="n"/>
+      <c r="O48" s="68" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="66" t="n"/>
-      <c r="B49" s="66" t="n"/>
-      <c r="C49" s="66" t="n"/>
-      <c r="D49" s="68" t="n"/>
-      <c r="E49" s="66" t="n"/>
-      <c r="F49" s="66" t="n"/>
-      <c r="G49" s="66" t="n"/>
-      <c r="H49" s="66" t="n"/>
-      <c r="N49" s="104" t="inlineStr">
+      <c r="A49" s="68" t="n"/>
+      <c r="B49" s="68" t="n"/>
+      <c r="C49" s="68" t="n"/>
+      <c r="D49" s="95" t="n"/>
+      <c r="E49" s="68" t="n"/>
+      <c r="F49" s="68" t="n"/>
+      <c r="G49" s="68" t="n"/>
+      <c r="H49" s="68" t="n"/>
+      <c r="N49" s="103" t="inlineStr">
         <is>
           <t>https://corporatefinanceinstitute.com/</t>
         </is>
       </c>
-      <c r="O49" s="66" t="n"/>
+      <c r="O49" s="68" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="66" t="n"/>
-      <c r="B50" s="105" t="inlineStr">
-        <is>
-          <t>Base FY25 OpInc=924,850 D&amp;A=14,952 Capex=39,407. WACC=9.6% g=3% EV/EBITDA=22x. Source: https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="C50" s="66" t="n"/>
-      <c r="D50" s="68" t="n"/>
-      <c r="E50" s="66" t="n"/>
-      <c r="F50" s="66" t="n"/>
-      <c r="G50" s="66" t="n"/>
-      <c r="H50" s="66" t="n"/>
-      <c r="O50" s="66" t="n"/>
+      <c r="A50" s="68" t="n"/>
+      <c r="B50" s="68" t="n"/>
+      <c r="C50" s="68" t="n"/>
+      <c r="D50" s="95" t="n"/>
+      <c r="E50" s="68" t="n"/>
+      <c r="F50" s="68" t="n"/>
+      <c r="G50" s="68" t="n"/>
+      <c r="H50" s="68" t="n"/>
+      <c r="O50" s="68" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="66" t="n"/>
-      <c r="B51" s="66" t="n"/>
-      <c r="C51" s="66" t="n"/>
-      <c r="D51" s="68" t="n"/>
-      <c r="E51" s="66" t="n"/>
-      <c r="F51" s="66" t="n"/>
-      <c r="G51" s="66" t="n"/>
-      <c r="H51" s="66" t="n"/>
-      <c r="M51" s="66" t="n"/>
-      <c r="O51" s="66" t="n"/>
+      <c r="A51" s="68" t="n"/>
+      <c r="B51" s="68" t="n"/>
+      <c r="C51" s="68" t="n"/>
+      <c r="D51" s="95" t="n"/>
+      <c r="E51" s="68" t="n"/>
+      <c r="F51" s="68" t="n"/>
+      <c r="G51" s="68" t="n"/>
+      <c r="H51" s="68" t="n"/>
+      <c r="M51" s="68" t="n"/>
+      <c r="O51" s="68" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="66" t="n"/>
-      <c r="B52" s="66" t="n"/>
-      <c r="C52" s="66" t="n"/>
-      <c r="D52" s="68" t="n"/>
-      <c r="E52" s="66" t="n"/>
-      <c r="F52" s="66" t="n"/>
-      <c r="G52" s="66" t="n"/>
-      <c r="H52" s="66" t="n"/>
-      <c r="I52" s="66" t="n"/>
-      <c r="J52" s="66" t="n"/>
-      <c r="K52" s="66" t="n"/>
-      <c r="L52" s="66" t="n"/>
-      <c r="M52" s="66" t="n"/>
-      <c r="N52" s="66" t="n"/>
-      <c r="O52" s="66" t="n"/>
+      <c r="A52" s="68" t="n"/>
+      <c r="B52" s="68" t="n"/>
+      <c r="C52" s="68" t="n"/>
+      <c r="D52" s="95" t="n"/>
+      <c r="E52" s="68" t="n"/>
+      <c r="F52" s="68" t="n"/>
+      <c r="G52" s="68" t="n"/>
+      <c r="H52" s="68" t="n"/>
+      <c r="I52" s="68" t="n"/>
+      <c r="J52" s="68" t="n"/>
+      <c r="K52" s="68" t="n"/>
+      <c r="L52" s="68" t="n"/>
+      <c r="M52" s="68" t="n"/>
+      <c r="N52" s="68" t="n"/>
+      <c r="O52" s="68" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="66" t="n"/>
-      <c r="B53" s="66" t="n"/>
-      <c r="C53" s="66" t="n"/>
-      <c r="D53" s="68" t="n"/>
-      <c r="E53" s="66" t="n"/>
-      <c r="F53" s="66" t="n"/>
-      <c r="G53" s="66" t="n"/>
-      <c r="H53" s="66" t="n"/>
-      <c r="I53" s="66" t="n"/>
-      <c r="J53" s="66" t="n"/>
-      <c r="K53" s="66" t="n"/>
-      <c r="L53" s="66" t="n"/>
-      <c r="M53" s="66" t="n"/>
-      <c r="N53" s="66" t="n"/>
-      <c r="O53" s="66" t="n"/>
+      <c r="A53" s="68" t="n"/>
+      <c r="B53" s="68" t="n"/>
+      <c r="C53" s="68" t="n"/>
+      <c r="D53" s="95" t="n"/>
+      <c r="E53" s="68" t="n"/>
+      <c r="F53" s="68" t="n"/>
+      <c r="G53" s="68" t="n"/>
+      <c r="H53" s="68" t="n"/>
+      <c r="I53" s="68" t="n"/>
+      <c r="J53" s="68" t="n"/>
+      <c r="K53" s="68" t="n"/>
+      <c r="L53" s="68" t="n"/>
+      <c r="M53" s="68" t="n"/>
+      <c r="N53" s="68" t="n"/>
+      <c r="O53" s="68" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="66" t="n"/>
-      <c r="B54" s="66" t="n"/>
-      <c r="C54" s="66" t="n"/>
-      <c r="D54" s="68" t="n"/>
-      <c r="E54" s="66" t="n"/>
-      <c r="F54" s="66" t="n"/>
-      <c r="G54" s="66" t="n"/>
-      <c r="H54" s="66" t="n"/>
-      <c r="I54" s="66" t="n"/>
-      <c r="J54" s="66" t="n"/>
-      <c r="K54" s="66" t="n"/>
-      <c r="L54" s="66" t="n"/>
-      <c r="M54" s="66" t="n"/>
-      <c r="N54" s="66" t="n"/>
-      <c r="O54" s="66" t="n"/>
+      <c r="A54" s="68" t="n"/>
+      <c r="B54" s="68" t="n"/>
+      <c r="C54" s="68" t="n"/>
+      <c r="D54" s="95" t="n"/>
+      <c r="E54" s="68" t="n"/>
+      <c r="F54" s="68" t="n"/>
+      <c r="G54" s="68" t="n"/>
+      <c r="H54" s="68" t="n"/>
+      <c r="I54" s="68" t="n"/>
+      <c r="J54" s="68" t="n"/>
+      <c r="K54" s="68" t="n"/>
+      <c r="L54" s="68" t="n"/>
+      <c r="M54" s="68" t="n"/>
+      <c r="N54" s="68" t="n"/>
+      <c r="O54" s="68" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="66" t="n"/>
-      <c r="B55" s="66" t="n"/>
-      <c r="C55" s="66" t="n"/>
-      <c r="D55" s="68" t="n"/>
-      <c r="E55" s="66" t="n"/>
-      <c r="F55" s="66" t="n"/>
-      <c r="G55" s="66" t="n"/>
-      <c r="H55" s="66" t="n"/>
-      <c r="I55" s="66" t="n"/>
-      <c r="J55" s="66" t="n"/>
-      <c r="K55" s="66" t="n"/>
-      <c r="L55" s="66" t="n"/>
-      <c r="M55" s="66" t="n"/>
-      <c r="N55" s="66" t="n"/>
-      <c r="O55" s="66" t="n"/>
+      <c r="A55" s="68" t="n"/>
+      <c r="B55" s="68" t="n"/>
+      <c r="C55" s="68" t="n"/>
+      <c r="D55" s="95" t="n"/>
+      <c r="E55" s="68" t="n"/>
+      <c r="F55" s="68" t="n"/>
+      <c r="G55" s="68" t="n"/>
+      <c r="H55" s="68" t="n"/>
+      <c r="I55" s="68" t="n"/>
+      <c r="J55" s="68" t="n"/>
+      <c r="K55" s="68" t="n"/>
+      <c r="L55" s="68" t="n"/>
+      <c r="M55" s="68" t="n"/>
+      <c r="N55" s="68" t="n"/>
+      <c r="O55" s="68" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="66" t="n"/>
-      <c r="B56" s="66" t="n"/>
-      <c r="C56" s="66" t="n"/>
-      <c r="D56" s="68" t="n"/>
-      <c r="E56" s="66" t="n"/>
-      <c r="F56" s="66" t="n"/>
-      <c r="G56" s="66" t="n"/>
-      <c r="H56" s="66" t="n"/>
-      <c r="I56" s="66" t="n"/>
-      <c r="J56" s="66" t="n"/>
-      <c r="K56" s="66" t="n"/>
-      <c r="L56" s="66" t="n"/>
-      <c r="M56" s="66" t="n"/>
-      <c r="N56" s="66" t="n"/>
-      <c r="O56" s="66" t="n"/>
+      <c r="A56" s="68" t="n"/>
+      <c r="B56" s="68" t="n"/>
+      <c r="C56" s="68" t="n"/>
+      <c r="D56" s="95" t="n"/>
+      <c r="E56" s="68" t="n"/>
+      <c r="F56" s="68" t="n"/>
+      <c r="G56" s="68" t="n"/>
+      <c r="H56" s="68" t="n"/>
+      <c r="I56" s="68" t="n"/>
+      <c r="J56" s="68" t="n"/>
+      <c r="K56" s="68" t="n"/>
+      <c r="L56" s="68" t="n"/>
+      <c r="M56" s="68" t="n"/>
+      <c r="N56" s="68" t="n"/>
+      <c r="O56" s="68" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="66" t="n"/>
-      <c r="B57" s="66" t="n"/>
-      <c r="C57" s="66" t="n"/>
-      <c r="D57" s="68" t="n"/>
-      <c r="E57" s="66" t="n"/>
-      <c r="F57" s="66" t="n"/>
-      <c r="G57" s="66" t="n"/>
-      <c r="H57" s="66" t="n"/>
-      <c r="I57" s="66" t="n"/>
-      <c r="J57" s="66" t="n"/>
-      <c r="K57" s="66" t="n"/>
-      <c r="L57" s="66" t="n"/>
-      <c r="M57" s="66" t="n"/>
-      <c r="N57" s="66" t="n"/>
-      <c r="O57" s="66" t="n"/>
+      <c r="A57" s="68" t="n"/>
+      <c r="B57" s="68" t="n"/>
+      <c r="C57" s="68" t="n"/>
+      <c r="D57" s="95" t="n"/>
+      <c r="E57" s="68" t="n"/>
+      <c r="F57" s="68" t="n"/>
+      <c r="G57" s="68" t="n"/>
+      <c r="H57" s="68" t="n"/>
+      <c r="I57" s="68" t="n"/>
+      <c r="J57" s="68" t="n"/>
+      <c r="K57" s="68" t="n"/>
+      <c r="L57" s="68" t="n"/>
+      <c r="M57" s="68" t="n"/>
+      <c r="N57" s="68" t="n"/>
+      <c r="O57" s="68" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="66" t="n"/>
-      <c r="B58" s="66" t="n"/>
-      <c r="C58" s="66" t="n"/>
-      <c r="D58" s="68" t="n"/>
-      <c r="E58" s="66" t="n"/>
-      <c r="F58" s="66" t="n"/>
-      <c r="G58" s="66" t="n"/>
-      <c r="H58" s="66" t="n"/>
-      <c r="I58" s="66" t="n"/>
-      <c r="J58" s="66" t="n"/>
-      <c r="K58" s="66" t="n"/>
-      <c r="L58" s="66" t="n"/>
-      <c r="M58" s="66" t="n"/>
-      <c r="N58" s="66" t="n"/>
-      <c r="O58" s="66" t="n"/>
+      <c r="A58" s="68" t="n"/>
+      <c r="B58" s="68" t="n"/>
+      <c r="C58" s="68" t="n"/>
+      <c r="D58" s="95" t="n"/>
+      <c r="E58" s="68" t="n"/>
+      <c r="F58" s="68" t="n"/>
+      <c r="G58" s="68" t="n"/>
+      <c r="H58" s="68" t="n"/>
+      <c r="I58" s="68" t="n"/>
+      <c r="J58" s="68" t="n"/>
+      <c r="K58" s="68" t="n"/>
+      <c r="L58" s="68" t="n"/>
+      <c r="M58" s="68" t="n"/>
+      <c r="N58" s="68" t="n"/>
+      <c r="O58" s="68" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="66" t="n"/>
-      <c r="B59" s="66" t="n"/>
-      <c r="C59" s="66" t="n"/>
-      <c r="D59" s="68" t="n"/>
-      <c r="E59" s="66" t="n"/>
-      <c r="F59" s="66" t="n"/>
-      <c r="G59" s="66" t="n"/>
-      <c r="H59" s="66" t="n"/>
-      <c r="I59" s="66" t="n"/>
-      <c r="J59" s="66" t="n"/>
-      <c r="K59" s="66" t="n"/>
-      <c r="L59" s="66" t="n"/>
-      <c r="M59" s="66" t="n"/>
-      <c r="N59" s="66" t="n"/>
-      <c r="O59" s="66" t="n"/>
+      <c r="A59" s="68" t="n"/>
+      <c r="B59" s="68" t="n"/>
+      <c r="C59" s="68" t="n"/>
+      <c r="D59" s="95" t="n"/>
+      <c r="E59" s="68" t="n"/>
+      <c r="F59" s="68" t="n"/>
+      <c r="G59" s="68" t="n"/>
+      <c r="H59" s="68" t="n"/>
+      <c r="I59" s="68" t="n"/>
+      <c r="J59" s="68" t="n"/>
+      <c r="K59" s="68" t="n"/>
+      <c r="L59" s="68" t="n"/>
+      <c r="M59" s="68" t="n"/>
+      <c r="N59" s="68" t="n"/>
+      <c r="O59" s="68" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="66" t="n"/>
-      <c r="B60" s="66" t="n"/>
-      <c r="C60" s="66" t="n"/>
-      <c r="D60" s="68" t="n"/>
-      <c r="E60" s="66" t="n"/>
-      <c r="F60" s="66" t="n"/>
-      <c r="G60" s="66" t="n"/>
-      <c r="H60" s="66" t="n"/>
-      <c r="I60" s="66" t="n"/>
-      <c r="J60" s="66" t="n"/>
-      <c r="K60" s="66" t="n"/>
-      <c r="L60" s="66" t="n"/>
-      <c r="M60" s="66" t="n"/>
-      <c r="N60" s="66" t="n"/>
-      <c r="O60" s="66" t="n"/>
+      <c r="A60" s="68" t="n"/>
+      <c r="B60" s="68" t="n"/>
+      <c r="C60" s="68" t="n"/>
+      <c r="D60" s="95" t="n"/>
+      <c r="E60" s="68" t="n"/>
+      <c r="F60" s="68" t="n"/>
+      <c r="G60" s="68" t="n"/>
+      <c r="H60" s="68" t="n"/>
+      <c r="I60" s="68" t="n"/>
+      <c r="J60" s="68" t="n"/>
+      <c r="K60" s="68" t="n"/>
+      <c r="L60" s="68" t="n"/>
+      <c r="M60" s="68" t="n"/>
+      <c r="N60" s="68" t="n"/>
+      <c r="O60" s="68" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="66" t="n"/>
-      <c r="C61" s="66" t="n"/>
-      <c r="D61" s="68" t="n"/>
-      <c r="E61" s="66" t="n"/>
-      <c r="F61" s="66" t="n"/>
-      <c r="G61" s="66" t="n"/>
-      <c r="H61" s="66" t="n"/>
-      <c r="I61" s="66" t="n"/>
-      <c r="J61" s="66" t="n"/>
-      <c r="K61" s="66" t="n"/>
-      <c r="L61" s="66" t="n"/>
+      <c r="B61" s="68" t="n"/>
+      <c r="C61" s="68" t="n"/>
+      <c r="D61" s="95" t="n"/>
+      <c r="E61" s="68" t="n"/>
+      <c r="F61" s="68" t="n"/>
+      <c r="G61" s="68" t="n"/>
+      <c r="H61" s="68" t="n"/>
+      <c r="I61" s="68" t="n"/>
+      <c r="J61" s="68" t="n"/>
+      <c r="K61" s="68" t="n"/>
+      <c r="L61" s="68" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>